--- a/pay.xlsx
+++ b/pay.xlsx
@@ -1,21 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E7B691E-7314-43AE-B6E2-DA9E9B78DCF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="191029" forceFullCalc="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="412">
   <si>
     <t>#</t>
   </si>
@@ -1256,23 +1272,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
@@ -1350,31 +1358,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="5" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="6" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="7" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1664,25 +1680,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I241"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="41.133" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="43.418" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="12.568" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="17.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="21.566" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="21.566" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="19.138" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="19.138" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1711,7 +1722,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1740,7 +1751,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1769,7 +1780,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -1798,7 +1809,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -1827,7 +1838,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -1856,7 +1867,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -1885,7 +1896,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -1914,7 +1925,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -1943,7 +1954,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -1972,7 +1983,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -2001,7 +2012,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -2030,7 +2041,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -2059,7 +2070,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -2088,7 +2099,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -2117,7 +2128,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -2146,7 +2157,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -2175,7 +2186,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -2204,7 +2215,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -2233,7 +2244,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -2262,7 +2273,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -2291,7 +2302,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -2320,7 +2331,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -2349,7 +2360,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -2378,7 +2389,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -2407,7 +2418,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -2436,7 +2447,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -2465,7 +2476,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -2494,7 +2505,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -2523,7 +2534,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -2552,7 +2563,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -2581,7 +2592,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -2610,7 +2621,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -2639,7 +2650,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -2668,7 +2679,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="6">
         <v>34</v>
       </c>
@@ -2697,7 +2708,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="6">
         <v>35</v>
       </c>
@@ -2726,7 +2737,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -2755,7 +2766,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="6">
         <v>37</v>
       </c>
@@ -2784,7 +2795,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -2813,7 +2824,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -2842,7 +2853,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -2871,7 +2882,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -2900,7 +2911,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -2929,7 +2940,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="6">
         <v>43</v>
       </c>
@@ -2958,7 +2969,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -2987,7 +2998,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -3016,7 +3027,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -3045,7 +3056,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -3074,7 +3085,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -3103,7 +3114,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>49</v>
       </c>
@@ -3132,7 +3143,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -3161,7 +3172,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -3190,7 +3201,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -3219,7 +3230,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="6">
         <v>53</v>
       </c>
@@ -3248,7 +3259,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>54</v>
       </c>
@@ -3277,7 +3288,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -3306,7 +3317,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -3335,7 +3346,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="6">
         <v>57</v>
       </c>
@@ -3364,7 +3375,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -3393,7 +3404,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
         <v>59</v>
       </c>
@@ -3422,7 +3433,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -3451,7 +3462,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>61</v>
       </c>
@@ -3480,7 +3491,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -3509,7 +3520,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -3538,7 +3549,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -3567,7 +3578,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -3596,7 +3607,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -3625,7 +3636,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
         <v>67</v>
       </c>
@@ -3654,7 +3665,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -3683,7 +3694,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -3712,7 +3723,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
         <v>70</v>
       </c>
@@ -3741,7 +3752,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
         <v>71</v>
       </c>
@@ -3770,7 +3781,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -3799,7 +3810,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
         <v>73</v>
       </c>
@@ -3828,7 +3839,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -3857,7 +3868,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
         <v>75</v>
       </c>
@@ -3886,7 +3897,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -3915,7 +3926,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
         <v>77</v>
       </c>
@@ -3944,7 +3955,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="6">
         <v>78</v>
       </c>
@@ -3973,7 +3984,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="6">
         <v>79</v>
       </c>
@@ -4002,7 +4013,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="6">
         <v>80</v>
       </c>
@@ -4031,7 +4042,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -4060,7 +4071,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>82</v>
       </c>
@@ -4089,7 +4100,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
         <v>83</v>
       </c>
@@ -4118,7 +4129,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -4147,7 +4158,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
         <v>85</v>
       </c>
@@ -4176,7 +4187,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -4205,7 +4216,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="6">
         <v>87</v>
       </c>
@@ -4234,7 +4245,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -4263,7 +4274,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
         <v>89</v>
       </c>
@@ -4292,7 +4303,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
         <v>90</v>
       </c>
@@ -4321,7 +4332,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="4">
         <v>91</v>
       </c>
@@ -4350,7 +4361,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
         <v>92</v>
       </c>
@@ -4379,7 +4390,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="4">
         <v>93</v>
       </c>
@@ -4408,7 +4419,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
         <v>94</v>
       </c>
@@ -4437,7 +4448,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" s="4">
         <v>95</v>
       </c>
@@ -4466,7 +4477,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" s="4">
         <v>96</v>
       </c>
@@ -4495,7 +4506,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="6">
         <v>97</v>
       </c>
@@ -4524,7 +4535,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="6">
         <v>98</v>
       </c>
@@ -4553,7 +4564,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>99</v>
       </c>
@@ -4582,7 +4593,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -4611,7 +4622,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="6">
         <v>101</v>
       </c>
@@ -4640,7 +4651,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="4">
         <v>102</v>
       </c>
@@ -4669,7 +4680,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" s="4">
         <v>103</v>
       </c>
@@ -4698,7 +4709,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
         <v>104</v>
       </c>
@@ -4727,7 +4738,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="4">
         <v>105</v>
       </c>
@@ -4756,7 +4767,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -4785,7 +4796,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="6">
         <v>107</v>
       </c>
@@ -4814,7 +4825,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="6">
         <v>108</v>
       </c>
@@ -4843,7 +4854,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="6">
         <v>109</v>
       </c>
@@ -4872,7 +4883,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="6">
         <v>110</v>
       </c>
@@ -4901,7 +4912,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
         <v>111</v>
       </c>
@@ -4930,7 +4941,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>112</v>
       </c>
@@ -4949,8 +4960,8 @@
       <c r="F113" s="5">
         <v>0</v>
       </c>
-      <c r="G113" s="5" t="s">
-        <v>12</v>
+      <c r="G113" s="5">
+        <v>0</v>
       </c>
       <c r="H113" s="5" t="s">
         <v>60</v>
@@ -4959,7 +4970,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
         <v>113</v>
       </c>
@@ -4988,7 +4999,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" s="4">
         <v>114</v>
       </c>
@@ -5017,7 +5028,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="116" spans="1:9">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="4">
         <v>115</v>
       </c>
@@ -5046,7 +5057,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>116</v>
       </c>
@@ -5075,7 +5086,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="4">
         <v>117</v>
       </c>
@@ -5104,7 +5115,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>118</v>
       </c>
@@ -5133,7 +5144,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="5">
         <v>119</v>
       </c>
@@ -5162,7 +5173,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="6">
         <v>120</v>
       </c>
@@ -5191,7 +5202,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="122" spans="1:9">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="6">
         <v>121</v>
       </c>
@@ -5220,7 +5231,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:9">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="6">
         <v>122</v>
       </c>
@@ -5249,7 +5260,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="124" spans="1:9">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
         <v>123</v>
       </c>
@@ -5278,7 +5289,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="125" spans="1:9">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <v>124</v>
       </c>
@@ -5307,7 +5318,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="126" spans="1:9">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
         <v>125</v>
       </c>
@@ -5336,7 +5347,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="127" spans="1:9">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>126</v>
       </c>
@@ -5365,7 +5376,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="128" spans="1:9">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
         <v>127</v>
       </c>
@@ -5394,7 +5405,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="129" spans="1:9">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="4">
         <v>128</v>
       </c>
@@ -5423,7 +5434,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="4">
         <v>129</v>
       </c>
@@ -5452,7 +5463,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="131" spans="1:9">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="4">
         <v>130</v>
       </c>
@@ -5481,7 +5492,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="132" spans="1:9">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="5">
         <v>131</v>
       </c>
@@ -5510,7 +5521,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="133" spans="1:9">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="4">
         <v>132</v>
       </c>
@@ -5539,7 +5550,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="134" spans="1:9">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
         <v>133</v>
       </c>
@@ -5568,7 +5579,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="135" spans="1:9">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -5597,7 +5608,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="136" spans="1:9">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="5">
         <v>135</v>
       </c>
@@ -5626,7 +5637,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="137" spans="1:9">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
         <v>136</v>
       </c>
@@ -5655,7 +5666,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="138" spans="1:9">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
         <v>137</v>
       </c>
@@ -5684,7 +5695,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="139" spans="1:9">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
         <v>138</v>
       </c>
@@ -5713,7 +5724,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="140" spans="1:9">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="4">
         <v>139</v>
       </c>
@@ -5742,7 +5753,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="141" spans="1:9">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -5771,7 +5782,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="142" spans="1:9">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" s="4">
         <v>141</v>
       </c>
@@ -5800,7 +5811,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="143" spans="1:9">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
         <v>142</v>
       </c>
@@ -5829,7 +5840,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="144" spans="1:9">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
         <v>143</v>
       </c>
@@ -5858,7 +5869,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="145" spans="1:9">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -5887,7 +5898,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="146" spans="1:9">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="6">
         <v>145</v>
       </c>
@@ -5916,7 +5927,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="147" spans="1:9">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="6">
         <v>146</v>
       </c>
@@ -5945,7 +5956,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="148" spans="1:9">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" s="6">
         <v>147</v>
       </c>
@@ -5974,7 +5985,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="149" spans="1:9">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" s="6">
         <v>148</v>
       </c>
@@ -6003,7 +6014,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="150" spans="1:9">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="6">
         <v>149</v>
       </c>
@@ -6032,7 +6043,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="151" spans="1:9">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
         <v>150</v>
       </c>
@@ -6061,7 +6072,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="152" spans="1:9">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
         <v>151</v>
       </c>
@@ -6090,7 +6101,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="153" spans="1:9">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="4">
         <v>152</v>
       </c>
@@ -6119,7 +6130,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="154" spans="1:9">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" s="5">
         <v>153</v>
       </c>
@@ -6148,7 +6159,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="155" spans="1:9">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" s="6">
         <v>154</v>
       </c>
@@ -6177,7 +6188,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="156" spans="1:9">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" s="4">
         <v>155</v>
       </c>
@@ -6206,7 +6217,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="157" spans="1:9">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" s="6">
         <v>156</v>
       </c>
@@ -6235,7 +6246,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="158" spans="1:9">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" s="4">
         <v>157</v>
       </c>
@@ -6264,7 +6275,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="159" spans="1:9">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
         <v>158</v>
       </c>
@@ -6293,7 +6304,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="160" spans="1:9">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" s="6">
         <v>159</v>
       </c>
@@ -6322,7 +6333,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="161" spans="1:9">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" s="4">
         <v>160</v>
       </c>
@@ -6351,7 +6362,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="162" spans="1:9">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" s="4">
         <v>161</v>
       </c>
@@ -6380,7 +6391,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="163" spans="1:9">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" s="6">
         <v>162</v>
       </c>
@@ -6409,7 +6420,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="164" spans="1:9">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
         <v>163</v>
       </c>
@@ -6438,7 +6449,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="165" spans="1:9">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" s="5">
         <v>164</v>
       </c>
@@ -6467,7 +6478,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="166" spans="1:9">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" s="4">
         <v>165</v>
       </c>
@@ -6496,7 +6507,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="167" spans="1:9">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" s="4">
         <v>166</v>
       </c>
@@ -6525,7 +6536,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="168" spans="1:9">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" s="5">
         <v>167</v>
       </c>
@@ -6554,7 +6565,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="169" spans="1:9">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" s="4">
         <v>168</v>
       </c>
@@ -6583,7 +6594,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="170" spans="1:9">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" s="6">
         <v>169</v>
       </c>
@@ -6612,7 +6623,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="171" spans="1:9">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" s="4">
         <v>170</v>
       </c>
@@ -6641,7 +6652,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="172" spans="1:9">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
         <v>171</v>
       </c>
@@ -6670,7 +6681,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="173" spans="1:9">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" s="3">
         <v>172</v>
       </c>
@@ -6699,7 +6710,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="174" spans="1:9">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" s="4">
         <v>173</v>
       </c>
@@ -6728,7 +6739,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="175" spans="1:9">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" s="4">
         <v>174</v>
       </c>
@@ -6757,7 +6768,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="176" spans="1:9">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" s="4">
         <v>175</v>
       </c>
@@ -6786,7 +6797,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="177" spans="1:9">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" s="2">
         <v>176</v>
       </c>
@@ -6815,7 +6826,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="178" spans="1:9">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" s="4">
         <v>177</v>
       </c>
@@ -6844,7 +6855,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="179" spans="1:9">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" s="2">
         <v>178</v>
       </c>
@@ -6873,7 +6884,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="180" spans="1:9">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" s="4">
         <v>179</v>
       </c>
@@ -6902,7 +6913,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="181" spans="1:9">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" s="6">
         <v>180</v>
       </c>
@@ -6931,7 +6942,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="182" spans="1:9">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" s="5">
         <v>181</v>
       </c>
@@ -6960,7 +6971,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="183" spans="1:9">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" s="6">
         <v>182</v>
       </c>
@@ -6989,7 +7000,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="184" spans="1:9">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" s="4">
         <v>183</v>
       </c>
@@ -7018,7 +7029,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="185" spans="1:9">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" s="3">
         <v>184</v>
       </c>
@@ -7047,7 +7058,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="186" spans="1:9">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" s="2">
         <v>185</v>
       </c>
@@ -7076,7 +7087,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="187" spans="1:9">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" s="6">
         <v>186</v>
       </c>
@@ -7105,7 +7116,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="188" spans="1:9">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" s="6">
         <v>187</v>
       </c>
@@ -7134,7 +7145,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="189" spans="1:9">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" s="6">
         <v>188</v>
       </c>
@@ -7163,7 +7174,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="190" spans="1:9">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" s="2">
         <v>189</v>
       </c>
@@ -7192,7 +7203,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="191" spans="1:9">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" s="2">
         <v>190</v>
       </c>
@@ -7221,7 +7232,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="192" spans="1:9">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" s="2">
         <v>191</v>
       </c>
@@ -7250,7 +7261,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="193" spans="1:9">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" s="6">
         <v>192</v>
       </c>
@@ -7279,7 +7290,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="194" spans="1:9">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" s="5">
         <v>193</v>
       </c>
@@ -7308,7 +7319,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="195" spans="1:9">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" s="3">
         <v>194</v>
       </c>
@@ -7337,7 +7348,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="196" spans="1:9">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
         <v>195</v>
       </c>
@@ -7366,7 +7377,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="197" spans="1:9">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" s="4">
         <v>196</v>
       </c>
@@ -7395,7 +7406,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="198" spans="1:9">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" s="5">
         <v>197</v>
       </c>
@@ -7424,7 +7435,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="199" spans="1:9">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" s="5">
         <v>198</v>
       </c>
@@ -7453,7 +7464,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="200" spans="1:9">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" s="2">
         <v>199</v>
       </c>
@@ -7482,7 +7493,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="201" spans="1:9">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" s="4">
         <v>200</v>
       </c>
@@ -7511,7 +7522,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="202" spans="1:9">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="5">
         <v>201</v>
       </c>
@@ -7540,7 +7551,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="203" spans="1:9">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" s="4">
         <v>202</v>
       </c>
@@ -7569,7 +7580,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="204" spans="1:9">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" s="4">
         <v>203</v>
       </c>
@@ -7598,7 +7609,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="205" spans="1:9">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" s="4">
         <v>204</v>
       </c>
@@ -7627,7 +7638,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="206" spans="1:9">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" s="4">
         <v>205</v>
       </c>
@@ -7656,7 +7667,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="207" spans="1:9">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" s="6">
         <v>206</v>
       </c>
@@ -7685,7 +7696,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="208" spans="1:9">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" s="3">
         <v>207</v>
       </c>
@@ -7714,7 +7725,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="209" spans="1:9">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" s="4">
         <v>208</v>
       </c>
@@ -7743,7 +7754,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="210" spans="1:9">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" s="4">
         <v>209</v>
       </c>
@@ -7772,7 +7783,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="211" spans="1:9">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" s="2">
         <v>210</v>
       </c>
@@ -7801,7 +7812,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="212" spans="1:9">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" s="4">
         <v>211</v>
       </c>
@@ -7830,7 +7841,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="213" spans="1:9">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" s="4">
         <v>212</v>
       </c>
@@ -7859,7 +7870,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="214" spans="1:9">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" s="5">
         <v>213</v>
       </c>
@@ -7888,7 +7899,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="215" spans="1:9">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" s="5">
         <v>214</v>
       </c>
@@ -7917,7 +7928,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="216" spans="1:9">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" s="4">
         <v>215</v>
       </c>
@@ -7946,7 +7957,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="217" spans="1:9">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" s="4">
         <v>216</v>
       </c>
@@ -7975,7 +7986,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="218" spans="1:9">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" s="5">
         <v>217</v>
       </c>
@@ -8004,7 +8015,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="219" spans="1:9">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" s="6">
         <v>218</v>
       </c>
@@ -8033,7 +8044,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="220" spans="1:9">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" s="4">
         <v>219</v>
       </c>
@@ -8062,7 +8073,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="221" spans="1:9">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" s="5">
         <v>220</v>
       </c>
@@ -8091,7 +8102,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="222" spans="1:9">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" s="4">
         <v>221</v>
       </c>
@@ -8120,7 +8131,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="223" spans="1:9">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" s="4">
         <v>222</v>
       </c>
@@ -8149,7 +8160,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="224" spans="1:9">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" s="5">
         <v>223</v>
       </c>
@@ -8178,7 +8189,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="225" spans="1:9">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" s="2">
         <v>224</v>
       </c>
@@ -8207,7 +8218,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="226" spans="1:9">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" s="2">
         <v>225</v>
       </c>
@@ -8236,7 +8247,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="227" spans="1:9">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" s="4">
         <v>226</v>
       </c>
@@ -8265,7 +8276,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="228" spans="1:9">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" s="6">
         <v>227</v>
       </c>
@@ -8294,7 +8305,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="229" spans="1:9">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" s="4">
         <v>228</v>
       </c>
@@ -8323,7 +8334,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="230" spans="1:9">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" s="6">
         <v>229</v>
       </c>
@@ -8352,7 +8363,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="231" spans="1:9">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" s="4">
         <v>230</v>
       </c>
@@ -8381,7 +8392,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="232" spans="1:9">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" s="2">
         <v>231</v>
       </c>
@@ -8410,7 +8421,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="233" spans="1:9">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" s="4">
         <v>232</v>
       </c>
@@ -8439,7 +8450,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="234" spans="1:9">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" s="2">
         <v>233</v>
       </c>
@@ -8468,7 +8479,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="235" spans="1:9">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" s="5">
         <v>234</v>
       </c>
@@ -8497,7 +8508,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="236" spans="1:9">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" s="6">
         <v>235</v>
       </c>
@@ -8526,7 +8537,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="237" spans="1:9">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" s="4">
         <v>236</v>
       </c>
@@ -8555,7 +8566,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="238" spans="1:9">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" s="4">
         <v>237</v>
       </c>
@@ -8584,7 +8595,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="239" spans="1:9">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" s="4">
         <v>238</v>
       </c>
@@ -8613,7 +8624,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="240" spans="1:9">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" s="6">
         <v>239</v>
       </c>
@@ -8642,7 +8653,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="241" spans="1:9">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" s="6">
         <v>240</v>
       </c>
@@ -8672,17 +8683,6 @@
       </c>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>
--- a/pay.xlsx
+++ b/pay.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E7B691E-7314-43AE-B6E2-DA9E9B78DCF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B263B3B-EABF-460D-B235-0119B25E786F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1032" windowWidth="21600" windowHeight="11208" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="412">
   <si>
     <t>#</t>
   </si>
@@ -7077,8 +7077,8 @@
       <c r="F186" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G186" s="2" t="s">
-        <v>14</v>
+      <c r="G186" s="2">
+        <v>0</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>

--- a/pay.xlsx
+++ b/pay.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B263B3B-EABF-460D-B235-0119B25E786F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5A0E01-5D10-4944-881C-680CB302074B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1032" windowWidth="21600" windowHeight="11208" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="411">
   <si>
     <t>#</t>
   </si>
@@ -814,9 +814,6 @@
   </si>
   <si>
     <t>طارق صلاح ياسر موسى</t>
-  </si>
-  <si>
-    <t>775,000</t>
   </si>
   <si>
     <t>61.73%</t>
@@ -5946,11 +5943,11 @@
       <c r="F147" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="G147" s="6" t="s">
+      <c r="G147" s="6">
+        <v>0</v>
+      </c>
+      <c r="H147" s="6" t="s">
         <v>261</v>
-      </c>
-      <c r="H147" s="6" t="s">
-        <v>262</v>
       </c>
       <c r="I147" s="6" t="s">
         <v>67</v>
@@ -5961,7 +5958,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>10</v>
@@ -5990,7 +5987,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>10</v>
@@ -6019,25 +6016,25 @@
         <v>149</v>
       </c>
       <c r="B150" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E150" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F150" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="C150" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D150" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="E150" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F150" s="6" t="s">
+      <c r="G150" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="G150" s="6" t="s">
+      <c r="H150" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H150" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I150" s="6" t="s">
         <v>67</v>
@@ -6048,25 +6045,25 @@
         <v>150</v>
       </c>
       <c r="B151" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F151" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="C151" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D151" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E151" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F151" s="2" t="s">
+      <c r="G151" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="G151" s="2" t="s">
+      <c r="H151" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="H151" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="I151" s="2" t="s">
         <v>16</v>
@@ -6077,25 +6074,25 @@
         <v>151</v>
       </c>
       <c r="B152" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F152" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="C152" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F152" s="2" t="s">
+      <c r="G152" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="G152" s="2" t="s">
+      <c r="H152" s="2" t="s">
         <v>275</v>
-      </c>
-      <c r="H152" s="2" t="s">
-        <v>276</v>
       </c>
       <c r="I152" s="2" t="s">
         <v>16</v>
@@ -6106,7 +6103,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>10</v>
@@ -6135,7 +6132,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C154" s="5" t="s">
         <v>10</v>
@@ -6153,7 +6150,7 @@
         <v>167</v>
       </c>
       <c r="H154" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I154" s="5" t="s">
         <v>61</v>
@@ -6164,7 +6161,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>10</v>
@@ -6179,10 +6176,10 @@
         <v>124</v>
       </c>
       <c r="G155" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="H155" s="6" t="s">
         <v>281</v>
-      </c>
-      <c r="H155" s="6" t="s">
-        <v>282</v>
       </c>
       <c r="I155" s="6" t="s">
         <v>67</v>
@@ -6193,7 +6190,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>10</v>
@@ -6222,7 +6219,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>10</v>
@@ -6251,7 +6248,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>10</v>
@@ -6280,7 +6277,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>10</v>
@@ -6292,13 +6289,13 @@
         <v>45</v>
       </c>
       <c r="F159" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G159" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="G159" s="2" t="s">
-        <v>288</v>
-      </c>
       <c r="H159" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I159" s="2" t="s">
         <v>16</v>
@@ -6309,7 +6306,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>10</v>
@@ -6338,7 +6335,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>10</v>
@@ -6367,7 +6364,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>10</v>
@@ -6396,7 +6393,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>10</v>
@@ -6425,7 +6422,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>10</v>
@@ -6454,25 +6451,25 @@
         <v>164</v>
       </c>
       <c r="B165" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D165" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="E165" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F165" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="C165" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D165" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="E165" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F165" s="5" t="s">
+      <c r="G165" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="G165" s="5" t="s">
+      <c r="H165" s="5" t="s">
         <v>296</v>
-      </c>
-      <c r="H165" s="5" t="s">
-        <v>297</v>
       </c>
       <c r="I165" s="5" t="s">
         <v>61</v>
@@ -6483,7 +6480,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>10</v>
@@ -6512,7 +6509,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>10</v>
@@ -6541,7 +6538,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C168" s="5" t="s">
         <v>10</v>
@@ -6570,7 +6567,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>10</v>
@@ -6599,7 +6596,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>10</v>
@@ -6614,10 +6611,10 @@
         <v>152</v>
       </c>
       <c r="G170" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="H170" s="6" t="s">
         <v>303</v>
-      </c>
-      <c r="H170" s="6" t="s">
-        <v>304</v>
       </c>
       <c r="I170" s="6" t="s">
         <v>67</v>
@@ -6628,7 +6625,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>10</v>
@@ -6657,7 +6654,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>10</v>
@@ -6686,25 +6683,25 @@
         <v>172</v>
       </c>
       <c r="B173" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E173" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F173" s="3" t="s">
         <v>307</v>
-      </c>
-      <c r="C173" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D173" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E173" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F173" s="3" t="s">
-        <v>308</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H173" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I173" s="3" t="s">
         <v>21</v>
@@ -6715,7 +6712,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>10</v>
@@ -6744,7 +6741,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>10</v>
@@ -6773,7 +6770,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>10</v>
@@ -6802,7 +6799,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>10</v>
@@ -6831,7 +6828,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>10</v>
@@ -6860,7 +6857,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>10</v>
@@ -6889,7 +6886,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>10</v>
@@ -6918,7 +6915,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>10</v>
@@ -6947,7 +6944,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C182" s="5" t="s">
         <v>10</v>
@@ -6976,7 +6973,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>10</v>
@@ -6994,7 +6991,7 @@
         <v>205</v>
       </c>
       <c r="H183" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I183" s="6" t="s">
         <v>67</v>
@@ -7005,7 +7002,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>10</v>
@@ -7034,7 +7031,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C185" s="3" t="s">
         <v>10</v>
@@ -7063,7 +7060,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>10</v>
@@ -7092,7 +7089,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C187" s="6" t="s">
         <v>10</v>
@@ -7104,13 +7101,13 @@
         <v>46</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G187" s="6" t="s">
         <v>226</v>
       </c>
       <c r="H187" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I187" s="6" t="s">
         <v>67</v>
@@ -7121,7 +7118,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>10</v>
@@ -7136,10 +7133,10 @@
         <v>124</v>
       </c>
       <c r="G188" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="H188" s="6" t="s">
         <v>328</v>
-      </c>
-      <c r="H188" s="6" t="s">
-        <v>329</v>
       </c>
       <c r="I188" s="6" t="s">
         <v>67</v>
@@ -7150,7 +7147,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>10</v>
@@ -7165,7 +7162,7 @@
         <v>152</v>
       </c>
       <c r="G189" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H189" s="6" t="s">
         <v>66</v>
@@ -7179,7 +7176,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>10</v>
@@ -7197,7 +7194,7 @@
         <v>168</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I190" s="2" t="s">
         <v>16</v>
@@ -7208,7 +7205,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>10</v>
@@ -7237,7 +7234,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>10</v>
@@ -7266,7 +7263,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>10</v>
@@ -7281,10 +7278,10 @@
         <v>191</v>
       </c>
       <c r="G193" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="H193" s="6" t="s">
         <v>337</v>
-      </c>
-      <c r="H193" s="6" t="s">
-        <v>338</v>
       </c>
       <c r="I193" s="6" t="s">
         <v>67</v>
@@ -7295,7 +7292,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C194" s="5" t="s">
         <v>10</v>
@@ -7313,7 +7310,7 @@
         <v>167</v>
       </c>
       <c r="H194" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I194" s="5" t="s">
         <v>61</v>
@@ -7324,7 +7321,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C195" s="3" t="s">
         <v>10</v>
@@ -7339,10 +7336,10 @@
         <v>221</v>
       </c>
       <c r="G195" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="H195" s="3" t="s">
         <v>341</v>
-      </c>
-      <c r="H195" s="3" t="s">
-        <v>342</v>
       </c>
       <c r="I195" s="3" t="s">
         <v>21</v>
@@ -7353,25 +7350,25 @@
         <v>195</v>
       </c>
       <c r="B196" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F196" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="C196" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D196" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E196" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F196" s="3" t="s">
+      <c r="G196" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="G196" s="3" t="s">
+      <c r="H196" s="3" t="s">
         <v>345</v>
-      </c>
-      <c r="H196" s="3" t="s">
-        <v>346</v>
       </c>
       <c r="I196" s="3" t="s">
         <v>21</v>
@@ -7382,7 +7379,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C197" s="4" t="s">
         <v>10</v>
@@ -7411,7 +7408,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C198" s="5" t="s">
         <v>10</v>
@@ -7440,7 +7437,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C199" s="5" t="s">
         <v>10</v>
@@ -7469,7 +7466,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>10</v>
@@ -7481,13 +7478,13 @@
         <v>12</v>
       </c>
       <c r="F200" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="G200" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="G200" s="2" t="s">
+      <c r="H200" s="2" t="s">
         <v>275</v>
-      </c>
-      <c r="H200" s="2" t="s">
-        <v>276</v>
       </c>
       <c r="I200" s="2" t="s">
         <v>16</v>
@@ -7498,7 +7495,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C201" s="4" t="s">
         <v>10</v>
@@ -7527,7 +7524,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C202" s="5" t="s">
         <v>10</v>
@@ -7556,7 +7553,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C203" s="4" t="s">
         <v>10</v>
@@ -7585,7 +7582,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C204" s="4" t="s">
         <v>10</v>
@@ -7614,7 +7611,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C205" s="4" t="s">
         <v>10</v>
@@ -7643,7 +7640,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C206" s="4" t="s">
         <v>10</v>
@@ -7672,7 +7669,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C207" s="6" t="s">
         <v>10</v>
@@ -7687,10 +7684,10 @@
         <v>163</v>
       </c>
       <c r="G207" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="H207" s="6" t="s">
         <v>358</v>
-      </c>
-      <c r="H207" s="6" t="s">
-        <v>359</v>
       </c>
       <c r="I207" s="6" t="s">
         <v>67</v>
@@ -7701,7 +7698,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C208" s="3" t="s">
         <v>10</v>
@@ -7730,7 +7727,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C209" s="4" t="s">
         <v>10</v>
@@ -7759,7 +7756,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C210" s="4" t="s">
         <v>10</v>
@@ -7788,25 +7785,25 @@
         <v>210</v>
       </c>
       <c r="B211" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F211" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C211" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D211" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E211" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F211" s="2" t="s">
+      <c r="G211" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="G211" s="2" t="s">
+      <c r="H211" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="H211" s="2" t="s">
-        <v>366</v>
       </c>
       <c r="I211" s="2" t="s">
         <v>16</v>
@@ -7817,7 +7814,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C212" s="4" t="s">
         <v>10</v>
@@ -7846,7 +7843,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C213" s="4" t="s">
         <v>10</v>
@@ -7875,7 +7872,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C214" s="5" t="s">
         <v>10</v>
@@ -7904,7 +7901,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C215" s="5" t="s">
         <v>10</v>
@@ -7922,7 +7919,7 @@
         <v>129</v>
       </c>
       <c r="H215" s="5" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="I215" s="5" t="s">
         <v>61</v>
@@ -7933,7 +7930,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C216" s="4" t="s">
         <v>10</v>
@@ -7962,7 +7959,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C217" s="4" t="s">
         <v>10</v>
@@ -7991,7 +7988,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C218" s="5" t="s">
         <v>10</v>
@@ -8020,7 +8017,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>10</v>
@@ -8049,7 +8046,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C220" s="4" t="s">
         <v>10</v>
@@ -8078,7 +8075,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C221" s="5" t="s">
         <v>10</v>
@@ -8107,7 +8104,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C222" s="4" t="s">
         <v>10</v>
@@ -8136,7 +8133,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C223" s="4" t="s">
         <v>10</v>
@@ -8165,7 +8162,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C224" s="5" t="s">
         <v>10</v>
@@ -8194,7 +8191,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>10</v>
@@ -8223,7 +8220,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>10</v>
@@ -8235,13 +8232,13 @@
         <v>18</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>41</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I226" s="2" t="s">
         <v>16</v>
@@ -8252,7 +8249,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C227" s="4" t="s">
         <v>10</v>
@@ -8281,25 +8278,25 @@
         <v>227</v>
       </c>
       <c r="B228" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="C228" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D228" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E228" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F228" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="C228" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D228" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="E228" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F228" s="6" t="s">
+      <c r="G228" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="G228" s="6" t="s">
+      <c r="H228" s="6" t="s">
         <v>386</v>
-      </c>
-      <c r="H228" s="6" t="s">
-        <v>387</v>
       </c>
       <c r="I228" s="6" t="s">
         <v>67</v>
@@ -8310,7 +8307,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C229" s="4" t="s">
         <v>10</v>
@@ -8339,7 +8336,7 @@
         <v>229</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C230" s="6" t="s">
         <v>10</v>
@@ -8354,7 +8351,7 @@
         <v>70</v>
       </c>
       <c r="G230" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H230" s="6" t="s">
         <v>154</v>
@@ -8368,7 +8365,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C231" s="4" t="s">
         <v>10</v>
@@ -8377,10 +8374,10 @@
         <v>174</v>
       </c>
       <c r="E231" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G231" s="4">
         <v>0</v>
@@ -8397,7 +8394,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>10</v>
@@ -8412,10 +8409,10 @@
         <v>13</v>
       </c>
       <c r="G232" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="H232" s="2" t="s">
         <v>394</v>
-      </c>
-      <c r="H232" s="2" t="s">
-        <v>395</v>
       </c>
       <c r="I232" s="2" t="s">
         <v>16</v>
@@ -8426,7 +8423,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C233" s="4" t="s">
         <v>10</v>
@@ -8455,7 +8452,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>10</v>
@@ -8467,13 +8464,13 @@
         <v>12</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I234" s="2" t="s">
         <v>16</v>
@@ -8484,7 +8481,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C235" s="5" t="s">
         <v>10</v>
@@ -8496,13 +8493,13 @@
         <v>12</v>
       </c>
       <c r="F235" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="G235" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="G235" s="5" t="s">
+      <c r="H235" s="5" t="s">
         <v>401</v>
-      </c>
-      <c r="H235" s="5" t="s">
-        <v>402</v>
       </c>
       <c r="I235" s="5" t="s">
         <v>61</v>
@@ -8513,7 +8510,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C236" s="6" t="s">
         <v>10</v>
@@ -8522,16 +8519,16 @@
         <v>174</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F236" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G236" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="H236" s="6" t="s">
         <v>404</v>
-      </c>
-      <c r="H236" s="6" t="s">
-        <v>405</v>
       </c>
       <c r="I236" s="6" t="s">
         <v>67</v>
@@ -8542,7 +8539,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C237" s="4" t="s">
         <v>10</v>
@@ -8571,7 +8568,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C238" s="4" t="s">
         <v>10</v>
@@ -8600,7 +8597,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C239" s="4" t="s">
         <v>10</v>
@@ -8629,7 +8626,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C240" s="6" t="s">
         <v>10</v>
@@ -8647,7 +8644,7 @@
         <v>18</v>
       </c>
       <c r="H240" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I240" s="6" t="s">
         <v>67</v>
@@ -8658,7 +8655,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C241" s="6" t="s">
         <v>10</v>
@@ -8673,10 +8670,10 @@
         <v>124</v>
       </c>
       <c r="G241" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="H241" s="6" t="s">
         <v>281</v>
-      </c>
-      <c r="H241" s="6" t="s">
-        <v>282</v>
       </c>
       <c r="I241" s="6" t="s">
         <v>67</v>

--- a/pay.xlsx
+++ b/pay.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5A0E01-5D10-4944-881C-680CB302074B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92768251-D18B-436E-A8DA-203A58A1EBDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="411">
   <si>
     <t>#</t>
   </si>
@@ -1354,7 +1354,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1372,6 +1372,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6871,8 +6874,8 @@
       <c r="F179" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="G179" s="2" t="s">
-        <v>168</v>
+      <c r="G179" s="7">
+        <v>0</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>169</v>

--- a/pay.xlsx
+++ b/pay.xlsx
@@ -1,37 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92768251-D18B-436E-A8DA-203A58A1EBDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" forceFullCalc="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="406">
   <si>
     <t>#</t>
   </si>
@@ -636,10 +620,10 @@
     <t>2,137,500</t>
   </si>
   <si>
-    <t>1,037,500</t>
-  </si>
-  <si>
-    <t>51.46%</t>
+    <t>637,500</t>
+  </si>
+  <si>
+    <t>70.18%</t>
   </si>
   <si>
     <t>افنان ناجي سليم عواد</t>
@@ -648,30 +632,30 @@
     <t>الحسين محمد علي صالح</t>
   </si>
   <si>
+    <t>امير علي احمد فريدون محمد</t>
+  </si>
+  <si>
+    <t>ايناس عبد السلام حسن عوده</t>
+  </si>
+  <si>
+    <t>أمير فراس زهير حسن</t>
+  </si>
+  <si>
+    <t>بنين حسين علي صباح</t>
+  </si>
+  <si>
+    <t>بنين حميد هاشم شريف</t>
+  </si>
+  <si>
+    <t>جاسم محمد عبد الله عبد</t>
+  </si>
+  <si>
+    <t>جعفر نضال كاظم احمد</t>
+  </si>
+  <si>
     <t>900,000</t>
   </si>
   <si>
-    <t>امير علي احمد فريدون محمد</t>
-  </si>
-  <si>
-    <t>ايناس عبد السلام حسن عوده</t>
-  </si>
-  <si>
-    <t>أمير فراس زهير حسن</t>
-  </si>
-  <si>
-    <t>بنين حسين علي صباح</t>
-  </si>
-  <si>
-    <t>بنين حميد هاشم شريف</t>
-  </si>
-  <si>
-    <t>جاسم محمد عبد الله عبد</t>
-  </si>
-  <si>
-    <t>جعفر نضال كاظم احمد</t>
-  </si>
-  <si>
     <t>1,350,000</t>
   </si>
   <si>
@@ -729,9 +713,6 @@
     <t>حيدر حبيب كاظم جواد</t>
   </si>
   <si>
-    <t>46.67%</t>
-  </si>
-  <si>
     <t>حيدر صفاء غازي حسن</t>
   </si>
   <si>
@@ -759,6 +740,9 @@
     <t>ريم حاتم جابر دحيح</t>
   </si>
   <si>
+    <t>90%</t>
+  </si>
+  <si>
     <t>ريم يونس مزيغر منصور</t>
   </si>
   <si>
@@ -816,6 +800,9 @@
     <t>طارق صلاح ياسر موسى</t>
   </si>
   <si>
+    <t>775,000</t>
+  </si>
+  <si>
     <t>61.73%</t>
   </si>
   <si>
@@ -828,15 +815,6 @@
     <t>عباس علي حسين علي</t>
   </si>
   <si>
-    <t>1,660,000</t>
-  </si>
-  <si>
-    <t>590,000</t>
-  </si>
-  <si>
-    <t>73.78%</t>
-  </si>
-  <si>
     <t>عبد الجليل خالد عبد الجليل ثعبان</t>
   </si>
   <si>
@@ -918,310 +896,301 @@
     <t>375,000</t>
   </si>
   <si>
+    <t>محمد صلاح خالد جلاب</t>
+  </si>
+  <si>
+    <t>محمد فراس جبير ابراهيم</t>
+  </si>
+  <si>
+    <t>محمد وليد خالد رشيد</t>
+  </si>
+  <si>
+    <t>مصطفى اياد محمد جاسم</t>
+  </si>
+  <si>
+    <t>مصطفى شاكر محمود محمد</t>
+  </si>
+  <si>
+    <t>487,500</t>
+  </si>
+  <si>
+    <t>71.11%</t>
+  </si>
+  <si>
+    <t>مصطفى علاء داود موسى</t>
+  </si>
+  <si>
+    <t>مصطفى علي ناصر حسين</t>
+  </si>
+  <si>
+    <t>مصطفى محمد علي طه</t>
+  </si>
+  <si>
+    <t>675,000</t>
+  </si>
+  <si>
+    <t>60%</t>
+  </si>
+  <si>
+    <t>معتز محمود مطر حسين</t>
+  </si>
+  <si>
+    <t>ملاك عباس عبد علي</t>
+  </si>
+  <si>
+    <t>منقذ عبد الكريم حسين كاظم</t>
+  </si>
+  <si>
+    <t>موده شهاب احمد راكع</t>
+  </si>
+  <si>
+    <t>مؤمن محمد قادر شاواز</t>
+  </si>
+  <si>
+    <t>ميس محمد عصام عبد الوهاب</t>
+  </si>
+  <si>
+    <t>نور ابراهيم خالد محمد</t>
+  </si>
+  <si>
+    <t>يوسف سيف محي جواد</t>
+  </si>
+  <si>
+    <t>يوسف شاكر سالم خلف</t>
+  </si>
+  <si>
+    <t>يوسف نزار هادي ثجيل</t>
+  </si>
+  <si>
+    <t>محمد حذيفة فليح حسن</t>
+  </si>
+  <si>
+    <t>حوراء محمد حسان ناجي</t>
+  </si>
+  <si>
+    <t>رقيه علاء صادق</t>
+  </si>
+  <si>
+    <t>مريم احمد محمود عبيد</t>
+  </si>
+  <si>
+    <t>1,375,000</t>
+  </si>
+  <si>
+    <t>67.9%</t>
+  </si>
+  <si>
+    <t>دينا اسعد حسين محمد</t>
+  </si>
+  <si>
+    <t>587,500</t>
+  </si>
+  <si>
+    <t>65.19%</t>
+  </si>
+  <si>
+    <t>تقى جعفر لعيبي جبار</t>
+  </si>
+  <si>
+    <t>600,000</t>
+  </si>
+  <si>
+    <t>اسياد اياد نايف عبد الحسين</t>
+  </si>
+  <si>
+    <t>80.25%</t>
+  </si>
+  <si>
+    <t>شمس مشتاق طالب علي</t>
+  </si>
+  <si>
+    <t>ترتيل عباس شهاب عبود</t>
+  </si>
+  <si>
+    <t>منتهى وسام عبد حسن حواس</t>
+  </si>
+  <si>
+    <t>975,000</t>
+  </si>
+  <si>
+    <t>51.85%</t>
+  </si>
+  <si>
+    <t>شايان مهدي داود عوده</t>
+  </si>
+  <si>
+    <t>احمد داود سلمان محمد</t>
+  </si>
+  <si>
+    <t>565,000</t>
+  </si>
+  <si>
+    <t>49.78%</t>
+  </si>
+  <si>
+    <t>احمد عبد الرحيم ابراهيم العسكري</t>
+  </si>
+  <si>
+    <t>860,000</t>
+  </si>
+  <si>
+    <t>1,390,000</t>
+  </si>
+  <si>
+    <t>38.22%</t>
+  </si>
+  <si>
+    <t>احمد عطيه محمد جياد</t>
+  </si>
+  <si>
+    <t>احمدي جعفر صادق حسين</t>
+  </si>
+  <si>
+    <t>اسامه خالد قدوري سلمان</t>
+  </si>
+  <si>
+    <t>اسراء سعد نعمة كاظم</t>
+  </si>
+  <si>
+    <t>اسراء شعلان احمد حزوم</t>
+  </si>
+  <si>
+    <t>امين عماد عبد الحميد احمد</t>
+  </si>
+  <si>
+    <t>ايه حامد حسين علوان</t>
+  </si>
+  <si>
+    <t>بشار محمد حاتم حسين</t>
+  </si>
+  <si>
+    <t>بهاء الدين احمد عويد كيطان</t>
+  </si>
+  <si>
+    <t>حيدر علي حسين كاظم</t>
+  </si>
+  <si>
+    <t>زمن داود بناي عبد الله</t>
+  </si>
+  <si>
+    <t>835,000</t>
+  </si>
+  <si>
+    <t>58.77%</t>
+  </si>
+  <si>
+    <t>زهراء عبد الكريم رضا جابر</t>
+  </si>
+  <si>
+    <t>سجاد فراس عباس فاضل</t>
+  </si>
+  <si>
+    <t>شهد عبد الكريم كاظم جلوب</t>
+  </si>
+  <si>
+    <t>عبد الرزاق حسين فوزي اسماعيل</t>
+  </si>
+  <si>
+    <t>2,170,000</t>
+  </si>
+  <si>
+    <t>80,000</t>
+  </si>
+  <si>
+    <t>96.44%</t>
+  </si>
+  <si>
+    <t>عزالدين عبدالكريم عفتان ثامر</t>
+  </si>
+  <si>
+    <t>علي رزاق عباس يوسف</t>
+  </si>
+  <si>
+    <t>عواد قدوري عواد داود</t>
+  </si>
+  <si>
+    <t>مائده عبد محسن فرحان</t>
+  </si>
+  <si>
+    <t>24.44%</t>
+  </si>
+  <si>
+    <t>مجتبى علي فيصل علوان</t>
+  </si>
+  <si>
+    <t>مجيد محمود مجيد حميد</t>
+  </si>
+  <si>
+    <t>محب جاسم محمد صالح</t>
+  </si>
+  <si>
+    <t>محمد محمود صابر صادق</t>
+  </si>
+  <si>
+    <t>مصطفى خلف عبد الله وهيب</t>
+  </si>
+  <si>
+    <t>مصطفى محمود صالح</t>
+  </si>
+  <si>
+    <t>منتظر معتز مهدي عبدالسادة</t>
+  </si>
+  <si>
+    <t>مؤيد وليد مؤيد احمد</t>
+  </si>
+  <si>
+    <t>ميلاد عبد الزهرة عبيد حسين</t>
+  </si>
+  <si>
+    <t>ندى علي عبد الحسين ابراهيم</t>
+  </si>
+  <si>
+    <t>نور صباح صالح نصرالله</t>
+  </si>
+  <si>
+    <t>هبه عبد الكريم جبار نفل</t>
+  </si>
+  <si>
+    <t>ياسر بشير صبر شراد</t>
+  </si>
+  <si>
+    <t>1,640,000</t>
+  </si>
+  <si>
+    <t>610,000</t>
+  </si>
+  <si>
+    <t>72.89%</t>
+  </si>
+  <si>
+    <t>ياسمين ابراهيم كاظم جلوب</t>
+  </si>
+  <si>
+    <t>ياسر محمد حسن حسين</t>
+  </si>
+  <si>
+    <t>حوراء عبد الكريم عاشور عودة</t>
+  </si>
+  <si>
+    <t>1,912,500</t>
+  </si>
+  <si>
+    <t>رقية خليل حمد رجيو</t>
+  </si>
+  <si>
+    <t>50,000</t>
+  </si>
+  <si>
+    <t>97.22%</t>
+  </si>
+  <si>
+    <t>سجى عبد اليمه حبيب</t>
+  </si>
+  <si>
+    <t>طيبة اثير عبد المنعم</t>
+  </si>
+  <si>
     <t>1,875,000</t>
-  </si>
-  <si>
-    <t>16.67%</t>
-  </si>
-  <si>
-    <t>محمد صلاح خالد جلاب</t>
-  </si>
-  <si>
-    <t>محمد فراس جبير ابراهيم</t>
-  </si>
-  <si>
-    <t>محمد وليد خالد رشيد</t>
-  </si>
-  <si>
-    <t>مصطفى اياد محمد جاسم</t>
-  </si>
-  <si>
-    <t>مصطفى شاكر محمود محمد</t>
-  </si>
-  <si>
-    <t>487,500</t>
-  </si>
-  <si>
-    <t>71.11%</t>
-  </si>
-  <si>
-    <t>مصطفى علاء داود موسى</t>
-  </si>
-  <si>
-    <t>مصطفى علي ناصر حسين</t>
-  </si>
-  <si>
-    <t>مصطفى محمد علي طه</t>
-  </si>
-  <si>
-    <t>675,000</t>
-  </si>
-  <si>
-    <t>30%</t>
-  </si>
-  <si>
-    <t>معتز محمود مطر حسين</t>
-  </si>
-  <si>
-    <t>ملاك عباس عبد علي</t>
-  </si>
-  <si>
-    <t>منقذ عبد الكريم حسين كاظم</t>
-  </si>
-  <si>
-    <t>موده شهاب احمد راكع</t>
-  </si>
-  <si>
-    <t>مؤمن محمد قادر شاواز</t>
-  </si>
-  <si>
-    <t>ميس محمد عصام عبد الوهاب</t>
-  </si>
-  <si>
-    <t>نور ابراهيم خالد محمد</t>
-  </si>
-  <si>
-    <t>يوسف سيف محي جواد</t>
-  </si>
-  <si>
-    <t>يوسف شاكر سالم خلف</t>
-  </si>
-  <si>
-    <t>يوسف نزار هادي ثجيل</t>
-  </si>
-  <si>
-    <t>60%</t>
-  </si>
-  <si>
-    <t>محمد حذيفة فليح حسن</t>
-  </si>
-  <si>
-    <t>حوراء محمد حسان ناجي</t>
-  </si>
-  <si>
-    <t>رقيه علاء صادق</t>
-  </si>
-  <si>
-    <t>مريم احمد محمود عبيد</t>
-  </si>
-  <si>
-    <t>1,375,000</t>
-  </si>
-  <si>
-    <t>67.9%</t>
-  </si>
-  <si>
-    <t>دينا اسعد حسين محمد</t>
-  </si>
-  <si>
-    <t>587,500</t>
-  </si>
-  <si>
-    <t>65.19%</t>
-  </si>
-  <si>
-    <t>تقى جعفر لعيبي جبار</t>
-  </si>
-  <si>
-    <t>600,000</t>
-  </si>
-  <si>
-    <t>اسياد اياد نايف عبد الحسين</t>
-  </si>
-  <si>
-    <t>80.25%</t>
-  </si>
-  <si>
-    <t>شمس مشتاق طالب علي</t>
-  </si>
-  <si>
-    <t>ترتيل عباس شهاب عبود</t>
-  </si>
-  <si>
-    <t>منتهى وسام عبد حسن حواس</t>
-  </si>
-  <si>
-    <t>975,000</t>
-  </si>
-  <si>
-    <t>51.85%</t>
-  </si>
-  <si>
-    <t>شايان مهدي داود عوده</t>
-  </si>
-  <si>
-    <t>احمد داود سلمان محمد</t>
-  </si>
-  <si>
-    <t>565,000</t>
-  </si>
-  <si>
-    <t>49.78%</t>
-  </si>
-  <si>
-    <t>احمد عبد الرحيم ابراهيم العسكري</t>
-  </si>
-  <si>
-    <t>860,000</t>
-  </si>
-  <si>
-    <t>1,390,000</t>
-  </si>
-  <si>
-    <t>38.22%</t>
-  </si>
-  <si>
-    <t>احمد عطيه محمد جياد</t>
-  </si>
-  <si>
-    <t>احمدي جعفر صادق حسين</t>
-  </si>
-  <si>
-    <t>اسامه خالد قدوري سلمان</t>
-  </si>
-  <si>
-    <t>اسراء سعد نعمة كاظم</t>
-  </si>
-  <si>
-    <t>اسراء شعلان احمد حزوم</t>
-  </si>
-  <si>
-    <t>امين عماد عبد الحميد احمد</t>
-  </si>
-  <si>
-    <t>ايه حامد حسين علوان</t>
-  </si>
-  <si>
-    <t>بشار محمد حاتم حسين</t>
-  </si>
-  <si>
-    <t>بهاء الدين احمد عويد كيطان</t>
-  </si>
-  <si>
-    <t>حيدر علي حسين كاظم</t>
-  </si>
-  <si>
-    <t>زمن داود بناي عبد الله</t>
-  </si>
-  <si>
-    <t>835,000</t>
-  </si>
-  <si>
-    <t>58.77%</t>
-  </si>
-  <si>
-    <t>زهراء عبد الكريم رضا جابر</t>
-  </si>
-  <si>
-    <t>سجاد فراس عباس فاضل</t>
-  </si>
-  <si>
-    <t>شهد عبد الكريم كاظم جلوب</t>
-  </si>
-  <si>
-    <t>عبد الرزاق حسين فوزي اسماعيل</t>
-  </si>
-  <si>
-    <t>2,170,000</t>
-  </si>
-  <si>
-    <t>80,000</t>
-  </si>
-  <si>
-    <t>96.44%</t>
-  </si>
-  <si>
-    <t>عزالدين عبدالكريم عفتان ثامر</t>
-  </si>
-  <si>
-    <t>علي رزاق عباس يوسف</t>
-  </si>
-  <si>
-    <t>عواد قدوري عواد داود</t>
-  </si>
-  <si>
-    <t>مائده عبد محسن فرحان</t>
-  </si>
-  <si>
-    <t>24.44%</t>
-  </si>
-  <si>
-    <t>مجتبى علي فيصل علوان</t>
-  </si>
-  <si>
-    <t>مجيد محمود مجيد حميد</t>
-  </si>
-  <si>
-    <t>محب جاسم محمد صالح</t>
-  </si>
-  <si>
-    <t>محمد محمود صابر صادق</t>
-  </si>
-  <si>
-    <t>مصطفى خلف عبد الله وهيب</t>
-  </si>
-  <si>
-    <t>مصطفى محمود صالح</t>
-  </si>
-  <si>
-    <t>منتظر معتز مهدي عبدالسادة</t>
-  </si>
-  <si>
-    <t>مؤيد وليد مؤيد احمد</t>
-  </si>
-  <si>
-    <t>ميلاد عبد الزهرة عبيد حسين</t>
-  </si>
-  <si>
-    <t>ندى علي عبد الحسين ابراهيم</t>
-  </si>
-  <si>
-    <t>نور صباح صالح نصرالله</t>
-  </si>
-  <si>
-    <t>هبه عبد الكريم جبار نفل</t>
-  </si>
-  <si>
-    <t>ياسر بشير صبر شراد</t>
-  </si>
-  <si>
-    <t>1,640,000</t>
-  </si>
-  <si>
-    <t>610,000</t>
-  </si>
-  <si>
-    <t>72.89%</t>
-  </si>
-  <si>
-    <t>ياسمين ابراهيم كاظم جلوب</t>
-  </si>
-  <si>
-    <t>ياسر محمد حسن حسين</t>
-  </si>
-  <si>
-    <t>687,500</t>
-  </si>
-  <si>
-    <t>حوراء عبد الكريم عاشور عودة</t>
-  </si>
-  <si>
-    <t>1,912,500</t>
-  </si>
-  <si>
-    <t>رقية خليل حمد رجيو</t>
-  </si>
-  <si>
-    <t>50,000</t>
-  </si>
-  <si>
-    <t>97.22%</t>
-  </si>
-  <si>
-    <t>سجى عبد اليمه حبيب</t>
-  </si>
-  <si>
-    <t>طيبة اثير عبد المنعم</t>
   </si>
   <si>
     <t>83.33%</t>
@@ -1269,15 +1238,23 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
@@ -1354,43 +1331,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+  <cellXfs count="7">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="5" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="6" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="7" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -1680,20 +1646,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:I241"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="41.133" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="43.418" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="12.568" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="17.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="21.566" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="21.566" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="19.138" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="19.138" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1722,7 +1693,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1751,7 +1722,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1780,7 +1751,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -1809,7 +1780,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -1838,7 +1809,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -1867,7 +1838,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -1896,7 +1867,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -1925,7 +1896,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -1954,7 +1925,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -1983,7 +1954,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -2012,7 +1983,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -2041,7 +2012,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -2070,7 +2041,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -2099,7 +2070,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -2128,7 +2099,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -2157,7 +2128,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -2186,7 +2157,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -2215,7 +2186,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -2244,7 +2215,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -2273,7 +2244,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -2302,7 +2273,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -2331,7 +2302,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -2360,7 +2331,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -2389,7 +2360,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -2418,7 +2389,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -2447,7 +2418,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -2476,7 +2447,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -2505,7 +2476,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -2534,7 +2505,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -2563,7 +2534,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -2592,7 +2563,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -2621,7 +2592,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -2650,7 +2621,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -2679,7 +2650,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9">
       <c r="A35" s="6">
         <v>34</v>
       </c>
@@ -2708,7 +2679,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9">
       <c r="A36" s="6">
         <v>35</v>
       </c>
@@ -2737,7 +2708,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -2766,7 +2737,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9">
       <c r="A38" s="6">
         <v>37</v>
       </c>
@@ -2795,7 +2766,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -2824,7 +2795,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -2853,7 +2824,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -2882,7 +2853,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -2911,7 +2882,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -2940,7 +2911,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9">
       <c r="A44" s="6">
         <v>43</v>
       </c>
@@ -2969,7 +2940,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -2998,7 +2969,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -3027,7 +2998,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -3056,7 +3027,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -3085,7 +3056,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -3114,7 +3085,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9">
       <c r="A50" s="4">
         <v>49</v>
       </c>
@@ -3143,7 +3114,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -3172,7 +3143,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -3201,7 +3172,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -3230,7 +3201,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9">
       <c r="A54" s="6">
         <v>53</v>
       </c>
@@ -3259,7 +3230,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9">
       <c r="A55" s="5">
         <v>54</v>
       </c>
@@ -3288,7 +3259,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -3317,7 +3288,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -3346,7 +3317,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9">
       <c r="A58" s="6">
         <v>57</v>
       </c>
@@ -3375,7 +3346,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -3404,7 +3375,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9">
       <c r="A60" s="4">
         <v>59</v>
       </c>
@@ -3433,7 +3404,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -3462,7 +3433,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9">
       <c r="A62" s="4">
         <v>61</v>
       </c>
@@ -3491,7 +3462,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -3520,7 +3491,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -3549,7 +3520,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -3578,7 +3549,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -3607,7 +3578,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -3636,7 +3607,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9">
       <c r="A68" s="4">
         <v>67</v>
       </c>
@@ -3665,7 +3636,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -3694,7 +3665,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -3723,7 +3694,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9">
       <c r="A71" s="4">
         <v>70</v>
       </c>
@@ -3752,7 +3723,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9">
       <c r="A72" s="4">
         <v>71</v>
       </c>
@@ -3781,7 +3752,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -3810,7 +3781,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9">
       <c r="A74" s="4">
         <v>73</v>
       </c>
@@ -3839,7 +3810,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -3868,7 +3839,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9">
       <c r="A76" s="4">
         <v>75</v>
       </c>
@@ -3897,7 +3868,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -3926,7 +3897,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9">
       <c r="A78" s="4">
         <v>77</v>
       </c>
@@ -3955,7 +3926,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9">
       <c r="A79" s="6">
         <v>78</v>
       </c>
@@ -3984,7 +3955,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9">
       <c r="A80" s="6">
         <v>79</v>
       </c>
@@ -4013,7 +3984,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9">
       <c r="A81" s="6">
         <v>80</v>
       </c>
@@ -4042,7 +4013,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -4071,7 +4042,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9">
       <c r="A83" s="5">
         <v>82</v>
       </c>
@@ -4100,7 +4071,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9">
       <c r="A84" s="4">
         <v>83</v>
       </c>
@@ -4129,7 +4100,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -4158,7 +4129,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9">
       <c r="A86" s="4">
         <v>85</v>
       </c>
@@ -4187,7 +4158,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -4216,7 +4187,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9">
       <c r="A88" s="6">
         <v>87</v>
       </c>
@@ -4245,7 +4216,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -4274,7 +4245,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9">
       <c r="A90" s="4">
         <v>89</v>
       </c>
@@ -4303,7 +4274,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9">
       <c r="A91" s="4">
         <v>90</v>
       </c>
@@ -4332,7 +4303,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9">
       <c r="A92" s="4">
         <v>91</v>
       </c>
@@ -4361,7 +4332,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9">
       <c r="A93" s="4">
         <v>92</v>
       </c>
@@ -4390,7 +4361,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9">
       <c r="A94" s="4">
         <v>93</v>
       </c>
@@ -4419,7 +4390,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9">
       <c r="A95" s="4">
         <v>94</v>
       </c>
@@ -4448,7 +4419,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9">
       <c r="A96" s="4">
         <v>95</v>
       </c>
@@ -4477,7 +4448,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9">
       <c r="A97" s="4">
         <v>96</v>
       </c>
@@ -4506,7 +4477,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9">
       <c r="A98" s="6">
         <v>97</v>
       </c>
@@ -4535,7 +4506,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9">
       <c r="A99" s="6">
         <v>98</v>
       </c>
@@ -4564,7 +4535,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9">
       <c r="A100" s="2">
         <v>99</v>
       </c>
@@ -4593,7 +4564,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -4622,7 +4593,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9">
       <c r="A102" s="6">
         <v>101</v>
       </c>
@@ -4651,7 +4622,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9">
       <c r="A103" s="4">
         <v>102</v>
       </c>
@@ -4680,7 +4651,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9">
       <c r="A104" s="4">
         <v>103</v>
       </c>
@@ -4709,7 +4680,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9">
       <c r="A105" s="4">
         <v>104</v>
       </c>
@@ -4738,7 +4709,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9">
       <c r="A106" s="4">
         <v>105</v>
       </c>
@@ -4767,7 +4738,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -4796,7 +4767,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9">
       <c r="A108" s="6">
         <v>107</v>
       </c>
@@ -4813,7 +4784,7 @@
         <v>200</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>124</v>
+        <v>64</v>
       </c>
       <c r="G108" s="6" t="s">
         <v>201</v>
@@ -4825,70 +4796,70 @@
         <v>67</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A109" s="6">
+    <row r="109" spans="1:9">
+      <c r="A109" s="4">
         <v>108</v>
       </c>
-      <c r="B109" s="6" t="s">
+      <c r="B109" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C109" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D109" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="E109" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F109" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="G109" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="H109" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="I109" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A110" s="6">
+      <c r="C109" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G109" s="4">
+        <v>0</v>
+      </c>
+      <c r="H109" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I109" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="A110" s="4">
         <v>109</v>
       </c>
-      <c r="B110" s="6" t="s">
+      <c r="B110" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="C110" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D110" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="E110" s="6" t="s">
+      <c r="C110" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E110" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F110" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G110" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="I110" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F110" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G110" s="4">
+        <v>0</v>
+      </c>
+      <c r="H110" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I110" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
       <c r="A111" s="6">
         <v>110</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>10</v>
@@ -4912,12 +4883,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9">
       <c r="A112" s="4">
         <v>111</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>10</v>
@@ -4941,12 +4912,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9">
       <c r="A113" s="5">
         <v>112</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>10</v>
@@ -4960,8 +4931,8 @@
       <c r="F113" s="5">
         <v>0</v>
       </c>
-      <c r="G113" s="5">
-        <v>0</v>
+      <c r="G113" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="H113" s="5" t="s">
         <v>60</v>
@@ -4970,12 +4941,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9">
       <c r="A114" s="4">
         <v>113</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>10</v>
@@ -4999,12 +4970,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9">
       <c r="A115" s="4">
         <v>114</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>10</v>
@@ -5028,12 +4999,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9">
       <c r="A116" s="4">
         <v>115</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>10</v>
@@ -5057,24 +5028,24 @@
         <v>24</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9">
       <c r="A117" s="3">
         <v>116</v>
       </c>
       <c r="B117" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F117" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F117" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="G117" s="3" t="s">
         <v>213</v>
@@ -5086,7 +5057,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9">
       <c r="A118" s="4">
         <v>117</v>
       </c>
@@ -5115,7 +5086,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9">
       <c r="A119" s="2">
         <v>118</v>
       </c>
@@ -5144,7 +5115,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9">
       <c r="A120" s="5">
         <v>119</v>
       </c>
@@ -5173,7 +5144,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9">
       <c r="A121" s="6">
         <v>120</v>
       </c>
@@ -5202,7 +5173,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9">
       <c r="A122" s="6">
         <v>121</v>
       </c>
@@ -5231,7 +5202,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9">
       <c r="A123" s="6">
         <v>122</v>
       </c>
@@ -5260,7 +5231,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9">
       <c r="A124" s="3">
         <v>123</v>
       </c>
@@ -5277,7 +5248,7 @@
         <v>12</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>213</v>
@@ -5289,7 +5260,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9">
       <c r="A125" s="2">
         <v>124</v>
       </c>
@@ -5318,41 +5289,41 @@
         <v>16</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A126" s="3">
+    <row r="126" spans="1:9">
+      <c r="A126" s="4">
         <v>125</v>
       </c>
-      <c r="B126" s="3" t="s">
+      <c r="B126" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="C126" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D126" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E126" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F126" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="G126" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="H126" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="I126" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C126" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G126" s="4">
+        <v>0</v>
+      </c>
+      <c r="H126" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I126" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
       <c r="A127" s="5">
         <v>126</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>10</v>
@@ -5376,12 +5347,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9">
       <c r="A128" s="4">
         <v>127</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>10</v>
@@ -5405,12 +5376,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9">
       <c r="A129" s="4">
         <v>128</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>10</v>
@@ -5434,12 +5405,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9">
       <c r="A130" s="4">
         <v>129</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>10</v>
@@ -5463,12 +5434,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9">
       <c r="A131" s="4">
         <v>130</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>10</v>
@@ -5492,12 +5463,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9">
       <c r="A132" s="5">
         <v>131</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C132" s="5" t="s">
         <v>10</v>
@@ -5521,24 +5492,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9">
       <c r="A133" s="4">
         <v>132</v>
       </c>
       <c r="B133" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E133" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="C133" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D133" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="E133" s="4" t="s">
-        <v>240</v>
-      </c>
       <c r="F133" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G133" s="4">
         <v>0</v>
@@ -5550,36 +5521,36 @@
         <v>24</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9">
       <c r="A134" s="2">
         <v>133</v>
       </c>
       <c r="B134" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H134" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F134" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G134" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="H134" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="I134" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -5608,7 +5579,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9">
       <c r="A136" s="5">
         <v>135</v>
       </c>
@@ -5637,7 +5608,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9">
       <c r="A137" s="2">
         <v>136</v>
       </c>
@@ -5666,7 +5637,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9">
       <c r="A138" s="2">
         <v>137</v>
       </c>
@@ -5695,7 +5666,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9">
       <c r="A139" s="4">
         <v>138</v>
       </c>
@@ -5724,7 +5695,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9">
       <c r="A140" s="4">
         <v>139</v>
       </c>
@@ -5753,7 +5724,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -5782,7 +5753,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9">
       <c r="A142" s="4">
         <v>141</v>
       </c>
@@ -5811,7 +5782,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9">
       <c r="A143" s="4">
         <v>142</v>
       </c>
@@ -5840,7 +5811,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9">
       <c r="A144" s="4">
         <v>143</v>
       </c>
@@ -5869,7 +5840,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -5898,7 +5869,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9">
       <c r="A146" s="6">
         <v>145</v>
       </c>
@@ -5927,7 +5898,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9">
       <c r="A147" s="6">
         <v>146</v>
       </c>
@@ -5946,51 +5917,51 @@
       <c r="F147" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="G147" s="6">
-        <v>0</v>
+      <c r="G147" s="6" t="s">
+        <v>261</v>
       </c>
       <c r="H147" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I147" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A148" s="6">
+    <row r="148" spans="1:9">
+      <c r="A148" s="4">
         <v>147</v>
       </c>
-      <c r="B148" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="C148" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D148" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="E148" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F148" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="G148" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="I148" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B148" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E148" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G148" s="4">
+        <v>0</v>
+      </c>
+      <c r="H148" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I148" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
       <c r="A149" s="6">
         <v>148</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>10</v>
@@ -6014,99 +5985,99 @@
         <v>67</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A150" s="6">
+    <row r="150" spans="1:9">
+      <c r="A150" s="4">
         <v>149</v>
       </c>
-      <c r="B150" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="C150" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D150" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="E150" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F150" s="6" t="s">
+      <c r="B150" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="G150" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="H150" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="I150" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C150" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E150" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G150" s="4">
+        <v>0</v>
+      </c>
+      <c r="H150" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I150" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
       <c r="A151" s="2">
         <v>150</v>
       </c>
       <c r="B151" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="G151" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C151" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D151" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E151" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F151" s="2" t="s">
+      <c r="H151" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="G151" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="H151" s="2" t="s">
-        <v>271</v>
       </c>
       <c r="I151" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9">
       <c r="A152" s="2">
         <v>151</v>
       </c>
       <c r="B152" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="G152" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C152" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F152" s="2" t="s">
+      <c r="H152" s="2" t="s">
         <v>273</v>
-      </c>
-      <c r="G152" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="H152" s="2" t="s">
-        <v>275</v>
       </c>
       <c r="I152" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9">
       <c r="A153" s="4">
         <v>152</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>10</v>
@@ -6130,12 +6101,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9">
       <c r="A154" s="5">
         <v>153</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C154" s="5" t="s">
         <v>10</v>
@@ -6153,18 +6124,18 @@
         <v>167</v>
       </c>
       <c r="H154" s="5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="I154" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9">
       <c r="A155" s="6">
         <v>154</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>10</v>
@@ -6179,21 +6150,21 @@
         <v>124</v>
       </c>
       <c r="G155" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H155" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I155" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9">
       <c r="A156" s="4">
         <v>155</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>10</v>
@@ -6217,12 +6188,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9">
       <c r="A157" s="6">
         <v>156</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>10</v>
@@ -6246,12 +6217,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9">
       <c r="A158" s="4">
         <v>157</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>10</v>
@@ -6275,12 +6246,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9">
       <c r="A159" s="2">
         <v>158</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>10</v>
@@ -6292,24 +6263,24 @@
         <v>45</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I159" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9">
       <c r="A160" s="6">
         <v>159</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>10</v>
@@ -6333,12 +6304,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9">
       <c r="A161" s="4">
         <v>160</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>10</v>
@@ -6362,12 +6333,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9">
       <c r="A162" s="4">
         <v>161</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>10</v>
@@ -6391,12 +6362,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9">
       <c r="A163" s="6">
         <v>162</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>10</v>
@@ -6420,12 +6391,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9">
       <c r="A164" s="2">
         <v>163</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>10</v>
@@ -6449,41 +6420,41 @@
         <v>16</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A165" s="5">
+    <row r="165" spans="1:9">
+      <c r="A165" s="3">
         <v>164</v>
       </c>
-      <c r="B165" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="C165" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D165" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="E165" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F165" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="G165" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="H165" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="I165" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B165" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H165" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I165" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9">
       <c r="A166" s="4">
         <v>165</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>10</v>
@@ -6507,12 +6478,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9">
       <c r="A167" s="4">
         <v>166</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>10</v>
@@ -6536,12 +6507,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9">
       <c r="A168" s="5">
         <v>167</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C168" s="5" t="s">
         <v>10</v>
@@ -6565,12 +6536,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9">
       <c r="A169" s="4">
         <v>168</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>10</v>
@@ -6594,12 +6565,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9">
       <c r="A170" s="6">
         <v>169</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>10</v>
@@ -6614,21 +6585,21 @@
         <v>152</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="H170" s="6" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="I170" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9">
       <c r="A171" s="4">
         <v>170</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>10</v>
@@ -6652,12 +6623,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9">
       <c r="A172" s="2">
         <v>171</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>10</v>
@@ -6681,41 +6652,41 @@
         <v>16</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A173" s="3">
+    <row r="173" spans="1:9">
+      <c r="A173" s="6">
         <v>172</v>
       </c>
-      <c r="B173" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="C173" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D173" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E173" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F173" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="G173" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H173" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="I173" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B173" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D173" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E173" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F173" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="G173" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H173" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="I173" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9">
       <c r="A174" s="4">
         <v>173</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>10</v>
@@ -6739,12 +6710,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9">
       <c r="A175" s="4">
         <v>174</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>10</v>
@@ -6768,12 +6739,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9">
       <c r="A176" s="4">
         <v>175</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>10</v>
@@ -6797,12 +6768,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9">
       <c r="A177" s="2">
         <v>176</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>10</v>
@@ -6826,12 +6797,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9">
       <c r="A178" s="4">
         <v>177</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>10</v>
@@ -6855,12 +6826,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9">
       <c r="A179" s="2">
         <v>178</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>10</v>
@@ -6874,8 +6845,8 @@
       <c r="F179" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="G179" s="7">
-        <v>0</v>
+      <c r="G179" s="2" t="s">
+        <v>168</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>169</v>
@@ -6884,12 +6855,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9">
       <c r="A180" s="4">
         <v>179</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>10</v>
@@ -6913,12 +6884,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9">
       <c r="A181" s="6">
         <v>180</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>10</v>
@@ -6942,41 +6913,41 @@
         <v>67</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A182" s="5">
+    <row r="182" spans="1:9">
+      <c r="A182" s="3">
         <v>181</v>
       </c>
-      <c r="B182" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="C182" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D182" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="E182" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F182" s="5" t="s">
+      <c r="B182" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E182" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F182" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G182" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H182" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="I182" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G182" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H182" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I182" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9">
       <c r="A183" s="6">
         <v>182</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>10</v>
@@ -6991,21 +6962,21 @@
         <v>213</v>
       </c>
       <c r="G183" s="6" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="H183" s="6" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="I183" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9">
       <c r="A184" s="4">
         <v>183</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>10</v>
@@ -7029,41 +7000,41 @@
         <v>24</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A185" s="3">
+    <row r="185" spans="1:9">
+      <c r="A185" s="6">
         <v>184</v>
       </c>
-      <c r="B185" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="C185" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D185" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E185" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F185" s="3" t="s">
+      <c r="B185" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="C185" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D185" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E185" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F185" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G185" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="G185" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="H185" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="I185" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H185" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I185" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9">
       <c r="A186" s="2">
         <v>185</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>10</v>
@@ -7077,8 +7048,8 @@
       <c r="F186" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G186" s="2">
-        <v>0</v>
+      <c r="G186" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
@@ -7087,12 +7058,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9">
       <c r="A187" s="6">
         <v>186</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C187" s="6" t="s">
         <v>10</v>
@@ -7104,24 +7075,24 @@
         <v>46</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="G187" s="6" t="s">
         <v>226</v>
       </c>
       <c r="H187" s="6" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="I187" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9">
       <c r="A188" s="6">
         <v>187</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>10</v>
@@ -7136,21 +7107,21 @@
         <v>124</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="I188" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9">
       <c r="A189" s="6">
         <v>188</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>10</v>
@@ -7165,7 +7136,7 @@
         <v>152</v>
       </c>
       <c r="G189" s="6" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="H189" s="6" t="s">
         <v>66</v>
@@ -7174,12 +7145,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9">
       <c r="A190" s="2">
         <v>189</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>10</v>
@@ -7197,18 +7168,18 @@
         <v>168</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="I190" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9">
       <c r="A191" s="2">
         <v>190</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>10</v>
@@ -7232,12 +7203,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9">
       <c r="A192" s="2">
         <v>191</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>10</v>
@@ -7261,12 +7232,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9">
       <c r="A193" s="6">
         <v>192</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>10</v>
@@ -7281,21 +7252,21 @@
         <v>191</v>
       </c>
       <c r="G193" s="6" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="H193" s="6" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="I193" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9">
       <c r="A194" s="5">
         <v>193</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C194" s="5" t="s">
         <v>10</v>
@@ -7313,18 +7284,18 @@
         <v>167</v>
       </c>
       <c r="H194" s="5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="I194" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9">
       <c r="A195" s="3">
         <v>194</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="C195" s="3" t="s">
         <v>10</v>
@@ -7339,21 +7310,21 @@
         <v>221</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="H195" s="3" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="I195" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9">
       <c r="A196" s="3">
         <v>195</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C196" s="3" t="s">
         <v>10</v>
@@ -7365,24 +7336,24 @@
         <v>12</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="H196" s="3" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="I196" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9">
       <c r="A197" s="4">
         <v>196</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="C197" s="4" t="s">
         <v>10</v>
@@ -7406,12 +7377,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9">
       <c r="A198" s="5">
         <v>197</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C198" s="5" t="s">
         <v>10</v>
@@ -7435,12 +7406,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9">
       <c r="A199" s="5">
         <v>198</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="C199" s="5" t="s">
         <v>10</v>
@@ -7464,41 +7435,41 @@
         <v>61</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A200" s="2">
+    <row r="200" spans="1:9">
+      <c r="A200" s="4">
         <v>199</v>
       </c>
-      <c r="B200" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D200" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E200" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F200" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="G200" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="H200" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="I200" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B200" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D200" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E200" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F200" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G200" s="4">
+        <v>0</v>
+      </c>
+      <c r="H200" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I200" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9">
       <c r="A201" s="4">
         <v>200</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C201" s="4" t="s">
         <v>10</v>
@@ -7522,12 +7493,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9">
       <c r="A202" s="5">
         <v>201</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C202" s="5" t="s">
         <v>10</v>
@@ -7551,12 +7522,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9">
       <c r="A203" s="4">
         <v>202</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="C203" s="4" t="s">
         <v>10</v>
@@ -7580,12 +7551,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9">
       <c r="A204" s="4">
         <v>203</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C204" s="4" t="s">
         <v>10</v>
@@ -7609,12 +7580,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9">
       <c r="A205" s="4">
         <v>204</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C205" s="4" t="s">
         <v>10</v>
@@ -7638,12 +7609,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9">
       <c r="A206" s="4">
         <v>205</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C206" s="4" t="s">
         <v>10</v>
@@ -7667,12 +7638,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9">
       <c r="A207" s="6">
         <v>206</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C207" s="6" t="s">
         <v>10</v>
@@ -7687,21 +7658,21 @@
         <v>163</v>
       </c>
       <c r="G207" s="6" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="H207" s="6" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="I207" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9">
       <c r="A208" s="3">
         <v>207</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C208" s="3" t="s">
         <v>10</v>
@@ -7725,12 +7696,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9">
       <c r="A209" s="4">
         <v>208</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C209" s="4" t="s">
         <v>10</v>
@@ -7754,12 +7725,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9">
       <c r="A210" s="4">
         <v>209</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C210" s="4" t="s">
         <v>10</v>
@@ -7783,12 +7754,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9">
       <c r="A211" s="2">
         <v>210</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>10</v>
@@ -7800,24 +7771,24 @@
         <v>12</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="I211" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9">
       <c r="A212" s="4">
         <v>211</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="C212" s="4" t="s">
         <v>10</v>
@@ -7841,12 +7812,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9">
       <c r="A213" s="4">
         <v>212</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C213" s="4" t="s">
         <v>10</v>
@@ -7870,12 +7841,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9">
       <c r="A214" s="5">
         <v>213</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C214" s="5" t="s">
         <v>10</v>
@@ -7899,12 +7870,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9">
       <c r="A215" s="5">
         <v>214</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C215" s="5" t="s">
         <v>10</v>
@@ -7922,18 +7893,18 @@
         <v>129</v>
       </c>
       <c r="H215" s="5" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I215" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9">
       <c r="A216" s="4">
         <v>215</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C216" s="4" t="s">
         <v>10</v>
@@ -7957,12 +7928,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9">
       <c r="A217" s="4">
         <v>216</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C217" s="4" t="s">
         <v>10</v>
@@ -7986,12 +7957,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9">
       <c r="A218" s="5">
         <v>217</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C218" s="5" t="s">
         <v>10</v>
@@ -8000,13 +7971,13 @@
         <v>190</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F218" s="5">
         <v>0</v>
       </c>
       <c r="G218" s="5" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H218" s="5" t="s">
         <v>60</v>
@@ -8015,12 +7986,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9">
       <c r="A219" s="6">
         <v>218</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>10</v>
@@ -8044,12 +8015,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9">
       <c r="A220" s="4">
         <v>219</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C220" s="4" t="s">
         <v>10</v>
@@ -8073,12 +8044,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9">
       <c r="A221" s="5">
         <v>220</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C221" s="5" t="s">
         <v>10</v>
@@ -8102,12 +8073,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9">
       <c r="A222" s="4">
         <v>221</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C222" s="4" t="s">
         <v>10</v>
@@ -8131,12 +8102,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9">
       <c r="A223" s="4">
         <v>222</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C223" s="4" t="s">
         <v>10</v>
@@ -8160,12 +8131,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9">
       <c r="A224" s="5">
         <v>223</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C224" s="5" t="s">
         <v>10</v>
@@ -8189,12 +8160,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9">
       <c r="A225" s="2">
         <v>224</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>10</v>
@@ -8218,12 +8189,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9">
       <c r="A226" s="2">
         <v>225</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>10</v>
@@ -8235,24 +8206,24 @@
         <v>18</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>41</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I226" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9">
       <c r="A227" s="4">
         <v>226</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C227" s="4" t="s">
         <v>10</v>
@@ -8276,12 +8247,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9">
       <c r="A228" s="6">
         <v>227</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C228" s="6" t="s">
         <v>10</v>
@@ -8293,24 +8264,24 @@
         <v>12</v>
       </c>
       <c r="F228" s="6" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="G228" s="6" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="H228" s="6" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="I228" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9">
       <c r="A229" s="4">
         <v>228</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C229" s="4" t="s">
         <v>10</v>
@@ -8334,41 +8305,41 @@
         <v>24</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A230" s="6">
+    <row r="230" spans="1:9">
+      <c r="A230" s="4">
         <v>229</v>
       </c>
-      <c r="B230" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="C230" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D230" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="E230" s="6" t="s">
+      <c r="B230" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="C230" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D230" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E230" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F230" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="G230" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="H230" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="I230" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F230" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G230" s="4">
+        <v>0</v>
+      </c>
+      <c r="H230" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I230" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9">
       <c r="A231" s="4">
         <v>230</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C231" s="4" t="s">
         <v>10</v>
@@ -8377,10 +8348,10 @@
         <v>174</v>
       </c>
       <c r="E231" s="4" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="G231" s="4">
         <v>0</v>
@@ -8392,12 +8363,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9">
       <c r="A232" s="2">
         <v>231</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>10</v>
@@ -8412,21 +8383,21 @@
         <v>13</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="I232" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9">
       <c r="A233" s="4">
         <v>232</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C233" s="4" t="s">
         <v>10</v>
@@ -8450,12 +8421,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9">
       <c r="A234" s="2">
         <v>233</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>10</v>
@@ -8467,24 +8438,24 @@
         <v>12</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>295</v>
+        <v>391</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="I234" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9">
       <c r="A235" s="5">
         <v>234</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C235" s="5" t="s">
         <v>10</v>
@@ -8496,24 +8467,24 @@
         <v>12</v>
       </c>
       <c r="F235" s="5" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="G235" s="5" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H235" s="5" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="I235" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9">
       <c r="A236" s="6">
         <v>235</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C236" s="6" t="s">
         <v>10</v>
@@ -8522,27 +8493,27 @@
         <v>174</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="F236" s="6" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="G236" s="6" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="H236" s="6" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="I236" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9">
       <c r="A237" s="4">
         <v>236</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C237" s="4" t="s">
         <v>10</v>
@@ -8566,12 +8537,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9">
       <c r="A238" s="4">
         <v>237</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C238" s="4" t="s">
         <v>10</v>
@@ -8595,12 +8566,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9">
       <c r="A239" s="4">
         <v>238</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C239" s="4" t="s">
         <v>10</v>
@@ -8624,12 +8595,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:9">
       <c r="A240" s="6">
         <v>239</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="C240" s="6" t="s">
         <v>10</v>
@@ -8647,18 +8618,18 @@
         <v>18</v>
       </c>
       <c r="H240" s="6" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="I240" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9">
       <c r="A241" s="6">
         <v>240</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C241" s="6" t="s">
         <v>10</v>
@@ -8673,16 +8644,27 @@
         <v>124</v>
       </c>
       <c r="G241" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H241" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I241" s="6" t="s">
         <v>67</v>
       </c>
     </row>
   </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>
--- a/pay.xlsx
+++ b/pay.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="400">
   <si>
     <t>#</t>
   </si>
@@ -137,1015 +137,997 @@
     <t>حسين عباس محمود عبد</t>
   </si>
   <si>
-    <t>2,100,000</t>
+    <t>حسين عبد الكريم جواد صفر</t>
+  </si>
+  <si>
+    <t>2,025,000</t>
+  </si>
+  <si>
+    <t>حسين علي كمال مرهون</t>
+  </si>
+  <si>
+    <t>1,800,000</t>
+  </si>
+  <si>
+    <t>حسين محمد فالح حسن</t>
+  </si>
+  <si>
+    <t>حوراء حيدر عبد الرزاق ناجي</t>
+  </si>
+  <si>
+    <t>خالد محمد حسين عباس</t>
+  </si>
+  <si>
+    <t>رقيه محسن جبير ناصر</t>
+  </si>
+  <si>
+    <t>رؤى ثامر عاشور خدي</t>
+  </si>
+  <si>
+    <t>رؤى جعفر كامل عباس</t>
+  </si>
+  <si>
+    <t>زهراء حسام ناصر محمد</t>
+  </si>
+  <si>
+    <t>زهراء محمد حسين علوان</t>
+  </si>
+  <si>
+    <t>زينب معد فالح حسن</t>
+  </si>
+  <si>
+    <t>سجاد ماجد حسين علوان</t>
+  </si>
+  <si>
+    <t>شهد نوري سعدون شمران</t>
+  </si>
+  <si>
+    <t>شيفان خليل محمد ملك</t>
+  </si>
+  <si>
+    <t>طه رعد جبير جميس</t>
+  </si>
+  <si>
+    <t>0%</t>
+  </si>
+  <si>
+    <t>أقل من 25%</t>
+  </si>
+  <si>
+    <t>طيبه عدنان عبد الجبار عبد الكريم</t>
+  </si>
+  <si>
+    <t>عباس خليل حيدر ادهم</t>
+  </si>
+  <si>
+    <t>1,500,000</t>
+  </si>
+  <si>
+    <t>750,000</t>
+  </si>
+  <si>
+    <t>66.67%</t>
+  </si>
+  <si>
+    <t>مسدد 50%+</t>
+  </si>
+  <si>
+    <t>عباس علي حسين داخل</t>
+  </si>
+  <si>
+    <t>1,250,000</t>
+  </si>
+  <si>
+    <t>1,000,000</t>
+  </si>
+  <si>
+    <t>55.56%</t>
+  </si>
+  <si>
+    <t>عبد الرحمن رائد عبد الحميد محمود</t>
+  </si>
+  <si>
+    <t>عبد السلام نوري سعدون حمادي</t>
+  </si>
+  <si>
+    <t>1,300,000</t>
+  </si>
+  <si>
+    <t>950,000</t>
+  </si>
+  <si>
+    <t>57.78%</t>
+  </si>
+  <si>
+    <t>عبد الله عوده مكي جواد</t>
+  </si>
+  <si>
+    <t>علي الرضا سعد عبد محمد</t>
+  </si>
+  <si>
+    <t>2,000,000</t>
+  </si>
+  <si>
+    <t>250,000</t>
+  </si>
+  <si>
+    <t>88.89%</t>
+  </si>
+  <si>
+    <t>علي جمال فتحي لطيف</t>
+  </si>
+  <si>
+    <t>علي حازم جبار جبر</t>
+  </si>
+  <si>
+    <t>علي خالد محمود سلطان</t>
+  </si>
+  <si>
+    <t>علي زاهد جاسم كاظم</t>
+  </si>
+  <si>
+    <t>1,675,000</t>
+  </si>
+  <si>
+    <t>575,000</t>
+  </si>
+  <si>
+    <t>74.44%</t>
+  </si>
+  <si>
+    <t>علي فراس كريم سلمان</t>
+  </si>
+  <si>
+    <t>علي لؤي صادق جعفر</t>
+  </si>
+  <si>
+    <t>علي مؤيد احمد صالح</t>
+  </si>
+  <si>
+    <t>عمر يحيى مراد صالح</t>
+  </si>
+  <si>
+    <t>غسق مهدي جابر حمودي</t>
+  </si>
+  <si>
+    <t>فاطمه حيدر مهدي خضير</t>
+  </si>
+  <si>
+    <t>قاسم كريم محمود عنبر</t>
+  </si>
+  <si>
+    <t>225,000</t>
+  </si>
+  <si>
+    <t>كرار حيدر عبود هادي</t>
+  </si>
+  <si>
+    <t>11.11%</t>
+  </si>
+  <si>
+    <t>كوثر حسن نعمه عيسى</t>
+  </si>
+  <si>
+    <t>562,500</t>
+  </si>
+  <si>
+    <t>محمد المهدي عيسى لطيف يونس</t>
+  </si>
+  <si>
+    <t>محمد صادق جعفر مجيد</t>
+  </si>
+  <si>
+    <t>450,000</t>
+  </si>
+  <si>
+    <t>22.22%</t>
+  </si>
+  <si>
+    <t>محمد علي عوج عجه</t>
+  </si>
+  <si>
+    <t>محمد كريم عمران موسى</t>
+  </si>
+  <si>
+    <t>محمد محمود ابراهيم محمود</t>
+  </si>
+  <si>
+    <t>1,550,000</t>
+  </si>
+  <si>
+    <t>700,000</t>
+  </si>
+  <si>
+    <t>68.89%</t>
+  </si>
+  <si>
+    <t>محمد منصور عبد الله مضهضب</t>
+  </si>
+  <si>
+    <t>مرتضى محمد عبد الخالق علوان</t>
+  </si>
+  <si>
+    <t>مصطفى حيدر محمود علي</t>
+  </si>
+  <si>
+    <t>مصطفى عبد الكاظم جليل عبد الرضا</t>
+  </si>
+  <si>
+    <t>مصطفى نبيل جاسم خضير</t>
+  </si>
+  <si>
+    <t>80%</t>
+  </si>
+  <si>
+    <t>مقتدى علي ابراهيم حسين</t>
+  </si>
+  <si>
+    <t>800,000</t>
+  </si>
+  <si>
+    <t>ملاك ثامر تركي خضير</t>
+  </si>
+  <si>
+    <t>منتظر حيدر خليل ابراهيم</t>
+  </si>
+  <si>
+    <t>منتظر يوسف حميد كاظم</t>
+  </si>
+  <si>
+    <t>1,100,000</t>
+  </si>
+  <si>
+    <t>1,150,000</t>
+  </si>
+  <si>
+    <t>48.89%</t>
+  </si>
+  <si>
+    <t>مهدي احمد عبد الأمير عبد الحسين</t>
+  </si>
+  <si>
+    <t>مهدي علي نبيل صالح</t>
+  </si>
+  <si>
+    <t>1,700,000</t>
+  </si>
+  <si>
+    <t>550,000</t>
+  </si>
+  <si>
+    <t>75.56%</t>
+  </si>
+  <si>
+    <t>مينا محمد رحيم مبارك</t>
+  </si>
+  <si>
+    <t>نبأ غازي عبد الامير حسن</t>
+  </si>
+  <si>
+    <t>نورهان معتز جميل احمد</t>
+  </si>
+  <si>
+    <t>هدير حيدر مهدي رضا</t>
+  </si>
+  <si>
+    <t>1,890,000</t>
+  </si>
+  <si>
+    <t>360,000</t>
+  </si>
+  <si>
+    <t>84%</t>
+  </si>
+  <si>
+    <t>ياسين مثنى محمد حمد</t>
+  </si>
+  <si>
+    <t>يسر حسين محسن ناصر</t>
+  </si>
+  <si>
+    <t>يقين كاظم تركي عذيب</t>
+  </si>
+  <si>
+    <t>مريم مازن منير فرحان</t>
+  </si>
+  <si>
+    <t>تبارك ربيع حسن محمد</t>
+  </si>
+  <si>
+    <t>علي عبد الكريم ابراهيم صالح</t>
+  </si>
+  <si>
+    <t>1,625,000</t>
+  </si>
+  <si>
+    <t>72.22%</t>
+  </si>
+  <si>
+    <t>قصي مصطفى عبيد ياسين</t>
+  </si>
+  <si>
+    <t>1,400,000</t>
+  </si>
+  <si>
+    <t>850,000</t>
+  </si>
+  <si>
+    <t>62.22%</t>
+  </si>
+  <si>
+    <t>مرتضى احمد هاشم جواد</t>
+  </si>
+  <si>
+    <t>1,200,000</t>
+  </si>
+  <si>
+    <t>825,000</t>
+  </si>
+  <si>
+    <t>59.26%</t>
+  </si>
+  <si>
+    <t>فاطمه مهند عبد الله عبد الوهاب</t>
+  </si>
+  <si>
+    <t>غازي فيصل فهيد نايف</t>
+  </si>
+  <si>
+    <t>20%</t>
+  </si>
+  <si>
+    <t>حكيم خالد عطيوي حسين</t>
+  </si>
+  <si>
+    <t>رسول رحيم دحام عناد</t>
+  </si>
+  <si>
+    <t>ضحى سمير عزاوي حمودي</t>
+  </si>
+  <si>
+    <t>نور حامد احمد صالح</t>
+  </si>
+  <si>
+    <t>مينا عبد الستار حماد عبد الله</t>
+  </si>
+  <si>
+    <t>1,190,000</t>
+  </si>
+  <si>
+    <t>1,060,000</t>
+  </si>
+  <si>
+    <t>52.89%</t>
+  </si>
+  <si>
+    <t>زينب علاء ناصر عبود</t>
+  </si>
+  <si>
+    <t>1,850,000</t>
+  </si>
+  <si>
+    <t>400,000</t>
+  </si>
+  <si>
+    <t>82.22%</t>
+  </si>
+  <si>
+    <t>طيبة حسين مزيهر سوادي</t>
+  </si>
+  <si>
+    <t>ابراهيم عماد عبدالعزيز حسين</t>
+  </si>
+  <si>
+    <t>فرح مصطفى ياسين عبد الله</t>
+  </si>
+  <si>
+    <t>ايه علي حسن احمد</t>
+  </si>
+  <si>
+    <t>الاولى</t>
+  </si>
+  <si>
+    <t>آمنه اكرم علوان حسين</t>
+  </si>
+  <si>
+    <t>تبارك قصي قاسم احمد</t>
+  </si>
+  <si>
+    <t>روتاج رعد حسين مفتي</t>
+  </si>
+  <si>
+    <t>عبد الله محمد عزيز عاكول</t>
+  </si>
+  <si>
+    <t>قاسم مهدي مجيد مذخور</t>
+  </si>
+  <si>
+    <t>1,530,000</t>
+  </si>
+  <si>
+    <t>720,000</t>
+  </si>
+  <si>
+    <t>68%</t>
+  </si>
+  <si>
+    <t>مختار ناظم عبيس عبد الرضا</t>
+  </si>
+  <si>
+    <t>علا داود سلمان عبد</t>
+  </si>
+  <si>
+    <t>1,775,000</t>
+  </si>
+  <si>
+    <t>475,000</t>
+  </si>
+  <si>
+    <t>78.89%</t>
+  </si>
+  <si>
+    <t>مريم مهدي رشيد سعيد</t>
+  </si>
+  <si>
+    <t>ابو الحسن خالد عوده ايدام</t>
+  </si>
+  <si>
+    <t>الثانية</t>
+  </si>
+  <si>
+    <t>1,050,000</t>
+  </si>
+  <si>
+    <t>53.33%</t>
+  </si>
+  <si>
+    <t>احمد جاسب حاتم جالس</t>
+  </si>
+  <si>
+    <t>احمد جواد كاظم كاوي</t>
+  </si>
+  <si>
+    <t>احمد عبد الرزاق حبيب محمد</t>
+  </si>
+  <si>
+    <t>اسراء حيدر كريم مطلوب</t>
+  </si>
+  <si>
+    <t>اسيل مهند ناظم جياد</t>
+  </si>
+  <si>
+    <t>33.33%</t>
+  </si>
+  <si>
+    <t>اسيل يوسف خضر تايه</t>
+  </si>
+  <si>
+    <t>2,137,500</t>
+  </si>
+  <si>
+    <t>637,500</t>
+  </si>
+  <si>
+    <t>70.18%</t>
+  </si>
+  <si>
+    <t>افنان ناجي سليم عواد</t>
+  </si>
+  <si>
+    <t>الحسين محمد علي صالح</t>
+  </si>
+  <si>
+    <t>امير علي احمد فريدون محمد</t>
+  </si>
+  <si>
+    <t>ايناس عبد السلام حسن عوده</t>
+  </si>
+  <si>
+    <t>أمير فراس زهير حسن</t>
+  </si>
+  <si>
+    <t>بنين حسين علي صباح</t>
+  </si>
+  <si>
+    <t>بنين حميد هاشم شريف</t>
+  </si>
+  <si>
+    <t>جاسم محمد عبد الله عبد</t>
+  </si>
+  <si>
+    <t>جعفر نضال كاظم احمد</t>
+  </si>
+  <si>
+    <t>900,000</t>
+  </si>
+  <si>
+    <t>1,350,000</t>
+  </si>
+  <si>
+    <t>40%</t>
+  </si>
+  <si>
+    <t>جنيد زياد هادي حمد</t>
+  </si>
+  <si>
+    <t>حسن حيدر كاظم فلحي</t>
+  </si>
+  <si>
+    <t>2,060,000</t>
+  </si>
+  <si>
+    <t>190,000</t>
+  </si>
+  <si>
+    <t>91.56%</t>
+  </si>
+  <si>
+    <t>حسن سعدون مزهر شنيور</t>
+  </si>
+  <si>
+    <t>560,000</t>
+  </si>
+  <si>
+    <t>1,690,000</t>
+  </si>
+  <si>
+    <t>24.89%</t>
+  </si>
+  <si>
+    <t>حسن طالب حسين صادق</t>
+  </si>
+  <si>
+    <t>حسين فراس عكار مطير</t>
+  </si>
+  <si>
+    <t>650,000</t>
+  </si>
+  <si>
+    <t>63.89%</t>
+  </si>
+  <si>
+    <t>حليمه مؤيد خيري ذاكر</t>
+  </si>
+  <si>
+    <t>حمزة محمد فالح رخيص</t>
+  </si>
+  <si>
+    <t>حوراء سمير سوادي حسن</t>
+  </si>
+  <si>
+    <t>حيدر حبيب كاظم جواد</t>
+  </si>
+  <si>
+    <t>حيدر صفاء غازي حسن</t>
+  </si>
+  <si>
+    <t>حيدر غسان جليل اسماعيل</t>
+  </si>
+  <si>
+    <t>دعاء علي حسين علي</t>
+  </si>
+  <si>
+    <t>دلال سعدي ناجي داود</t>
+  </si>
+  <si>
+    <t>رحاب نهاد خزعل ابراهيم</t>
+  </si>
+  <si>
+    <t>رقيه حسين عدنان مهدي</t>
+  </si>
+  <si>
+    <t>ريام عز الدين جلوب حمادي</t>
+  </si>
+  <si>
+    <t>ريم حاتم جابر دحيح</t>
+  </si>
+  <si>
+    <t>90%</t>
+  </si>
+  <si>
+    <t>ريم يونس مزيغر منصور</t>
+  </si>
+  <si>
+    <t>زهراء عبد الخضر كاظم عبيد</t>
+  </si>
+  <si>
+    <t>زهراء فراس جاسم حمادي</t>
+  </si>
+  <si>
+    <t>1,825,000</t>
+  </si>
+  <si>
+    <t>425,000</t>
+  </si>
+  <si>
+    <t>81.11%</t>
+  </si>
+  <si>
+    <t>زيد احمد سالم حسن</t>
+  </si>
+  <si>
+    <t>1,110,000</t>
+  </si>
+  <si>
+    <t>15,000</t>
+  </si>
+  <si>
+    <t>98.67%</t>
+  </si>
+  <si>
+    <t>زينب حسن انور مصطفى</t>
+  </si>
+  <si>
+    <t>سارة احمد جواد كاظم</t>
+  </si>
+  <si>
+    <t>سما صفاء بشان عبيد</t>
+  </si>
+  <si>
+    <t>سما صلاح حسن حسين</t>
+  </si>
+  <si>
+    <t>شهد صالح حميد جواد</t>
+  </si>
+  <si>
+    <t>صادق طاهر جاسم محمد</t>
+  </si>
+  <si>
+    <t>صفا حسين حمود محمد</t>
+  </si>
+  <si>
+    <t>ضحى راضي علي سلوم</t>
+  </si>
+  <si>
+    <t>طارق صلاح ياسر موسى</t>
+  </si>
+  <si>
+    <t>775,000</t>
+  </si>
+  <si>
+    <t>61.73%</t>
+  </si>
+  <si>
+    <t>طيبه ايهاب نافع عيد</t>
+  </si>
+  <si>
+    <t>عباس رائد علي محمد</t>
+  </si>
+  <si>
+    <t>عباس علي حسين علي</t>
+  </si>
+  <si>
+    <t>عبد الجليل خالد عبد الجليل ثعبان</t>
+  </si>
+  <si>
+    <t>1,695,000</t>
+  </si>
+  <si>
+    <t>555,000</t>
+  </si>
+  <si>
+    <t>75.33%</t>
+  </si>
+  <si>
+    <t>عبد الرحمن عباس محمود علي</t>
+  </si>
+  <si>
+    <t>عبد الله محمود اسماعيل جواد</t>
+  </si>
+  <si>
+    <t>عبد الله معمر موفق حمود</t>
+  </si>
+  <si>
+    <t>17.78%</t>
+  </si>
+  <si>
+    <t>عبد الوهاب ثامر محمد حسن</t>
+  </si>
+  <si>
+    <t>925,000</t>
+  </si>
+  <si>
+    <t>54.32%</t>
+  </si>
+  <si>
+    <t>علي سليمان عبد حسون</t>
+  </si>
+  <si>
+    <t>علي عادل نعمه</t>
+  </si>
+  <si>
+    <t>علي فرحان جاسم محمد</t>
+  </si>
+  <si>
+    <t>علي فلاح حسن فاضل</t>
+  </si>
+  <si>
+    <t>1,560,000</t>
+  </si>
+  <si>
+    <t>240,000</t>
+  </si>
+  <si>
+    <t>86.67%</t>
+  </si>
+  <si>
+    <t>عمار صباح عبد الستار احمد</t>
+  </si>
+  <si>
+    <t>ليلى سالم عبد اللطيف عبد الكريم</t>
+  </si>
+  <si>
+    <t>ماّب عامر عبد القادر فليح</t>
+  </si>
+  <si>
+    <t>محمد باقر نجم متعب</t>
+  </si>
+  <si>
+    <t>محمد جاسم محمد حسون</t>
+  </si>
+  <si>
+    <t>محمد جمال كاظم احمد</t>
+  </si>
+  <si>
+    <t>375,000</t>
+  </si>
+  <si>
+    <t>محمد صلاح خالد جلاب</t>
+  </si>
+  <si>
+    <t>محمد فراس جبير ابراهيم</t>
+  </si>
+  <si>
+    <t>محمد وليد خالد رشيد</t>
+  </si>
+  <si>
+    <t>مصطفى اياد محمد جاسم</t>
+  </si>
+  <si>
+    <t>مصطفى شاكر محمود محمد</t>
+  </si>
+  <si>
+    <t>1,687,500</t>
+  </si>
+  <si>
+    <t>487,500</t>
+  </si>
+  <si>
+    <t>71.11%</t>
+  </si>
+  <si>
+    <t>مصطفى علاء داود موسى</t>
+  </si>
+  <si>
+    <t>مصطفى علي ناصر حسين</t>
+  </si>
+  <si>
+    <t>مصطفى محمد علي طه</t>
+  </si>
+  <si>
+    <t>675,000</t>
+  </si>
+  <si>
+    <t>60%</t>
+  </si>
+  <si>
+    <t>معتز محمود مطر حسين</t>
+  </si>
+  <si>
+    <t>ملاك عباس عبد علي</t>
+  </si>
+  <si>
+    <t>منقذ عبد الكريم حسين كاظم</t>
+  </si>
+  <si>
+    <t>موده شهاب احمد راكع</t>
+  </si>
+  <si>
+    <t>مؤمن محمد قادر شاواز</t>
+  </si>
+  <si>
+    <t>ميس محمد عصام عبد الوهاب</t>
+  </si>
+  <si>
+    <t>نور ابراهيم خالد محمد</t>
+  </si>
+  <si>
+    <t>يوسف سيف محي جواد</t>
+  </si>
+  <si>
+    <t>يوسف شاكر سالم خلف</t>
+  </si>
+  <si>
+    <t>يوسف نزار هادي ثجيل</t>
+  </si>
+  <si>
+    <t>محمد حذيفة فليح حسن</t>
+  </si>
+  <si>
+    <t>حوراء محمد حسان ناجي</t>
+  </si>
+  <si>
+    <t>رقيه علاء صادق</t>
+  </si>
+  <si>
+    <t>مريم احمد محمود عبيد</t>
+  </si>
+  <si>
+    <t>1,375,000</t>
+  </si>
+  <si>
+    <t>67.9%</t>
+  </si>
+  <si>
+    <t>دينا اسعد حسين محمد</t>
+  </si>
+  <si>
+    <t>587,500</t>
+  </si>
+  <si>
+    <t>65.19%</t>
+  </si>
+  <si>
+    <t>تقى جعفر لعيبي جبار</t>
+  </si>
+  <si>
+    <t>600,000</t>
+  </si>
+  <si>
+    <t>اسياد اياد نايف عبد الحسين</t>
+  </si>
+  <si>
+    <t>80.25%</t>
+  </si>
+  <si>
+    <t>شمس مشتاق طالب علي</t>
+  </si>
+  <si>
+    <t>ترتيل عباس شهاب عبود</t>
+  </si>
+  <si>
+    <t>منتهى وسام عبد حسن حواس</t>
+  </si>
+  <si>
+    <t>975,000</t>
+  </si>
+  <si>
+    <t>51.85%</t>
+  </si>
+  <si>
+    <t>شايان مهدي داود عوده</t>
+  </si>
+  <si>
+    <t>احمد داود سلمان محمد</t>
+  </si>
+  <si>
+    <t>565,000</t>
+  </si>
+  <si>
+    <t>49.78%</t>
+  </si>
+  <si>
+    <t>احمد عبد الرحيم ابراهيم العسكري</t>
+  </si>
+  <si>
+    <t>860,000</t>
+  </si>
+  <si>
+    <t>1,390,000</t>
+  </si>
+  <si>
+    <t>38.22%</t>
+  </si>
+  <si>
+    <t>احمد عطيه محمد جياد</t>
+  </si>
+  <si>
+    <t>احمدي جعفر صادق حسين</t>
+  </si>
+  <si>
+    <t>اسامه خالد قدوري سلمان</t>
+  </si>
+  <si>
+    <t>اسراء سعد نعمة كاظم</t>
+  </si>
+  <si>
+    <t>اسراء شعلان احمد حزوم</t>
+  </si>
+  <si>
+    <t>امين عماد عبد الحميد احمد</t>
+  </si>
+  <si>
+    <t>ايه حامد حسين علوان</t>
+  </si>
+  <si>
+    <t>بشار محمد حاتم حسين</t>
+  </si>
+  <si>
+    <t>بهاء الدين احمد عويد كيطان</t>
+  </si>
+  <si>
+    <t>حيدر علي حسين كاظم</t>
+  </si>
+  <si>
+    <t>زمن داود بناي عبد الله</t>
+  </si>
+  <si>
+    <t>835,000</t>
+  </si>
+  <si>
+    <t>58.77%</t>
+  </si>
+  <si>
+    <t>زهراء عبد الكريم رضا جابر</t>
+  </si>
+  <si>
+    <t>سجاد فراس عباس فاضل</t>
+  </si>
+  <si>
+    <t>شهد عبد الكريم كاظم جلوب</t>
+  </si>
+  <si>
+    <t>عبد الرزاق حسين فوزي اسماعيل</t>
+  </si>
+  <si>
+    <t>2,170,000</t>
+  </si>
+  <si>
+    <t>80,000</t>
+  </si>
+  <si>
+    <t>96.44%</t>
+  </si>
+  <si>
+    <t>عزالدين عبدالكريم عفتان ثامر</t>
+  </si>
+  <si>
+    <t>علي رزاق عباس يوسف</t>
+  </si>
+  <si>
+    <t>عواد قدوري عواد داود</t>
+  </si>
+  <si>
+    <t>مائده عبد محسن فرحان</t>
+  </si>
+  <si>
+    <t>24.44%</t>
+  </si>
+  <si>
+    <t>مجتبى علي فيصل علوان</t>
+  </si>
+  <si>
+    <t>مجيد محمود مجيد حميد</t>
+  </si>
+  <si>
+    <t>محب جاسم محمد صالح</t>
+  </si>
+  <si>
+    <t>محمد محمود صابر صادق</t>
+  </si>
+  <si>
+    <t>مصطفى خلف عبد الله وهيب</t>
+  </si>
+  <si>
+    <t>مصطفى محمود صالح</t>
+  </si>
+  <si>
+    <t>منتظر معتز مهدي عبدالسادة</t>
+  </si>
+  <si>
+    <t>مؤيد وليد مؤيد احمد</t>
+  </si>
+  <si>
+    <t>ميلاد عبد الزهرة عبيد حسين</t>
+  </si>
+  <si>
+    <t>ندى علي عبد الحسين ابراهيم</t>
+  </si>
+  <si>
+    <t>نور صباح صالح نصرالله</t>
   </si>
   <si>
     <t>150,000</t>
-  </si>
-  <si>
-    <t>93.33%</t>
-  </si>
-  <si>
-    <t>حسين عبد الكريم جواد صفر</t>
-  </si>
-  <si>
-    <t>حسين علي كمال مرهون</t>
-  </si>
-  <si>
-    <t>1,800,000</t>
-  </si>
-  <si>
-    <t>2,025,000</t>
-  </si>
-  <si>
-    <t>حسين محمد فالح حسن</t>
-  </si>
-  <si>
-    <t>حوراء حيدر عبد الرزاق ناجي</t>
-  </si>
-  <si>
-    <t>خالد محمد حسين عباس</t>
-  </si>
-  <si>
-    <t>رقيه محسن جبير ناصر</t>
-  </si>
-  <si>
-    <t>رؤى ثامر عاشور خدي</t>
-  </si>
-  <si>
-    <t>رؤى جعفر كامل عباس</t>
-  </si>
-  <si>
-    <t>زهراء حسام ناصر محمد</t>
-  </si>
-  <si>
-    <t>زهراء محمد حسين علوان</t>
-  </si>
-  <si>
-    <t>زينب معد فالح حسن</t>
-  </si>
-  <si>
-    <t>سجاد ماجد حسين علوان</t>
-  </si>
-  <si>
-    <t>شهد نوري سعدون شمران</t>
-  </si>
-  <si>
-    <t>شيفان خليل محمد ملك</t>
-  </si>
-  <si>
-    <t>طه رعد جبير جميس</t>
-  </si>
-  <si>
-    <t>0%</t>
-  </si>
-  <si>
-    <t>أقل من 25%</t>
-  </si>
-  <si>
-    <t>طيبه عدنان عبد الجبار عبد الكريم</t>
-  </si>
-  <si>
-    <t>عباس خليل حيدر ادهم</t>
-  </si>
-  <si>
-    <t>1,500,000</t>
-  </si>
-  <si>
-    <t>750,000</t>
-  </si>
-  <si>
-    <t>66.67%</t>
-  </si>
-  <si>
-    <t>مسدد 50%+</t>
-  </si>
-  <si>
-    <t>عباس علي حسين داخل</t>
-  </si>
-  <si>
-    <t>1,250,000</t>
-  </si>
-  <si>
-    <t>1,000,000</t>
-  </si>
-  <si>
-    <t>55.56%</t>
-  </si>
-  <si>
-    <t>عبد الرحمن رائد عبد الحميد محمود</t>
-  </si>
-  <si>
-    <t>عبد السلام نوري سعدون حمادي</t>
-  </si>
-  <si>
-    <t>1,300,000</t>
-  </si>
-  <si>
-    <t>950,000</t>
-  </si>
-  <si>
-    <t>57.78%</t>
-  </si>
-  <si>
-    <t>عبد الله عوده مكي جواد</t>
-  </si>
-  <si>
-    <t>علي الرضا سعد عبد محمد</t>
-  </si>
-  <si>
-    <t>2,000,000</t>
-  </si>
-  <si>
-    <t>250,000</t>
-  </si>
-  <si>
-    <t>88.89%</t>
-  </si>
-  <si>
-    <t>علي جمال فتحي لطيف</t>
-  </si>
-  <si>
-    <t>علي حازم جبار جبر</t>
-  </si>
-  <si>
-    <t>علي خالد محمود سلطان</t>
-  </si>
-  <si>
-    <t>علي زاهد جاسم كاظم</t>
-  </si>
-  <si>
-    <t>1,675,000</t>
-  </si>
-  <si>
-    <t>575,000</t>
-  </si>
-  <si>
-    <t>74.44%</t>
-  </si>
-  <si>
-    <t>علي فراس كريم سلمان</t>
-  </si>
-  <si>
-    <t>علي لؤي صادق جعفر</t>
-  </si>
-  <si>
-    <t>علي مؤيد احمد صالح</t>
-  </si>
-  <si>
-    <t>عمر يحيى مراد صالح</t>
-  </si>
-  <si>
-    <t>غسق مهدي جابر حمودي</t>
-  </si>
-  <si>
-    <t>فاطمه حيدر مهدي خضير</t>
-  </si>
-  <si>
-    <t>قاسم كريم محمود عنبر</t>
-  </si>
-  <si>
-    <t>225,000</t>
-  </si>
-  <si>
-    <t>كرار حيدر عبود هادي</t>
-  </si>
-  <si>
-    <t>11.11%</t>
-  </si>
-  <si>
-    <t>كوثر حسن نعمه عيسى</t>
-  </si>
-  <si>
-    <t>1,687,500</t>
-  </si>
-  <si>
-    <t>1,187,500</t>
-  </si>
-  <si>
-    <t>29.63%</t>
-  </si>
-  <si>
-    <t>محمد المهدي عيسى لطيف يونس</t>
-  </si>
-  <si>
-    <t>محمد صادق جعفر مجيد</t>
-  </si>
-  <si>
-    <t>450,000</t>
-  </si>
-  <si>
-    <t>22.22%</t>
-  </si>
-  <si>
-    <t>محمد علي عوج عجه</t>
-  </si>
-  <si>
-    <t>محمد كريم عمران موسى</t>
-  </si>
-  <si>
-    <t>محمد محمود ابراهيم محمود</t>
-  </si>
-  <si>
-    <t>1,550,000</t>
-  </si>
-  <si>
-    <t>700,000</t>
-  </si>
-  <si>
-    <t>68.89%</t>
-  </si>
-  <si>
-    <t>محمد منصور عبد الله مضهضب</t>
-  </si>
-  <si>
-    <t>مرتضى محمد عبد الخالق علوان</t>
-  </si>
-  <si>
-    <t>مصطفى حيدر محمود علي</t>
-  </si>
-  <si>
-    <t>مصطفى عبد الكاظم جليل عبد الرضا</t>
-  </si>
-  <si>
-    <t>مصطفى نبيل جاسم خضير</t>
-  </si>
-  <si>
-    <t>80%</t>
-  </si>
-  <si>
-    <t>مقتدى علي ابراهيم حسين</t>
-  </si>
-  <si>
-    <t>800,000</t>
-  </si>
-  <si>
-    <t>ملاك ثامر تركي خضير</t>
-  </si>
-  <si>
-    <t>منتظر حيدر خليل ابراهيم</t>
-  </si>
-  <si>
-    <t>منتظر يوسف حميد كاظم</t>
-  </si>
-  <si>
-    <t>1,100,000</t>
-  </si>
-  <si>
-    <t>1,150,000</t>
-  </si>
-  <si>
-    <t>48.89%</t>
-  </si>
-  <si>
-    <t>مهدي احمد عبد الأمير عبد الحسين</t>
-  </si>
-  <si>
-    <t>مهدي علي نبيل صالح</t>
-  </si>
-  <si>
-    <t>1,700,000</t>
-  </si>
-  <si>
-    <t>550,000</t>
-  </si>
-  <si>
-    <t>75.56%</t>
-  </si>
-  <si>
-    <t>مينا محمد رحيم مبارك</t>
-  </si>
-  <si>
-    <t>نبأ غازي عبد الامير حسن</t>
-  </si>
-  <si>
-    <t>نورهان معتز جميل احمد</t>
-  </si>
-  <si>
-    <t>هدير حيدر مهدي رضا</t>
-  </si>
-  <si>
-    <t>1,890,000</t>
-  </si>
-  <si>
-    <t>360,000</t>
-  </si>
-  <si>
-    <t>84%</t>
-  </si>
-  <si>
-    <t>ياسين مثنى محمد حمد</t>
-  </si>
-  <si>
-    <t>يسر حسين محسن ناصر</t>
-  </si>
-  <si>
-    <t>يقين كاظم تركي عذيب</t>
-  </si>
-  <si>
-    <t>مريم مازن منير فرحان</t>
-  </si>
-  <si>
-    <t>تبارك ربيع حسن محمد</t>
-  </si>
-  <si>
-    <t>علي عبد الكريم ابراهيم صالح</t>
-  </si>
-  <si>
-    <t>1,625,000</t>
-  </si>
-  <si>
-    <t>72.22%</t>
-  </si>
-  <si>
-    <t>قصي مصطفى عبيد ياسين</t>
-  </si>
-  <si>
-    <t>1,400,000</t>
-  </si>
-  <si>
-    <t>850,000</t>
-  </si>
-  <si>
-    <t>62.22%</t>
-  </si>
-  <si>
-    <t>مرتضى احمد هاشم جواد</t>
-  </si>
-  <si>
-    <t>1,200,000</t>
-  </si>
-  <si>
-    <t>825,000</t>
-  </si>
-  <si>
-    <t>59.26%</t>
-  </si>
-  <si>
-    <t>فاطمه مهند عبد الله عبد الوهاب</t>
-  </si>
-  <si>
-    <t>غازي فيصل فهيد نايف</t>
-  </si>
-  <si>
-    <t>20%</t>
-  </si>
-  <si>
-    <t>حكيم خالد عطيوي حسين</t>
-  </si>
-  <si>
-    <t>رسول رحيم دحام عناد</t>
-  </si>
-  <si>
-    <t>ضحى سمير عزاوي حمودي</t>
-  </si>
-  <si>
-    <t>نور حامد احمد صالح</t>
-  </si>
-  <si>
-    <t>مينا عبد الستار حماد عبد الله</t>
-  </si>
-  <si>
-    <t>1,190,000</t>
-  </si>
-  <si>
-    <t>1,060,000</t>
-  </si>
-  <si>
-    <t>52.89%</t>
-  </si>
-  <si>
-    <t>زينب علاء ناصر عبود</t>
-  </si>
-  <si>
-    <t>1,850,000</t>
-  </si>
-  <si>
-    <t>400,000</t>
-  </si>
-  <si>
-    <t>82.22%</t>
-  </si>
-  <si>
-    <t>طيبة حسين مزيهر سوادي</t>
-  </si>
-  <si>
-    <t>ابراهيم عماد عبدالعزيز حسين</t>
-  </si>
-  <si>
-    <t>فرح مصطفى ياسين عبد الله</t>
-  </si>
-  <si>
-    <t>ايه علي حسن احمد</t>
-  </si>
-  <si>
-    <t>الاولى</t>
-  </si>
-  <si>
-    <t>آمنه اكرم علوان حسين</t>
-  </si>
-  <si>
-    <t>تبارك قصي قاسم احمد</t>
-  </si>
-  <si>
-    <t>روتاج رعد حسين مفتي</t>
-  </si>
-  <si>
-    <t>عبد الله محمد عزيز عاكول</t>
-  </si>
-  <si>
-    <t>قاسم مهدي مجيد مذخور</t>
-  </si>
-  <si>
-    <t>1,530,000</t>
-  </si>
-  <si>
-    <t>720,000</t>
-  </si>
-  <si>
-    <t>68%</t>
-  </si>
-  <si>
-    <t>مختار ناظم عبيس عبد الرضا</t>
-  </si>
-  <si>
-    <t>علا داود سلمان عبد</t>
-  </si>
-  <si>
-    <t>1,775,000</t>
-  </si>
-  <si>
-    <t>475,000</t>
-  </si>
-  <si>
-    <t>78.89%</t>
-  </si>
-  <si>
-    <t>مريم مهدي رشيد سعيد</t>
-  </si>
-  <si>
-    <t>ابو الحسن خالد عوده ايدام</t>
-  </si>
-  <si>
-    <t>الثانية</t>
-  </si>
-  <si>
-    <t>1,050,000</t>
-  </si>
-  <si>
-    <t>53.33%</t>
-  </si>
-  <si>
-    <t>احمد جاسب حاتم جالس</t>
-  </si>
-  <si>
-    <t>احمد جواد كاظم كاوي</t>
-  </si>
-  <si>
-    <t>احمد عبد الرزاق حبيب محمد</t>
-  </si>
-  <si>
-    <t>اسراء حيدر كريم مطلوب</t>
-  </si>
-  <si>
-    <t>اسيل مهند ناظم جياد</t>
-  </si>
-  <si>
-    <t>33.33%</t>
-  </si>
-  <si>
-    <t>اسيل يوسف خضر تايه</t>
-  </si>
-  <si>
-    <t>2,137,500</t>
-  </si>
-  <si>
-    <t>637,500</t>
-  </si>
-  <si>
-    <t>70.18%</t>
-  </si>
-  <si>
-    <t>افنان ناجي سليم عواد</t>
-  </si>
-  <si>
-    <t>الحسين محمد علي صالح</t>
-  </si>
-  <si>
-    <t>امير علي احمد فريدون محمد</t>
-  </si>
-  <si>
-    <t>ايناس عبد السلام حسن عوده</t>
-  </si>
-  <si>
-    <t>أمير فراس زهير حسن</t>
-  </si>
-  <si>
-    <t>بنين حسين علي صباح</t>
-  </si>
-  <si>
-    <t>بنين حميد هاشم شريف</t>
-  </si>
-  <si>
-    <t>جاسم محمد عبد الله عبد</t>
-  </si>
-  <si>
-    <t>جعفر نضال كاظم احمد</t>
-  </si>
-  <si>
-    <t>900,000</t>
-  </si>
-  <si>
-    <t>1,350,000</t>
-  </si>
-  <si>
-    <t>40%</t>
-  </si>
-  <si>
-    <t>جنيد زياد هادي حمد</t>
-  </si>
-  <si>
-    <t>حسن حيدر كاظم فلحي</t>
-  </si>
-  <si>
-    <t>2,060,000</t>
-  </si>
-  <si>
-    <t>190,000</t>
-  </si>
-  <si>
-    <t>91.56%</t>
-  </si>
-  <si>
-    <t>حسن سعدون مزهر شنيور</t>
-  </si>
-  <si>
-    <t>560,000</t>
-  </si>
-  <si>
-    <t>1,690,000</t>
-  </si>
-  <si>
-    <t>24.89%</t>
-  </si>
-  <si>
-    <t>حسن طالب حسين صادق</t>
-  </si>
-  <si>
-    <t>حسين فراس عكار مطير</t>
-  </si>
-  <si>
-    <t>650,000</t>
-  </si>
-  <si>
-    <t>63.89%</t>
-  </si>
-  <si>
-    <t>حليمه مؤيد خيري ذاكر</t>
-  </si>
-  <si>
-    <t>حمزة محمد فالح رخيص</t>
-  </si>
-  <si>
-    <t>حوراء سمير سوادي حسن</t>
-  </si>
-  <si>
-    <t>حيدر حبيب كاظم جواد</t>
-  </si>
-  <si>
-    <t>حيدر صفاء غازي حسن</t>
-  </si>
-  <si>
-    <t>حيدر غسان جليل اسماعيل</t>
-  </si>
-  <si>
-    <t>دعاء علي حسين علي</t>
-  </si>
-  <si>
-    <t>دلال سعدي ناجي داود</t>
-  </si>
-  <si>
-    <t>رحاب نهاد خزعل ابراهيم</t>
-  </si>
-  <si>
-    <t>رقيه حسين عدنان مهدي</t>
-  </si>
-  <si>
-    <t>ريام عز الدين جلوب حمادي</t>
-  </si>
-  <si>
-    <t>562,500</t>
-  </si>
-  <si>
-    <t>ريم حاتم جابر دحيح</t>
-  </si>
-  <si>
-    <t>90%</t>
-  </si>
-  <si>
-    <t>ريم يونس مزيغر منصور</t>
-  </si>
-  <si>
-    <t>زهراء عبد الخضر كاظم عبيد</t>
-  </si>
-  <si>
-    <t>زهراء فراس جاسم حمادي</t>
-  </si>
-  <si>
-    <t>1,825,000</t>
-  </si>
-  <si>
-    <t>425,000</t>
-  </si>
-  <si>
-    <t>81.11%</t>
-  </si>
-  <si>
-    <t>زيد احمد سالم حسن</t>
-  </si>
-  <si>
-    <t>1,110,000</t>
-  </si>
-  <si>
-    <t>15,000</t>
-  </si>
-  <si>
-    <t>98.67%</t>
-  </si>
-  <si>
-    <t>زينب حسن انور مصطفى</t>
-  </si>
-  <si>
-    <t>سارة احمد جواد كاظم</t>
-  </si>
-  <si>
-    <t>سما صفاء بشان عبيد</t>
-  </si>
-  <si>
-    <t>سما صلاح حسن حسين</t>
-  </si>
-  <si>
-    <t>شهد صالح حميد جواد</t>
-  </si>
-  <si>
-    <t>صادق طاهر جاسم محمد</t>
-  </si>
-  <si>
-    <t>صفا حسين حمود محمد</t>
-  </si>
-  <si>
-    <t>ضحى راضي علي سلوم</t>
-  </si>
-  <si>
-    <t>طارق صلاح ياسر موسى</t>
-  </si>
-  <si>
-    <t>775,000</t>
-  </si>
-  <si>
-    <t>61.73%</t>
-  </si>
-  <si>
-    <t>طيبه ايهاب نافع عيد</t>
-  </si>
-  <si>
-    <t>عباس رائد علي محمد</t>
-  </si>
-  <si>
-    <t>عباس علي حسين علي</t>
-  </si>
-  <si>
-    <t>عبد الجليل خالد عبد الجليل ثعبان</t>
-  </si>
-  <si>
-    <t>1,695,000</t>
-  </si>
-  <si>
-    <t>555,000</t>
-  </si>
-  <si>
-    <t>75.33%</t>
-  </si>
-  <si>
-    <t>عبد الرحمن عباس محمود علي</t>
-  </si>
-  <si>
-    <t>1,950,000</t>
-  </si>
-  <si>
-    <t>300,000</t>
-  </si>
-  <si>
-    <t>86.67%</t>
-  </si>
-  <si>
-    <t>عبد الله محمود اسماعيل جواد</t>
-  </si>
-  <si>
-    <t>عبد الله معمر موفق حمود</t>
-  </si>
-  <si>
-    <t>17.78%</t>
-  </si>
-  <si>
-    <t>عبد الوهاب ثامر محمد حسن</t>
-  </si>
-  <si>
-    <t>925,000</t>
-  </si>
-  <si>
-    <t>54.32%</t>
-  </si>
-  <si>
-    <t>علي سليمان عبد حسون</t>
-  </si>
-  <si>
-    <t>علي عادل نعمه</t>
-  </si>
-  <si>
-    <t>علي فرحان جاسم محمد</t>
-  </si>
-  <si>
-    <t>علي فلاح حسن فاضل</t>
-  </si>
-  <si>
-    <t>1,560,000</t>
-  </si>
-  <si>
-    <t>240,000</t>
-  </si>
-  <si>
-    <t>عمار صباح عبد الستار احمد</t>
-  </si>
-  <si>
-    <t>ليلى سالم عبد اللطيف عبد الكريم</t>
-  </si>
-  <si>
-    <t>ماّب عامر عبد القادر فليح</t>
-  </si>
-  <si>
-    <t>محمد باقر نجم متعب</t>
-  </si>
-  <si>
-    <t>محمد جاسم محمد حسون</t>
-  </si>
-  <si>
-    <t>محمد جمال كاظم احمد</t>
-  </si>
-  <si>
-    <t>375,000</t>
-  </si>
-  <si>
-    <t>محمد صلاح خالد جلاب</t>
-  </si>
-  <si>
-    <t>محمد فراس جبير ابراهيم</t>
-  </si>
-  <si>
-    <t>محمد وليد خالد رشيد</t>
-  </si>
-  <si>
-    <t>مصطفى اياد محمد جاسم</t>
-  </si>
-  <si>
-    <t>مصطفى شاكر محمود محمد</t>
-  </si>
-  <si>
-    <t>487,500</t>
-  </si>
-  <si>
-    <t>71.11%</t>
-  </si>
-  <si>
-    <t>مصطفى علاء داود موسى</t>
-  </si>
-  <si>
-    <t>مصطفى علي ناصر حسين</t>
-  </si>
-  <si>
-    <t>مصطفى محمد علي طه</t>
-  </si>
-  <si>
-    <t>675,000</t>
-  </si>
-  <si>
-    <t>60%</t>
-  </si>
-  <si>
-    <t>معتز محمود مطر حسين</t>
-  </si>
-  <si>
-    <t>ملاك عباس عبد علي</t>
-  </si>
-  <si>
-    <t>منقذ عبد الكريم حسين كاظم</t>
-  </si>
-  <si>
-    <t>موده شهاب احمد راكع</t>
-  </si>
-  <si>
-    <t>مؤمن محمد قادر شاواز</t>
-  </si>
-  <si>
-    <t>ميس محمد عصام عبد الوهاب</t>
-  </si>
-  <si>
-    <t>نور ابراهيم خالد محمد</t>
-  </si>
-  <si>
-    <t>يوسف سيف محي جواد</t>
-  </si>
-  <si>
-    <t>يوسف شاكر سالم خلف</t>
-  </si>
-  <si>
-    <t>يوسف نزار هادي ثجيل</t>
-  </si>
-  <si>
-    <t>محمد حذيفة فليح حسن</t>
-  </si>
-  <si>
-    <t>حوراء محمد حسان ناجي</t>
-  </si>
-  <si>
-    <t>رقيه علاء صادق</t>
-  </si>
-  <si>
-    <t>مريم احمد محمود عبيد</t>
-  </si>
-  <si>
-    <t>1,375,000</t>
-  </si>
-  <si>
-    <t>67.9%</t>
-  </si>
-  <si>
-    <t>دينا اسعد حسين محمد</t>
-  </si>
-  <si>
-    <t>587,500</t>
-  </si>
-  <si>
-    <t>65.19%</t>
-  </si>
-  <si>
-    <t>تقى جعفر لعيبي جبار</t>
-  </si>
-  <si>
-    <t>600,000</t>
-  </si>
-  <si>
-    <t>اسياد اياد نايف عبد الحسين</t>
-  </si>
-  <si>
-    <t>80.25%</t>
-  </si>
-  <si>
-    <t>شمس مشتاق طالب علي</t>
-  </si>
-  <si>
-    <t>ترتيل عباس شهاب عبود</t>
-  </si>
-  <si>
-    <t>منتهى وسام عبد حسن حواس</t>
-  </si>
-  <si>
-    <t>975,000</t>
-  </si>
-  <si>
-    <t>51.85%</t>
-  </si>
-  <si>
-    <t>شايان مهدي داود عوده</t>
-  </si>
-  <si>
-    <t>احمد داود سلمان محمد</t>
-  </si>
-  <si>
-    <t>565,000</t>
-  </si>
-  <si>
-    <t>49.78%</t>
-  </si>
-  <si>
-    <t>احمد عبد الرحيم ابراهيم العسكري</t>
-  </si>
-  <si>
-    <t>860,000</t>
-  </si>
-  <si>
-    <t>1,390,000</t>
-  </si>
-  <si>
-    <t>38.22%</t>
-  </si>
-  <si>
-    <t>احمد عطيه محمد جياد</t>
-  </si>
-  <si>
-    <t>احمدي جعفر صادق حسين</t>
-  </si>
-  <si>
-    <t>اسامه خالد قدوري سلمان</t>
-  </si>
-  <si>
-    <t>اسراء سعد نعمة كاظم</t>
-  </si>
-  <si>
-    <t>اسراء شعلان احمد حزوم</t>
-  </si>
-  <si>
-    <t>امين عماد عبد الحميد احمد</t>
-  </si>
-  <si>
-    <t>ايه حامد حسين علوان</t>
-  </si>
-  <si>
-    <t>بشار محمد حاتم حسين</t>
-  </si>
-  <si>
-    <t>بهاء الدين احمد عويد كيطان</t>
-  </si>
-  <si>
-    <t>حيدر علي حسين كاظم</t>
-  </si>
-  <si>
-    <t>زمن داود بناي عبد الله</t>
-  </si>
-  <si>
-    <t>835,000</t>
-  </si>
-  <si>
-    <t>58.77%</t>
-  </si>
-  <si>
-    <t>زهراء عبد الكريم رضا جابر</t>
-  </si>
-  <si>
-    <t>سجاد فراس عباس فاضل</t>
-  </si>
-  <si>
-    <t>شهد عبد الكريم كاظم جلوب</t>
-  </si>
-  <si>
-    <t>عبد الرزاق حسين فوزي اسماعيل</t>
-  </si>
-  <si>
-    <t>2,170,000</t>
-  </si>
-  <si>
-    <t>80,000</t>
-  </si>
-  <si>
-    <t>96.44%</t>
-  </si>
-  <si>
-    <t>عزالدين عبدالكريم عفتان ثامر</t>
-  </si>
-  <si>
-    <t>علي رزاق عباس يوسف</t>
-  </si>
-  <si>
-    <t>عواد قدوري عواد داود</t>
-  </si>
-  <si>
-    <t>مائده عبد محسن فرحان</t>
-  </si>
-  <si>
-    <t>24.44%</t>
-  </si>
-  <si>
-    <t>مجتبى علي فيصل علوان</t>
-  </si>
-  <si>
-    <t>مجيد محمود مجيد حميد</t>
-  </si>
-  <si>
-    <t>محب جاسم محمد صالح</t>
-  </si>
-  <si>
-    <t>محمد محمود صابر صادق</t>
-  </si>
-  <si>
-    <t>مصطفى خلف عبد الله وهيب</t>
-  </si>
-  <si>
-    <t>مصطفى محمود صالح</t>
-  </si>
-  <si>
-    <t>منتظر معتز مهدي عبدالسادة</t>
-  </si>
-  <si>
-    <t>مؤيد وليد مؤيد احمد</t>
-  </si>
-  <si>
-    <t>ميلاد عبد الزهرة عبيد حسين</t>
-  </si>
-  <si>
-    <t>ندى علي عبد الحسين ابراهيم</t>
-  </si>
-  <si>
-    <t>نور صباح صالح نصرالله</t>
   </si>
   <si>
     <t>هبه عبد الكريم جبار نفل</t>
@@ -2158,61 +2140,61 @@
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="2">
+      <c r="A18" s="4">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="2" t="s">
+      <c r="C18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="C19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="2">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>16</v>
+      <c r="F19" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -2220,7 +2202,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>10</v>
@@ -2229,10 +2211,10 @@
         <v>11</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G20" s="4">
         <v>0</v>
@@ -2249,7 +2231,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>10</v>
@@ -2278,7 +2260,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>10</v>
@@ -2287,10 +2269,10 @@
         <v>11</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G22" s="4">
         <v>0</v>
@@ -2307,7 +2289,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>10</v>
@@ -2336,7 +2318,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>10</v>
@@ -2365,7 +2347,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>10</v>
@@ -2374,10 +2356,10 @@
         <v>11</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G25" s="4">
         <v>0</v>
@@ -2394,7 +2376,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>10</v>
@@ -2423,7 +2405,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>10</v>
@@ -2432,10 +2414,10 @@
         <v>11</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G27" s="4">
         <v>0</v>
@@ -2452,7 +2434,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>10</v>
@@ -2461,10 +2443,10 @@
         <v>11</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G28" s="4">
         <v>0</v>
@@ -2481,7 +2463,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>10</v>
@@ -2490,10 +2472,10 @@
         <v>11</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G29" s="4">
         <v>0</v>
@@ -2510,7 +2492,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>10</v>
@@ -2539,7 +2521,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>10</v>
@@ -2568,7 +2550,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>10</v>
@@ -2577,10 +2559,10 @@
         <v>11</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G32" s="4">
         <v>0</v>
@@ -2597,7 +2579,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>10</v>
@@ -2606,19 +2588,19 @@
         <v>11</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F33" s="5">
         <v>0</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -2626,7 +2608,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>10</v>
@@ -2655,28 +2637,28 @@
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H35" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" s="6" t="s">
+      <c r="I35" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -2684,28 +2666,28 @@
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>71</v>
-      </c>
       <c r="I36" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -2713,7 +2695,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>10</v>
@@ -2731,10 +2713,10 @@
         <v>12</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -2742,28 +2724,28 @@
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>76</v>
-      </c>
       <c r="I38" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -2771,7 +2753,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>10</v>
@@ -2800,25 +2782,25 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H40" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>16</v>
@@ -2829,7 +2811,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>10</v>
@@ -2858,7 +2840,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>10</v>
@@ -2870,10 +2852,10 @@
         <v>12</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>20</v>
@@ -2887,7 +2869,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>10</v>
@@ -2896,10 +2878,10 @@
         <v>11</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G43" s="4">
         <v>0</v>
@@ -2916,28 +2898,28 @@
         <v>43</v>
       </c>
       <c r="B44" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C44" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>88</v>
-      </c>
       <c r="I44" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -2945,7 +2927,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>10</v>
@@ -2963,10 +2945,10 @@
         <v>12</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -2974,7 +2956,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>10</v>
@@ -3003,7 +2985,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>10</v>
@@ -3032,7 +3014,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>10</v>
@@ -3044,13 +3026,13 @@
         <v>12</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>16</v>
@@ -3061,7 +3043,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>10</v>
@@ -3090,7 +3072,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>10</v>
@@ -3119,7 +3101,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>10</v>
@@ -3128,16 +3110,16 @@
         <v>11</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>16</v>
@@ -3148,57 +3130,57 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="4">
+        <v>52</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C52" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="G52" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="H52" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="I52" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="3">
-        <v>52</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>21</v>
+      <c r="F53" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G53" s="4">
+        <v>0</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -3206,7 +3188,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>10</v>
@@ -3218,16 +3200,16 @@
         <v>12</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -3235,7 +3217,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>10</v>
@@ -3244,19 +3226,19 @@
         <v>11</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>27</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -3264,7 +3246,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>10</v>
@@ -3276,13 +3258,13 @@
         <v>12</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>16</v>
@@ -3293,7 +3275,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>10</v>
@@ -3305,10 +3287,10 @@
         <v>12</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>20</v>
@@ -3322,7 +3304,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>10</v>
@@ -3334,16 +3316,16 @@
         <v>12</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -3351,7 +3333,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>10</v>
@@ -3360,10 +3342,10 @@
         <v>11</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G59" s="4">
         <v>0</v>
@@ -3380,7 +3362,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>10</v>
@@ -3409,7 +3391,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>10</v>
@@ -3438,7 +3420,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>10</v>
@@ -3467,7 +3449,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>10</v>
@@ -3479,13 +3461,13 @@
         <v>12</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>16</v>
@@ -3496,7 +3478,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>10</v>
@@ -3505,13 +3487,13 @@
         <v>11</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>20</v>
@@ -3525,7 +3507,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>10</v>
@@ -3554,7 +3536,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>10</v>
@@ -3583,7 +3565,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>10</v>
@@ -3595,13 +3577,13 @@
         <v>12</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>21</v>
@@ -3612,7 +3594,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>10</v>
@@ -3641,7 +3623,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>10</v>
@@ -3653,13 +3635,13 @@
         <v>12</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>16</v>
@@ -3670,7 +3652,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>10</v>
@@ -3682,13 +3664,13 @@
         <v>12</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>16</v>
@@ -3699,7 +3681,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>10</v>
@@ -3708,10 +3690,10 @@
         <v>11</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G71" s="4">
         <v>0</v>
@@ -3728,7 +3710,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>10</v>
@@ -3757,7 +3739,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>10</v>
@@ -3769,13 +3751,13 @@
         <v>12</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>16</v>
@@ -3786,7 +3768,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>10</v>
@@ -3815,7 +3797,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>10</v>
@@ -3844,7 +3826,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>10</v>
@@ -3873,7 +3855,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>10</v>
@@ -3902,7 +3884,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>10</v>
@@ -3931,7 +3913,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>10</v>
@@ -3943,16 +3925,16 @@
         <v>12</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G79" s="6" t="s">
         <v>19</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -3960,7 +3942,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>10</v>
@@ -3972,16 +3954,16 @@
         <v>12</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -3989,7 +3971,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>10</v>
@@ -3998,48 +3980,48 @@
         <v>11</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="82" spans="1:9">
-      <c r="A82" s="2">
+      <c r="A82" s="4">
         <v>81</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I82" s="2" t="s">
-        <v>16</v>
+      <c r="B82" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G82" s="4">
+        <v>0</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I82" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -4047,7 +4029,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>10</v>
@@ -4059,16 +4041,16 @@
         <v>12</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -4076,7 +4058,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>10</v>
@@ -4105,7 +4087,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>10</v>
@@ -4134,7 +4116,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>10</v>
@@ -4163,7 +4145,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>10</v>
@@ -4192,7 +4174,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>10</v>
@@ -4204,16 +4186,16 @@
         <v>12</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -4221,7 +4203,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>10</v>
@@ -4233,13 +4215,13 @@
         <v>12</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>16</v>
@@ -4250,7 +4232,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>10</v>
@@ -4279,7 +4261,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>10</v>
@@ -4308,7 +4290,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>10</v>
@@ -4337,13 +4319,13 @@
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>12</v>
@@ -4366,7 +4348,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>10</v>
@@ -4395,7 +4377,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>10</v>
@@ -4424,7 +4406,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>10</v>
@@ -4453,7 +4435,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>10</v>
@@ -4482,7 +4464,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>10</v>
@@ -4494,16 +4476,16 @@
         <v>12</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -4511,7 +4493,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>10</v>
@@ -4523,16 +4505,16 @@
         <v>12</v>
       </c>
       <c r="F99" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="I99" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="G99" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="H99" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="I99" s="6" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -4540,7 +4522,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>10</v>
@@ -4552,13 +4534,13 @@
         <v>12</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>16</v>
@@ -4569,7 +4551,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>10</v>
@@ -4598,28 +4580,28 @@
         <v>101</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -4627,13 +4609,13 @@
         <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E103" s="4" t="s">
         <v>12</v>
@@ -4656,13 +4638,13 @@
         <v>103</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E104" s="4" t="s">
         <v>12</v>
@@ -4685,13 +4667,13 @@
         <v>104</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E105" s="4" t="s">
         <v>12</v>
@@ -4714,13 +4696,13 @@
         <v>105</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>12</v>
@@ -4743,25 +4725,25 @@
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>21</v>
@@ -4772,28 +4754,28 @@
         <v>107</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="F108" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G108" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I108" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="G108" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="I108" s="6" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -4801,13 +4783,13 @@
         <v>108</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E109" s="4" t="s">
         <v>12</v>
@@ -4830,19 +4812,19 @@
         <v>109</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G110" s="4">
         <v>0</v>
@@ -4859,28 +4841,28 @@
         <v>110</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E111" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F111" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G111" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H111" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="I111" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="G111" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="H111" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="I111" s="6" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -4888,13 +4870,13 @@
         <v>111</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E112" s="4" t="s">
         <v>12</v>
@@ -4917,13 +4899,13 @@
         <v>112</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>12</v>
@@ -4935,10 +4917,10 @@
         <v>12</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I113" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -4946,13 +4928,13 @@
         <v>113</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E114" s="4" t="s">
         <v>12</v>
@@ -4975,13 +4957,13 @@
         <v>114</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E115" s="4" t="s">
         <v>12</v>
@@ -5004,13 +4986,13 @@
         <v>115</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E116" s="4" t="s">
         <v>12</v>
@@ -5033,25 +5015,25 @@
         <v>116</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E117" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>21</v>
@@ -5062,13 +5044,13 @@
         <v>117</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E118" s="4" t="s">
         <v>12</v>
@@ -5091,25 +5073,25 @@
         <v>118</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="I119" s="2" t="s">
         <v>16</v>
@@ -5120,57 +5102,57 @@
         <v>119</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C120" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E120" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="I120" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="121" spans="1:9">
-      <c r="A121" s="6">
+      <c r="A121" s="4">
         <v>120</v>
       </c>
-      <c r="B121" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="C121" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="E121" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F121" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="G121" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H121" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="I121" s="6" t="s">
-        <v>67</v>
+      <c r="B121" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G121" s="4">
+        <v>0</v>
+      </c>
+      <c r="H121" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I121" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -5178,28 +5160,28 @@
         <v>121</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -5207,28 +5189,28 @@
         <v>122</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E123" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G123" s="6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H123" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I123" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -5236,25 +5218,25 @@
         <v>123</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="I124" s="3" t="s">
         <v>21</v>
@@ -5265,13 +5247,13 @@
         <v>124</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>12</v>
@@ -5294,13 +5276,13 @@
         <v>125</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E126" s="4" t="s">
         <v>12</v>
@@ -5323,13 +5305,13 @@
         <v>126</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E127" s="5" t="s">
         <v>12</v>
@@ -5341,10 +5323,10 @@
         <v>12</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I127" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -5352,13 +5334,13 @@
         <v>127</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E128" s="4" t="s">
         <v>12</v>
@@ -5381,19 +5363,19 @@
         <v>128</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G129" s="4">
         <v>0</v>
@@ -5410,13 +5392,13 @@
         <v>129</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E130" s="4" t="s">
         <v>12</v>
@@ -5439,13 +5421,13 @@
         <v>130</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E131" s="4" t="s">
         <v>12</v>
@@ -5468,13 +5450,13 @@
         <v>131</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C132" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E132" s="5" t="s">
         <v>12</v>
@@ -5486,10 +5468,10 @@
         <v>12</v>
       </c>
       <c r="H132" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I132" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -5497,19 +5479,19 @@
         <v>132</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>239</v>
+        <v>97</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>239</v>
+        <v>97</v>
       </c>
       <c r="G133" s="4">
         <v>0</v>
@@ -5526,25 +5508,25 @@
         <v>133</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="I134" s="2" t="s">
         <v>16</v>
@@ -5555,13 +5537,13 @@
         <v>134</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E135" s="4" t="s">
         <v>12</v>
@@ -5584,13 +5566,13 @@
         <v>135</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C136" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E136" s="5" t="s">
         <v>12</v>
@@ -5602,10 +5584,10 @@
         <v>12</v>
       </c>
       <c r="H136" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I136" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -5613,25 +5595,25 @@
         <v>136</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I137" s="2" t="s">
         <v>16</v>
@@ -5642,25 +5624,25 @@
         <v>137</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="I138" s="2" t="s">
         <v>16</v>
@@ -5671,13 +5653,13 @@
         <v>138</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E139" s="4" t="s">
         <v>18</v>
@@ -5700,13 +5682,13 @@
         <v>139</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E140" s="4" t="s">
         <v>12</v>
@@ -5729,13 +5711,13 @@
         <v>140</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E141" s="4" t="s">
         <v>12</v>
@@ -5758,13 +5740,13 @@
         <v>141</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E142" s="4" t="s">
         <v>12</v>
@@ -5787,13 +5769,13 @@
         <v>142</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E143" s="4" t="s">
         <v>18</v>
@@ -5816,13 +5798,13 @@
         <v>143</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E144" s="4" t="s">
         <v>12</v>
@@ -5845,13 +5827,13 @@
         <v>144</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E145" s="4">
         <v>0</v>
@@ -5874,28 +5856,28 @@
         <v>145</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F146" s="6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -5903,28 +5885,28 @@
         <v>146</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F147" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G147" s="6" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="H147" s="6" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="I147" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -5932,13 +5914,13 @@
         <v>147</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E148" s="4" t="s">
         <v>12</v>
@@ -5961,28 +5943,28 @@
         <v>148</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E149" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F149" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G149" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H149" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="I149" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="G149" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="H149" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="I149" s="6" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -5990,13 +5972,13 @@
         <v>149</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E150" s="4" t="s">
         <v>12</v>
@@ -6019,57 +6001,57 @@
         <v>150</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="I151" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="152" spans="1:9">
-      <c r="A152" s="2">
+      <c r="A152" s="4">
         <v>151</v>
       </c>
-      <c r="B152" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F152" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="G152" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="H152" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="I152" s="2" t="s">
-        <v>16</v>
+      <c r="B152" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="E152" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G152" s="4">
+        <v>0</v>
+      </c>
+      <c r="H152" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I152" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -6077,13 +6059,13 @@
         <v>152</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E153" s="4" t="s">
         <v>18</v>
@@ -6106,28 +6088,28 @@
         <v>153</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="C154" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E154" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="H154" s="5" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="I154" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -6135,28 +6117,28 @@
         <v>154</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F155" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="G155" s="6" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="H155" s="6" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="I155" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -6164,19 +6146,19 @@
         <v>155</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G156" s="4">
         <v>0</v>
@@ -6193,28 +6175,28 @@
         <v>156</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E157" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F157" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G157" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H157" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="I157" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="G157" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="H157" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="I157" s="6" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -6222,13 +6204,13 @@
         <v>157</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E158" s="4" t="s">
         <v>12</v>
@@ -6251,25 +6233,25 @@
         <v>158</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="I159" s="2" t="s">
         <v>16</v>
@@ -6280,28 +6262,28 @@
         <v>159</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F160" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G160" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H160" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="I160" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="G160" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="H160" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="I160" s="6" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -6309,13 +6291,13 @@
         <v>160</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E161" s="4" t="s">
         <v>12</v>
@@ -6338,13 +6320,13 @@
         <v>161</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E162" s="4" t="s">
         <v>12</v>
@@ -6367,28 +6349,28 @@
         <v>162</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E163" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F163" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G163" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H163" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="I163" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="G163" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="H163" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="I163" s="6" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -6396,25 +6378,25 @@
         <v>163</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="I164" s="2" t="s">
         <v>16</v>
@@ -6425,25 +6407,25 @@
         <v>164</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="C165" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="I165" s="3" t="s">
         <v>21</v>
@@ -6454,19 +6436,19 @@
         <v>165</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G166" s="4">
         <v>0</v>
@@ -6483,19 +6465,19 @@
         <v>166</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G167" s="4">
         <v>0</v>
@@ -6512,13 +6494,13 @@
         <v>167</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="C168" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E168" s="5" t="s">
         <v>12</v>
@@ -6530,10 +6512,10 @@
         <v>13</v>
       </c>
       <c r="H168" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="I168" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -6541,13 +6523,13 @@
         <v>168</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E169" s="4" t="s">
         <v>12</v>
@@ -6570,28 +6552,28 @@
         <v>169</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>100</v>
+        <v>290</v>
       </c>
       <c r="F170" s="6" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="H170" s="6" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="I170" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -6599,13 +6581,13 @@
         <v>170</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E171" s="4" t="s">
         <v>12</v>
@@ -6628,25 +6610,25 @@
         <v>171</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I172" s="2" t="s">
         <v>16</v>
@@ -6657,28 +6639,28 @@
         <v>172</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="C173" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E173" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F173" s="6" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="G173" s="6" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H173" s="6" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="I173" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="174" spans="1:9">
@@ -6686,13 +6668,13 @@
         <v>173</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E174" s="4" t="s">
         <v>12</v>
@@ -6715,13 +6697,13 @@
         <v>174</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E175" s="4" t="s">
         <v>12</v>
@@ -6744,13 +6726,13 @@
         <v>175</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E176" s="4" t="s">
         <v>12</v>
@@ -6769,32 +6751,32 @@
       </c>
     </row>
     <row r="177" spans="1:9">
-      <c r="A177" s="2">
+      <c r="A177" s="4">
         <v>176</v>
       </c>
-      <c r="B177" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D177" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E177" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F177" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G177" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="H177" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I177" s="2" t="s">
-        <v>16</v>
+      <c r="B177" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="E177" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F177" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G177" s="4">
+        <v>0</v>
+      </c>
+      <c r="H177" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I177" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="178" spans="1:9">
@@ -6802,13 +6784,13 @@
         <v>177</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E178" s="4" t="s">
         <v>12</v>
@@ -6831,25 +6813,25 @@
         <v>178</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="I179" s="2" t="s">
         <v>16</v>
@@ -6860,13 +6842,13 @@
         <v>179</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E180" s="4" t="s">
         <v>12</v>
@@ -6889,28 +6871,28 @@
         <v>180</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E181" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F181" s="6" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G181" s="6" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H181" s="6" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="I181" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="182" spans="1:9">
@@ -6918,13 +6900,13 @@
         <v>181</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C182" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E182" s="3" t="s">
         <v>18</v>
@@ -6947,28 +6929,28 @@
         <v>182</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E183" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F183" s="6" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="G183" s="6" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="H183" s="6" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="I183" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="184" spans="1:9">
@@ -6976,13 +6958,13 @@
         <v>183</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E184" s="4" t="s">
         <v>12</v>
@@ -7005,28 +6987,28 @@
         <v>184</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E185" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F185" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G185" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H185" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="I185" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="G185" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="H185" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="I185" s="6" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="186" spans="1:9">
@@ -7034,13 +7016,13 @@
         <v>185</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>12</v>
@@ -7063,28 +7045,28 @@
         <v>186</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="C187" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E187" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="G187" s="6" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H187" s="6" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="I187" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="188" spans="1:9">
@@ -7092,28 +7074,28 @@
         <v>187</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>100</v>
+        <v>290</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="I188" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="189" spans="1:9">
@@ -7121,28 +7103,28 @@
         <v>188</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E189" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G189" s="6" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="H189" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I189" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="190" spans="1:9">
@@ -7150,25 +7132,25 @@
         <v>189</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="I190" s="2" t="s">
         <v>16</v>
@@ -7179,25 +7161,25 @@
         <v>190</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I191" s="2" t="s">
         <v>16</v>
@@ -7208,13 +7190,13 @@
         <v>191</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>12</v>
@@ -7237,28 +7219,28 @@
         <v>192</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E193" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="G193" s="6" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="H193" s="6" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="I193" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="194" spans="1:9">
@@ -7266,28 +7248,28 @@
         <v>193</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="C194" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E194" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F194" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G194" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="H194" s="5" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="I194" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="195" spans="1:9">
@@ -7295,25 +7277,25 @@
         <v>194</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C195" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E195" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="H195" s="3" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="I195" s="3" t="s">
         <v>21</v>
@@ -7324,25 +7306,25 @@
         <v>195</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="C196" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E196" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="H196" s="3" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="I196" s="3" t="s">
         <v>21</v>
@@ -7353,13 +7335,13 @@
         <v>196</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="C197" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E197" s="4" t="s">
         <v>12</v>
@@ -7382,13 +7364,13 @@
         <v>197</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C198" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E198" s="5" t="s">
         <v>12</v>
@@ -7400,10 +7382,10 @@
         <v>12</v>
       </c>
       <c r="H198" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I198" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -7411,28 +7393,28 @@
         <v>198</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C199" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E199" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="G199" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H199" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I199" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="200" spans="1:9">
@@ -7440,13 +7422,13 @@
         <v>199</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="C200" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E200" s="4" t="s">
         <v>12</v>
@@ -7469,13 +7451,13 @@
         <v>200</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C201" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E201" s="4" t="s">
         <v>18</v>
@@ -7498,13 +7480,13 @@
         <v>201</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="C202" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D202" s="5" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E202" s="5" t="s">
         <v>12</v>
@@ -7516,10 +7498,10 @@
         <v>12</v>
       </c>
       <c r="H202" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I202" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -7527,13 +7509,13 @@
         <v>202</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="C203" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E203" s="4" t="s">
         <v>12</v>
@@ -7556,13 +7538,13 @@
         <v>203</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="C204" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E204" s="4" t="s">
         <v>12</v>
@@ -7585,13 +7567,13 @@
         <v>204</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="C205" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E205" s="4" t="s">
         <v>12</v>
@@ -7614,13 +7596,13 @@
         <v>205</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="C206" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E206" s="4" t="s">
         <v>18</v>
@@ -7643,28 +7625,28 @@
         <v>206</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="C207" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E207" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F207" s="6" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G207" s="6" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="H207" s="6" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="I207" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -7672,22 +7654,22 @@
         <v>207</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="C208" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E208" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H208" s="3" t="s">
         <v>20</v>
@@ -7701,13 +7683,13 @@
         <v>208</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C209" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E209" s="4" t="s">
         <v>18</v>
@@ -7730,13 +7712,13 @@
         <v>209</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="C210" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E210" s="4" t="s">
         <v>18</v>
@@ -7759,25 +7741,25 @@
         <v>210</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="I211" s="2" t="s">
         <v>16</v>
@@ -7788,19 +7770,19 @@
         <v>211</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="C212" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E212" s="4" t="s">
-        <v>100</v>
+        <v>290</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>100</v>
+        <v>290</v>
       </c>
       <c r="G212" s="4">
         <v>0</v>
@@ -7817,13 +7799,13 @@
         <v>212</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="C213" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E213" s="4" t="s">
         <v>12</v>
@@ -7846,13 +7828,13 @@
         <v>213</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="C214" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E214" s="5" t="s">
         <v>12</v>
@@ -7864,10 +7846,10 @@
         <v>12</v>
       </c>
       <c r="H214" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I214" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="215" spans="1:9">
@@ -7875,28 +7857,28 @@
         <v>214</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="C215" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E215" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F215" s="5" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G215" s="5" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="H215" s="5" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="I215" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="216" spans="1:9">
@@ -7904,19 +7886,19 @@
         <v>215</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C216" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E216" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G216" s="4">
         <v>0</v>
@@ -7933,19 +7915,19 @@
         <v>216</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C217" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E217" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F217" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G217" s="4">
         <v>0</v>
@@ -7962,13 +7944,13 @@
         <v>217</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="C218" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E218" s="5" t="s">
         <v>18</v>
@@ -7980,10 +7962,10 @@
         <v>18</v>
       </c>
       <c r="H218" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I218" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="219" spans="1:9">
@@ -7991,28 +7973,28 @@
         <v>218</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D219" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E219" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F219" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G219" s="6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H219" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I219" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="220" spans="1:9">
@@ -8020,13 +8002,13 @@
         <v>219</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="C220" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E220" s="4" t="s">
         <v>12</v>
@@ -8049,13 +8031,13 @@
         <v>220</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="C221" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E221" s="5" t="s">
         <v>12</v>
@@ -8067,10 +8049,10 @@
         <v>13</v>
       </c>
       <c r="H221" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="I221" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="222" spans="1:9">
@@ -8078,13 +8060,13 @@
         <v>221</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C222" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E222" s="4" t="s">
         <v>12</v>
@@ -8107,13 +8089,13 @@
         <v>222</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="C223" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E223" s="4" t="s">
         <v>12</v>
@@ -8136,13 +8118,13 @@
         <v>223</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C224" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E224" s="5" t="s">
         <v>12</v>
@@ -8154,10 +8136,10 @@
         <v>13</v>
       </c>
       <c r="H224" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="I224" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="225" spans="1:9">
@@ -8165,25 +8147,25 @@
         <v>224</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I225" s="2" t="s">
         <v>16</v>
@@ -8194,25 +8176,25 @@
         <v>225</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>41</v>
+        <v>370</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="I226" s="2" t="s">
         <v>16</v>
@@ -8223,13 +8205,13 @@
         <v>226</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="C227" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E227" s="4" t="s">
         <v>12</v>
@@ -8252,28 +8234,28 @@
         <v>227</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="C228" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D228" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F228" s="6" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="G228" s="6" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="H228" s="6" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="I228" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="229" spans="1:9">
@@ -8281,13 +8263,13 @@
         <v>228</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="C229" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E229" s="4" t="s">
         <v>12</v>
@@ -8310,19 +8292,19 @@
         <v>229</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="C230" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E230" s="4" t="s">
-        <v>100</v>
+        <v>290</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>100</v>
+        <v>290</v>
       </c>
       <c r="G230" s="4">
         <v>0</v>
@@ -8339,19 +8321,19 @@
         <v>230</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C231" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E231" s="4" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="G231" s="4">
         <v>0</v>
@@ -8368,25 +8350,25 @@
         <v>231</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F232" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="I232" s="2" t="s">
         <v>16</v>
@@ -8397,19 +8379,19 @@
         <v>232</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C233" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E233" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G233" s="4">
         <v>0</v>
@@ -8426,25 +8408,25 @@
         <v>233</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="I234" s="2" t="s">
         <v>16</v>
@@ -8455,28 +8437,28 @@
         <v>234</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="C235" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E235" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F235" s="5" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="G235" s="5" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="H235" s="5" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="I235" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="236" spans="1:9">
@@ -8484,28 +8466,28 @@
         <v>235</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C236" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D236" s="6" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="F236" s="6" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G236" s="6" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="H236" s="6" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="I236" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="237" spans="1:9">
@@ -8513,19 +8495,19 @@
         <v>236</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="C237" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E237" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G237" s="4">
         <v>0</v>
@@ -8542,19 +8524,19 @@
         <v>237</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C238" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E238" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G238" s="4">
         <v>0</v>
@@ -8571,13 +8553,13 @@
         <v>238</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C239" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E239" s="4" t="s">
         <v>18</v>
@@ -8600,13 +8582,13 @@
         <v>239</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="C240" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E240" s="6" t="s">
         <v>12</v>
@@ -8618,10 +8600,10 @@
         <v>18</v>
       </c>
       <c r="H240" s="6" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="I240" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="241" spans="1:9">
@@ -8629,28 +8611,28 @@
         <v>240</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="C241" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E241" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F241" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="G241" s="6" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="H241" s="6" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="I241" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/pay.xlsx
+++ b/pay.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81937A87-EFF0-42A0-8C7A-0467D116C60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75773D10-82FD-4753-8978-71A3F0528A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1768" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1767" uniqueCount="390">
   <si>
     <t>#</t>
   </si>
@@ -3473,8 +3473,8 @@
       <c r="F64" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="G64" s="3" t="s">
-        <v>207</v>
+      <c r="G64" s="3">
+        <v>0</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>208</v>

--- a/pay.xlsx
+++ b/pay.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75773D10-82FD-4753-8978-71A3F0528A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F76BD1-C05C-4461-8048-3882B9C554A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1032" windowWidth="21600" windowHeight="11208" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1767" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1766" uniqueCount="390">
   <si>
     <t>#</t>
   </si>
@@ -5271,8 +5271,8 @@
       <c r="F126" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="G126" s="6" t="s">
-        <v>62</v>
+      <c r="G126" s="6">
+        <v>0</v>
       </c>
       <c r="H126" s="6" t="s">
         <v>63</v>

--- a/pay.xlsx
+++ b/pay.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F76BD1-C05C-4461-8048-3882B9C554A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77674738-CCE6-44B9-88FB-4B72961AA98B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1440" yWindow="1032" windowWidth="21600" windowHeight="11208" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1766" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="389">
   <si>
     <t>#</t>
   </si>
@@ -667,9 +667,6 @@
   </si>
   <si>
     <t>2,060,000</t>
-  </si>
-  <si>
-    <t>190,000</t>
   </si>
   <si>
     <t>91.56%</t>
@@ -1835,7 +1832,7 @@
         <v>194</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>10</v>
@@ -1847,13 +1844,13 @@
         <v>18</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>316</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>317</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>21</v>
@@ -1864,25 +1861,25 @@
         <v>195</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>320</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>321</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>21</v>
@@ -1922,7 +1919,7 @@
         <v>196</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>10</v>
@@ -1980,7 +1977,7 @@
         <v>197</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>10</v>
@@ -2038,7 +2035,7 @@
         <v>198</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>10</v>
@@ -2096,7 +2093,7 @@
         <v>199</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>10</v>
@@ -2125,7 +2122,7 @@
         <v>200</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>10</v>
@@ -2154,7 +2151,7 @@
         <v>189</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>10</v>
@@ -2172,7 +2169,7 @@
         <v>163</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>16</v>
@@ -2415,7 +2412,7 @@
         <v>201</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>10</v>
@@ -2531,7 +2528,7 @@
         <v>202</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>10</v>
@@ -2763,7 +2760,7 @@
         <v>203</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>10</v>
@@ -2879,7 +2876,7 @@
         <v>204</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>10</v>
@@ -2995,7 +2992,7 @@
         <v>191</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>10</v>
@@ -3024,7 +3021,7 @@
         <v>188</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>10</v>
@@ -3039,7 +3036,7 @@
         <v>147</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>63</v>
@@ -3154,11 +3151,11 @@
       <c r="F53" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="G53" s="2">
+        <v>0</v>
+      </c>
+      <c r="H53" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>213</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>16</v>
@@ -3198,7 +3195,7 @@
         <v>119</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>10</v>
@@ -3227,7 +3224,7 @@
         <v>120</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>10</v>
@@ -3343,7 +3340,7 @@
         <v>121</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>10</v>
@@ -3358,10 +3355,10 @@
         <v>120</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>217</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>218</v>
       </c>
       <c r="I60" s="6" t="s">
         <v>64</v>
@@ -3430,7 +3427,7 @@
         <v>122</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>10</v>
@@ -3459,7 +3456,7 @@
         <v>123</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>10</v>
@@ -3517,7 +3514,7 @@
         <v>124</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>10</v>
@@ -3546,7 +3543,7 @@
         <v>230</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>10</v>
@@ -3555,10 +3552,10 @@
         <v>169</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G67" s="4">
         <v>0</v>
@@ -3575,7 +3572,7 @@
         <v>184</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>10</v>
@@ -3604,7 +3601,7 @@
         <v>125</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>10</v>
@@ -3633,7 +3630,7 @@
         <v>126</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>10</v>
@@ -3662,7 +3659,7 @@
         <v>205</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>10</v>
@@ -3691,7 +3688,7 @@
         <v>127</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>10</v>
@@ -3749,7 +3746,7 @@
         <v>128</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>10</v>
@@ -3778,7 +3775,7 @@
         <v>129</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>10</v>
@@ -3807,7 +3804,7 @@
         <v>187</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>10</v>
@@ -3816,16 +3813,16 @@
         <v>169</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>119</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>302</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>303</v>
       </c>
       <c r="I76" s="6" t="s">
         <v>64</v>
@@ -3836,7 +3833,7 @@
         <v>234</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>10</v>
@@ -3848,13 +3845,13 @@
         <v>12</v>
       </c>
       <c r="F77" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="G77" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="G77" s="5" t="s">
+      <c r="H77" s="5" t="s">
         <v>377</v>
-      </c>
-      <c r="H77" s="5" t="s">
-        <v>378</v>
       </c>
       <c r="I77" s="5" t="s">
         <v>58</v>
@@ -3865,7 +3862,7 @@
         <v>130</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>10</v>
@@ -3923,7 +3920,7 @@
         <v>240</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>10</v>
@@ -3938,10 +3935,10 @@
         <v>119</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>388</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>389</v>
       </c>
       <c r="I80" s="6" t="s">
         <v>64</v>
@@ -3952,7 +3949,7 @@
         <v>231</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>10</v>
@@ -3967,10 +3964,10 @@
         <v>13</v>
       </c>
       <c r="G81" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="H81" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>370</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>16</v>
@@ -3981,7 +3978,7 @@
         <v>131</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>10</v>
@@ -4010,7 +4007,7 @@
         <v>185</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>10</v>
@@ -4155,7 +4152,7 @@
         <v>132</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>10</v>
@@ -4184,7 +4181,7 @@
         <v>235</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>10</v>
@@ -4193,16 +4190,16 @@
         <v>169</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G89" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="H89" s="6" t="s">
         <v>380</v>
-      </c>
-      <c r="H89" s="6" t="s">
-        <v>381</v>
       </c>
       <c r="I89" s="6" t="s">
         <v>64</v>
@@ -4213,7 +4210,7 @@
         <v>133</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>10</v>
@@ -4242,7 +4239,7 @@
         <v>134</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>10</v>
@@ -4271,7 +4268,7 @@
         <v>206</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>10</v>
@@ -4283,13 +4280,13 @@
         <v>41</v>
       </c>
       <c r="F92" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G92" s="2">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2" t="s">
         <v>333</v>
-      </c>
-      <c r="G92" s="2">
-        <v>0</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>334</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>16</v>
@@ -4329,7 +4326,7 @@
         <v>135</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>10</v>
@@ -4358,7 +4355,7 @@
         <v>207</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>10</v>
@@ -4387,7 +4384,7 @@
         <v>136</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>10</v>
@@ -4445,7 +4442,7 @@
         <v>137</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>10</v>
@@ -4457,13 +4454,13 @@
         <v>18</v>
       </c>
       <c r="F98" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="G98" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="G98" s="2" t="s">
+      <c r="H98" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>16</v>
@@ -4474,7 +4471,7 @@
         <v>138</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>10</v>
@@ -4503,7 +4500,7 @@
         <v>239</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>10</v>
@@ -4521,7 +4518,7 @@
         <v>18</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I100" s="6" t="s">
         <v>64</v>
@@ -4590,7 +4587,7 @@
         <v>139</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>10</v>
@@ -4619,7 +4616,7 @@
         <v>208</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>10</v>
@@ -4677,7 +4674,7 @@
         <v>232</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>10</v>
@@ -4706,7 +4703,7 @@
         <v>140</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>10</v>
@@ -4735,7 +4732,7 @@
         <v>141</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>10</v>
@@ -4764,7 +4761,7 @@
         <v>193</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>10</v>
@@ -4782,7 +4779,7 @@
         <v>162</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I109" s="5" t="s">
         <v>58</v>
@@ -4793,7 +4790,7 @@
         <v>190</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>10</v>
@@ -4822,7 +4819,7 @@
         <v>142</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>10</v>
@@ -4851,7 +4848,7 @@
         <v>209</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>10</v>
@@ -4938,7 +4935,7 @@
         <v>143</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>10</v>
@@ -4967,7 +4964,7 @@
         <v>144</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>10</v>
@@ -4996,7 +4993,7 @@
         <v>145</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>10</v>
@@ -5054,7 +5051,7 @@
         <v>146</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>10</v>
@@ -5069,10 +5066,10 @@
         <v>66</v>
       </c>
       <c r="G119" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H119" s="6" t="s">
         <v>247</v>
-      </c>
-      <c r="H119" s="6" t="s">
-        <v>248</v>
       </c>
       <c r="I119" s="6" t="s">
         <v>64</v>
@@ -5112,7 +5109,7 @@
         <v>233</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>10</v>
@@ -5124,13 +5121,13 @@
         <v>12</v>
       </c>
       <c r="F121" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H121" s="2" t="s">
         <v>373</v>
-      </c>
-      <c r="G121" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>374</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>16</v>
@@ -5170,7 +5167,7 @@
         <v>147</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>10</v>
@@ -5257,7 +5254,7 @@
         <v>148</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>10</v>
@@ -5315,7 +5312,7 @@
         <v>149</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>10</v>
@@ -5344,7 +5341,7 @@
         <v>150</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>10</v>
@@ -5402,7 +5399,7 @@
         <v>151</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>10</v>
@@ -5431,25 +5428,25 @@
         <v>210</v>
       </c>
       <c r="B132" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F132" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="C132" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F132" s="2" t="s">
+      <c r="G132" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="G132" s="2" t="s">
+      <c r="H132" s="2" t="s">
         <v>340</v>
-      </c>
-      <c r="H132" s="2" t="s">
-        <v>341</v>
       </c>
       <c r="I132" s="2" t="s">
         <v>16</v>
@@ -5547,7 +5544,7 @@
         <v>152</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>10</v>
@@ -5576,7 +5573,7 @@
         <v>153</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C137" s="5" t="s">
         <v>10</v>
@@ -5594,7 +5591,7 @@
         <v>162</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I137" s="5" t="s">
         <v>58</v>
@@ -5605,7 +5602,7 @@
         <v>154</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>10</v>
@@ -5617,13 +5614,13 @@
         <v>41</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G138" s="2">
         <v>0</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I138" s="2" t="s">
         <v>16</v>
@@ -5634,7 +5631,7 @@
         <v>211</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>10</v>
@@ -5643,10 +5640,10 @@
         <v>185</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G139" s="4">
         <v>0</v>
@@ -5808,7 +5805,7 @@
         <v>212</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>10</v>
@@ -5866,7 +5863,7 @@
         <v>155</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>10</v>
@@ -5895,7 +5892,7 @@
         <v>156</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>10</v>
@@ -5982,7 +5979,7 @@
         <v>157</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>10</v>
@@ -6011,7 +6008,7 @@
         <v>158</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>10</v>
@@ -6023,13 +6020,13 @@
         <v>43</v>
       </c>
       <c r="F152" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="G152" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="G152" s="2" t="s">
+      <c r="H152" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="H152" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="I152" s="2" t="s">
         <v>16</v>
@@ -6098,7 +6095,7 @@
         <v>159</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>10</v>
@@ -6156,7 +6153,7 @@
         <v>213</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C157" s="5" t="s">
         <v>10</v>
@@ -6475,7 +6472,7 @@
         <v>160</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>10</v>
@@ -6504,7 +6501,7 @@
         <v>161</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>10</v>
@@ -6533,7 +6530,7 @@
         <v>214</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C170" s="5" t="s">
         <v>10</v>
@@ -6551,7 +6548,7 @@
         <v>124</v>
       </c>
       <c r="H170" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="I170" s="5" t="s">
         <v>58</v>
@@ -6562,7 +6559,7 @@
         <v>215</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>10</v>
@@ -6591,7 +6588,7 @@
         <v>216</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>10</v>
@@ -6620,7 +6617,7 @@
         <v>217</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C173" s="5" t="s">
         <v>10</v>
@@ -6678,7 +6675,7 @@
         <v>162</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C175" s="6" t="s">
         <v>10</v>
@@ -6707,7 +6704,7 @@
         <v>163</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>10</v>
@@ -6736,7 +6733,7 @@
         <v>164</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C177" s="3" t="s">
         <v>10</v>
@@ -6748,13 +6745,13 @@
         <v>18</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G177" s="3" t="s">
         <v>62</v>
       </c>
       <c r="H177" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I177" s="3" t="s">
         <v>21</v>
@@ -6765,7 +6762,7 @@
         <v>183</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>10</v>
@@ -6823,7 +6820,7 @@
         <v>165</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>10</v>
@@ -6881,7 +6878,7 @@
         <v>166</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>10</v>
@@ -6968,7 +6965,7 @@
         <v>218</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>10</v>
@@ -7026,7 +7023,7 @@
         <v>167</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C187" s="5" t="s">
         <v>10</v>
@@ -7113,7 +7110,7 @@
         <v>237</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>10</v>
@@ -7171,7 +7168,7 @@
         <v>186</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>10</v>
@@ -7183,13 +7180,13 @@
         <v>41</v>
       </c>
       <c r="F192" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="G192" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="H192" s="6" t="s">
         <v>299</v>
-      </c>
-      <c r="G192" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="H192" s="6" t="s">
-        <v>300</v>
       </c>
       <c r="I192" s="6" t="s">
         <v>64</v>
@@ -7258,7 +7255,7 @@
         <v>168</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C195" s="4" t="s">
         <v>10</v>
@@ -7316,7 +7313,7 @@
         <v>219</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C197" s="4" t="s">
         <v>10</v>
@@ -7345,19 +7342,19 @@
         <v>169</v>
       </c>
       <c r="B198" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D198" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="E198" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="C198" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D198" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E198" s="4" t="s">
-        <v>280</v>
-      </c>
       <c r="F198" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G198" s="4">
         <v>0</v>
@@ -7403,7 +7400,7 @@
         <v>170</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C200" s="4" t="s">
         <v>10</v>
@@ -7432,7 +7429,7 @@
         <v>171</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>10</v>
@@ -7461,7 +7458,7 @@
         <v>172</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C202" s="4" t="s">
         <v>10</v>
@@ -7490,7 +7487,7 @@
         <v>220</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C203" s="5" t="s">
         <v>10</v>
@@ -7548,7 +7545,7 @@
         <v>173</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C205" s="4" t="s">
         <v>10</v>
@@ -7635,7 +7632,7 @@
         <v>174</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C208" s="4" t="s">
         <v>10</v>
@@ -7693,7 +7690,7 @@
         <v>221</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C210" s="4" t="s">
         <v>10</v>
@@ -7751,7 +7748,7 @@
         <v>192</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C212" s="6" t="s">
         <v>10</v>
@@ -7766,10 +7763,10 @@
         <v>186</v>
       </c>
       <c r="G212" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H212" s="6" t="s">
         <v>311</v>
-      </c>
-      <c r="H212" s="6" t="s">
-        <v>312</v>
       </c>
       <c r="I212" s="6" t="s">
         <v>64</v>
@@ -7780,7 +7777,7 @@
         <v>175</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C213" s="4" t="s">
         <v>10</v>
@@ -7867,7 +7864,7 @@
         <v>176</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C216" s="4" t="s">
         <v>10</v>
@@ -7896,7 +7893,7 @@
         <v>177</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C217" s="4" t="s">
         <v>10</v>
@@ -7925,7 +7922,7 @@
         <v>222</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C218" s="4" t="s">
         <v>10</v>
@@ -7954,7 +7951,7 @@
         <v>178</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>10</v>
@@ -7983,7 +7980,7 @@
         <v>223</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C220" s="5" t="s">
         <v>10</v>
@@ -8012,7 +8009,7 @@
         <v>238</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C221" s="4" t="s">
         <v>10</v>
@@ -8128,7 +8125,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>10</v>
@@ -8157,7 +8154,7 @@
         <v>179</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C226" s="4" t="s">
         <v>10</v>
@@ -8215,7 +8212,7 @@
         <v>225</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>10</v>
@@ -8227,13 +8224,13 @@
         <v>18</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I228" s="2" t="s">
         <v>16</v>
@@ -8273,7 +8270,7 @@
         <v>226</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C230" s="4" t="s">
         <v>10</v>
@@ -8331,7 +8328,7 @@
         <v>236</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C232" s="4" t="s">
         <v>10</v>
@@ -8360,25 +8357,25 @@
         <v>227</v>
       </c>
       <c r="B233" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="C233" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D233" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="E233" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F233" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="C233" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D233" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="E233" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F233" s="6" t="s">
+      <c r="G233" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="G233" s="6" t="s">
+      <c r="H233" s="6" t="s">
         <v>362</v>
-      </c>
-      <c r="H233" s="6" t="s">
-        <v>363</v>
       </c>
       <c r="I233" s="6" t="s">
         <v>64</v>
@@ -8389,7 +8386,7 @@
         <v>229</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C234" s="4" t="s">
         <v>10</v>
@@ -8398,10 +8395,10 @@
         <v>185</v>
       </c>
       <c r="E234" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G234" s="4">
         <v>0</v>
@@ -8418,7 +8415,7 @@
         <v>228</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C235" s="4" t="s">
         <v>10</v>
@@ -8534,7 +8531,7 @@
         <v>180</v>
       </c>
       <c r="B239" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C239" s="6" t="s">
         <v>10</v>
@@ -8563,7 +8560,7 @@
         <v>181</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C240" s="3" t="s">
         <v>10</v>
@@ -8592,7 +8589,7 @@
         <v>182</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C241" s="6" t="s">
         <v>10</v>
@@ -8610,7 +8607,7 @@
         <v>206</v>
       </c>
       <c r="H241" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I241" s="6" t="s">
         <v>64</v>

--- a/pay.xlsx
+++ b/pay.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77674738-CCE6-44B9-88FB-4B72961AA98B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{099CF277-FEEF-4FC7-BB3A-BC033F4D0B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1032" windowWidth="21600" windowHeight="11208" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="379">
   <si>
     <t>#</t>
   </si>
@@ -231,105 +231,102 @@
     <t>عباس علي حسين داخل</t>
   </si>
   <si>
+    <t>عبد الرحمن رائد عبد الحميد محمود</t>
+  </si>
+  <si>
+    <t>عبد السلام نوري سعدون حمادي</t>
+  </si>
+  <si>
+    <t>1,300,000</t>
+  </si>
+  <si>
+    <t>950,000</t>
+  </si>
+  <si>
+    <t>57.78%</t>
+  </si>
+  <si>
+    <t>عبد الله عوده مكي جواد</t>
+  </si>
+  <si>
+    <t>علي الرضا سعد عبد محمد</t>
+  </si>
+  <si>
+    <t>علي جمال فتحي لطيف</t>
+  </si>
+  <si>
+    <t>علي حازم جبار جبر</t>
+  </si>
+  <si>
+    <t>1,000,000</t>
+  </si>
+  <si>
     <t>1,250,000</t>
   </si>
   <si>
-    <t>1,000,000</t>
+    <t>علي خالد محمود سلطان</t>
+  </si>
+  <si>
+    <t>علي زاهد جاسم كاظم</t>
+  </si>
+  <si>
+    <t>1,675,000</t>
+  </si>
+  <si>
+    <t>575,000</t>
+  </si>
+  <si>
+    <t>74.44%</t>
+  </si>
+  <si>
+    <t>علي فراس كريم سلمان</t>
+  </si>
+  <si>
+    <t>علي لؤي صادق جعفر</t>
+  </si>
+  <si>
+    <t>علي مؤيد احمد صالح</t>
+  </si>
+  <si>
+    <t>عمر يحيى مراد صالح</t>
+  </si>
+  <si>
+    <t>2,000,000</t>
+  </si>
+  <si>
+    <t>250,000</t>
+  </si>
+  <si>
+    <t>88.89%</t>
+  </si>
+  <si>
+    <t>غسق مهدي جابر حمودي</t>
+  </si>
+  <si>
+    <t>فاطمه حيدر مهدي خضير</t>
+  </si>
+  <si>
+    <t>قاسم كريم محمود عنبر</t>
+  </si>
+  <si>
+    <t>كرار حيدر عبود هادي</t>
+  </si>
+  <si>
+    <t>11.11%</t>
+  </si>
+  <si>
+    <t>كوثر حسن نعمه عيسى</t>
+  </si>
+  <si>
+    <t>562,500</t>
+  </si>
+  <si>
+    <t>محمد المهدي عيسى لطيف يونس</t>
   </si>
   <si>
     <t>55.56%</t>
   </si>
   <si>
-    <t>عبد الرحمن رائد عبد الحميد محمود</t>
-  </si>
-  <si>
-    <t>عبد السلام نوري سعدون حمادي</t>
-  </si>
-  <si>
-    <t>1,300,000</t>
-  </si>
-  <si>
-    <t>950,000</t>
-  </si>
-  <si>
-    <t>57.78%</t>
-  </si>
-  <si>
-    <t>عبد الله عوده مكي جواد</t>
-  </si>
-  <si>
-    <t>علي الرضا سعد عبد محمد</t>
-  </si>
-  <si>
-    <t>2,000,000</t>
-  </si>
-  <si>
-    <t>250,000</t>
-  </si>
-  <si>
-    <t>88.89%</t>
-  </si>
-  <si>
-    <t>علي جمال فتحي لطيف</t>
-  </si>
-  <si>
-    <t>علي حازم جبار جبر</t>
-  </si>
-  <si>
-    <t>علي خالد محمود سلطان</t>
-  </si>
-  <si>
-    <t>علي زاهد جاسم كاظم</t>
-  </si>
-  <si>
-    <t>1,675,000</t>
-  </si>
-  <si>
-    <t>575,000</t>
-  </si>
-  <si>
-    <t>74.44%</t>
-  </si>
-  <si>
-    <t>علي فراس كريم سلمان</t>
-  </si>
-  <si>
-    <t>علي لؤي صادق جعفر</t>
-  </si>
-  <si>
-    <t>علي مؤيد احمد صالح</t>
-  </si>
-  <si>
-    <t>عمر يحيى مراد صالح</t>
-  </si>
-  <si>
-    <t>غسق مهدي جابر حمودي</t>
-  </si>
-  <si>
-    <t>فاطمه حيدر مهدي خضير</t>
-  </si>
-  <si>
-    <t>قاسم كريم محمود عنبر</t>
-  </si>
-  <si>
-    <t>225,000</t>
-  </si>
-  <si>
-    <t>كرار حيدر عبود هادي</t>
-  </si>
-  <si>
-    <t>11.11%</t>
-  </si>
-  <si>
-    <t>كوثر حسن نعمه عيسى</t>
-  </si>
-  <si>
-    <t>562,500</t>
-  </si>
-  <si>
-    <t>محمد المهدي عيسى لطيف يونس</t>
-  </si>
-  <si>
     <t>محمد صادق جعفر مجيد</t>
   </si>
   <si>
@@ -405,6 +402,9 @@
     <t>مهدي علي نبيل صالح</t>
   </si>
   <si>
+    <t>مينا محمد رحيم مبارك</t>
+  </si>
+  <si>
     <t>1,700,000</t>
   </si>
   <si>
@@ -414,9 +414,6 @@
     <t>75.56%</t>
   </si>
   <si>
-    <t>مينا محمد رحيم مبارك</t>
-  </si>
-  <si>
     <t>نبأ غازي عبد الامير حسن</t>
   </si>
   <si>
@@ -519,450 +516,432 @@
     <t>زينب علاء ناصر عبود</t>
   </si>
   <si>
+    <t>طيبة حسين مزيهر سوادي</t>
+  </si>
+  <si>
+    <t>ابراهيم عماد عبدالعزيز حسين</t>
+  </si>
+  <si>
+    <t>فرح مصطفى ياسين عبد الله</t>
+  </si>
+  <si>
+    <t>ايه علي حسن احمد</t>
+  </si>
+  <si>
+    <t>الاولى</t>
+  </si>
+  <si>
+    <t>آمنه اكرم علوان حسين</t>
+  </si>
+  <si>
+    <t>تبارك قصي قاسم احمد</t>
+  </si>
+  <si>
+    <t>روتاج رعد حسين مفتي</t>
+  </si>
+  <si>
+    <t>عبد الله محمد عزيز عاكول</t>
+  </si>
+  <si>
+    <t>قاسم مهدي مجيد مذخور</t>
+  </si>
+  <si>
+    <t>مختار ناظم عبيس عبد الرضا</t>
+  </si>
+  <si>
+    <t>علا داود سلمان عبد</t>
+  </si>
+  <si>
+    <t>1,775,000</t>
+  </si>
+  <si>
+    <t>475,000</t>
+  </si>
+  <si>
+    <t>78.89%</t>
+  </si>
+  <si>
+    <t>مريم مهدي رشيد سعيد</t>
+  </si>
+  <si>
+    <t>ابو الحسن خالد عوده ايدام</t>
+  </si>
+  <si>
+    <t>الثانية</t>
+  </si>
+  <si>
+    <t>90%</t>
+  </si>
+  <si>
+    <t>احمد جاسب حاتم جالس</t>
+  </si>
+  <si>
+    <t>احمد جواد كاظم كاوي</t>
+  </si>
+  <si>
+    <t>احمد عبد الرزاق حبيب محمد</t>
+  </si>
+  <si>
+    <t>اسراء حيدر كريم مطلوب</t>
+  </si>
+  <si>
+    <t>اسيل مهند ناظم جياد</t>
+  </si>
+  <si>
+    <t>اسيل يوسف خضر تايه</t>
+  </si>
+  <si>
+    <t>2,137,500</t>
+  </si>
+  <si>
+    <t>637,500</t>
+  </si>
+  <si>
+    <t>70.18%</t>
+  </si>
+  <si>
+    <t>افنان ناجي سليم عواد</t>
+  </si>
+  <si>
+    <t>الحسين محمد علي صالح</t>
+  </si>
+  <si>
+    <t>امير علي احمد فريدون محمد</t>
+  </si>
+  <si>
+    <t>ايناس عبد السلام حسن عوده</t>
+  </si>
+  <si>
+    <t>أمير فراس زهير حسن</t>
+  </si>
+  <si>
+    <t>بنين حسين علي صباح</t>
+  </si>
+  <si>
+    <t>بنين حميد هاشم شريف</t>
+  </si>
+  <si>
+    <t>جاسم محمد عبد الله عبد</t>
+  </si>
+  <si>
+    <t>جعفر نضال كاظم احمد</t>
+  </si>
+  <si>
+    <t>900,000</t>
+  </si>
+  <si>
+    <t>1,350,000</t>
+  </si>
+  <si>
+    <t>40%</t>
+  </si>
+  <si>
+    <t>جنيد زياد هادي حمد</t>
+  </si>
+  <si>
+    <t>حسن حيدر كاظم فلحي</t>
+  </si>
+  <si>
+    <t>2,060,000</t>
+  </si>
+  <si>
+    <t>190,000</t>
+  </si>
+  <si>
+    <t>91.56%</t>
+  </si>
+  <si>
+    <t>حسن سعدون مزهر شنيور</t>
+  </si>
+  <si>
+    <t>حسن طالب حسين صادق</t>
+  </si>
+  <si>
+    <t>حسين فراس عكار مطير</t>
+  </si>
+  <si>
+    <t>650,000</t>
+  </si>
+  <si>
+    <t>63.89%</t>
+  </si>
+  <si>
+    <t>حليمه مؤيد خيري ذاكر</t>
+  </si>
+  <si>
+    <t>حمزة محمد فالح رخيص</t>
+  </si>
+  <si>
+    <t>حوراء سمير سوادي حسن</t>
+  </si>
+  <si>
+    <t>حيدر حبيب كاظم جواد</t>
+  </si>
+  <si>
+    <t>حيدر صفاء غازي حسن</t>
+  </si>
+  <si>
+    <t>حيدر غسان جليل اسماعيل</t>
+  </si>
+  <si>
+    <t>دعاء علي حسين علي</t>
+  </si>
+  <si>
+    <t>دلال سعدي ناجي داود</t>
+  </si>
+  <si>
+    <t>رحاب نهاد خزعل ابراهيم</t>
+  </si>
+  <si>
+    <t>رقيه حسين عدنان مهدي</t>
+  </si>
+  <si>
+    <t>ريام عز الدين جلوب حمادي</t>
+  </si>
+  <si>
+    <t>ريم حاتم جابر دحيح</t>
+  </si>
+  <si>
+    <t>ريم يونس مزيغر منصور</t>
+  </si>
+  <si>
+    <t>زهراء عبد الخضر كاظم عبيد</t>
+  </si>
+  <si>
+    <t>زهراء فراس جاسم حمادي</t>
+  </si>
+  <si>
+    <t>زيد احمد سالم حسن</t>
+  </si>
+  <si>
+    <t>زينب حسن انور مصطفى</t>
+  </si>
+  <si>
+    <t>سارة احمد جواد كاظم</t>
+  </si>
+  <si>
+    <t>سما صفاء بشان عبيد</t>
+  </si>
+  <si>
+    <t>سما صلاح حسن حسين</t>
+  </si>
+  <si>
+    <t>شهد صالح حميد جواد</t>
+  </si>
+  <si>
+    <t>صادق طاهر جاسم محمد</t>
+  </si>
+  <si>
+    <t>صفا حسين حمود محمد</t>
+  </si>
+  <si>
+    <t>ضحى راضي علي سلوم</t>
+  </si>
+  <si>
+    <t>طارق صلاح ياسر موسى</t>
+  </si>
+  <si>
+    <t>775,000</t>
+  </si>
+  <si>
+    <t>61.73%</t>
+  </si>
+  <si>
+    <t>طيبه ايهاب نافع عيد</t>
+  </si>
+  <si>
+    <t>عباس رائد علي محمد</t>
+  </si>
+  <si>
+    <t>عباس علي حسين علي</t>
+  </si>
+  <si>
+    <t>عبد الجليل خالد عبد الجليل ثعبان</t>
+  </si>
+  <si>
+    <t>عبد الرحمن عباس محمود علي</t>
+  </si>
+  <si>
+    <t>عبد الله محمود اسماعيل جواد</t>
+  </si>
+  <si>
+    <t>عبد الله معمر موفق حمود</t>
+  </si>
+  <si>
+    <t>400,000</t>
+  </si>
+  <si>
     <t>1,850,000</t>
   </si>
   <si>
-    <t>400,000</t>
+    <t>17.78%</t>
+  </si>
+  <si>
+    <t>عبد الوهاب ثامر محمد حسن</t>
+  </si>
+  <si>
+    <t>1,650,000</t>
+  </si>
+  <si>
+    <t>375,000</t>
+  </si>
+  <si>
+    <t>81.48%</t>
+  </si>
+  <si>
+    <t>علي سليمان عبد حسون</t>
+  </si>
+  <si>
+    <t>علي عادل نعمه</t>
+  </si>
+  <si>
+    <t>علي فرحان جاسم محمد</t>
+  </si>
+  <si>
+    <t>علي فلاح حسن فاضل</t>
+  </si>
+  <si>
+    <t>1,560,000</t>
+  </si>
+  <si>
+    <t>240,000</t>
+  </si>
+  <si>
+    <t>86.67%</t>
+  </si>
+  <si>
+    <t>عمار صباح عبد الستار احمد</t>
+  </si>
+  <si>
+    <t>ليلى سالم عبد اللطيف عبد الكريم</t>
+  </si>
+  <si>
+    <t>ماّب عامر عبد القادر فليح</t>
+  </si>
+  <si>
+    <t>محمد باقر نجم متعب</t>
+  </si>
+  <si>
+    <t>محمد جاسم محمد حسون</t>
+  </si>
+  <si>
+    <t>محمد جمال كاظم احمد</t>
+  </si>
+  <si>
+    <t>33.33%</t>
+  </si>
+  <si>
+    <t>محمد صلاح خالد جلاب</t>
+  </si>
+  <si>
+    <t>محمد فراس جبير ابراهيم</t>
+  </si>
+  <si>
+    <t>محمد وليد خالد رشيد</t>
+  </si>
+  <si>
+    <t>مصطفى اياد محمد جاسم</t>
+  </si>
+  <si>
+    <t>مصطفى شاكر محمود محمد</t>
+  </si>
+  <si>
+    <t>1,687,500</t>
+  </si>
+  <si>
+    <t>مصطفى علاء داود موسى</t>
+  </si>
+  <si>
+    <t>مصطفى علي ناصر حسين</t>
+  </si>
+  <si>
+    <t>مصطفى محمد علي طه</t>
+  </si>
+  <si>
+    <t>معتز محمود مطر حسين</t>
+  </si>
+  <si>
+    <t>ملاك عباس عبد علي</t>
+  </si>
+  <si>
+    <t>منقذ عبد الكريم حسين كاظم</t>
+  </si>
+  <si>
+    <t>موده شهاب احمد راكع</t>
+  </si>
+  <si>
+    <t>مؤمن محمد قادر شاواز</t>
+  </si>
+  <si>
+    <t>ميس محمد عصام عبد الوهاب</t>
   </si>
   <si>
     <t>82.22%</t>
   </si>
   <si>
-    <t>طيبة حسين مزيهر سوادي</t>
-  </si>
-  <si>
-    <t>ابراهيم عماد عبدالعزيز حسين</t>
-  </si>
-  <si>
-    <t>فرح مصطفى ياسين عبد الله</t>
-  </si>
-  <si>
-    <t>ايه علي حسن احمد</t>
-  </si>
-  <si>
-    <t>الاولى</t>
-  </si>
-  <si>
-    <t>آمنه اكرم علوان حسين</t>
-  </si>
-  <si>
-    <t>تبارك قصي قاسم احمد</t>
-  </si>
-  <si>
-    <t>روتاج رعد حسين مفتي</t>
-  </si>
-  <si>
-    <t>عبد الله محمد عزيز عاكول</t>
-  </si>
-  <si>
-    <t>قاسم مهدي مجيد مذخور</t>
-  </si>
-  <si>
-    <t>1,530,000</t>
-  </si>
-  <si>
-    <t>720,000</t>
-  </si>
-  <si>
-    <t>68%</t>
-  </si>
-  <si>
-    <t>مختار ناظم عبيس عبد الرضا</t>
-  </si>
-  <si>
-    <t>علا داود سلمان عبد</t>
-  </si>
-  <si>
-    <t>1,775,000</t>
-  </si>
-  <si>
-    <t>475,000</t>
-  </si>
-  <si>
-    <t>78.89%</t>
-  </si>
-  <si>
-    <t>مريم مهدي رشيد سعيد</t>
-  </si>
-  <si>
-    <t>ابو الحسن خالد عوده ايدام</t>
-  </si>
-  <si>
-    <t>الثانية</t>
+    <t>نور ابراهيم خالد محمد</t>
+  </si>
+  <si>
+    <t>يوسف سيف محي جواد</t>
+  </si>
+  <si>
+    <t>يوسف شاكر سالم خلف</t>
+  </si>
+  <si>
+    <t>يوسف نزار هادي ثجيل</t>
+  </si>
+  <si>
+    <t>محمد حذيفة فليح حسن</t>
+  </si>
+  <si>
+    <t>حوراء محمد حسان ناجي</t>
+  </si>
+  <si>
+    <t>رقيه علاء صادق</t>
+  </si>
+  <si>
+    <t>مريم احمد محمود عبيد</t>
+  </si>
+  <si>
+    <t>1,375,000</t>
+  </si>
+  <si>
+    <t>67.9%</t>
+  </si>
+  <si>
+    <t>دينا اسعد حسين محمد</t>
+  </si>
+  <si>
+    <t>587,500</t>
+  </si>
+  <si>
+    <t>65.19%</t>
+  </si>
+  <si>
+    <t>تقى جعفر لعيبي جبار</t>
+  </si>
+  <si>
+    <t>600,000</t>
+  </si>
+  <si>
+    <t>اسياد اياد نايف عبد الحسين</t>
+  </si>
+  <si>
+    <t>80.25%</t>
+  </si>
+  <si>
+    <t>شمس مشتاق طالب علي</t>
+  </si>
+  <si>
+    <t>ترتيل عباس شهاب عبود</t>
+  </si>
+  <si>
+    <t>منتهى وسام عبد حسن حواس</t>
   </si>
   <si>
     <t>1,050,000</t>
   </si>
   <si>
-    <t>53.33%</t>
-  </si>
-  <si>
-    <t>احمد جاسب حاتم جالس</t>
-  </si>
-  <si>
-    <t>احمد جواد كاظم كاوي</t>
-  </si>
-  <si>
-    <t>احمد عبد الرزاق حبيب محمد</t>
-  </si>
-  <si>
-    <t>اسراء حيدر كريم مطلوب</t>
-  </si>
-  <si>
-    <t>اسيل مهند ناظم جياد</t>
-  </si>
-  <si>
-    <t>اسيل يوسف خضر تايه</t>
-  </si>
-  <si>
-    <t>2,137,500</t>
-  </si>
-  <si>
-    <t>637,500</t>
-  </si>
-  <si>
-    <t>70.18%</t>
-  </si>
-  <si>
-    <t>افنان ناجي سليم عواد</t>
-  </si>
-  <si>
-    <t>الحسين محمد علي صالح</t>
-  </si>
-  <si>
-    <t>امير علي احمد فريدون محمد</t>
-  </si>
-  <si>
-    <t>ايناس عبد السلام حسن عوده</t>
-  </si>
-  <si>
-    <t>أمير فراس زهير حسن</t>
-  </si>
-  <si>
-    <t>بنين حسين علي صباح</t>
-  </si>
-  <si>
-    <t>بنين حميد هاشم شريف</t>
-  </si>
-  <si>
-    <t>جاسم محمد عبد الله عبد</t>
-  </si>
-  <si>
-    <t>جعفر نضال كاظم احمد</t>
-  </si>
-  <si>
-    <t>900,000</t>
-  </si>
-  <si>
-    <t>1,350,000</t>
-  </si>
-  <si>
-    <t>40%</t>
-  </si>
-  <si>
-    <t>جنيد زياد هادي حمد</t>
-  </si>
-  <si>
-    <t>حسن حيدر كاظم فلحي</t>
-  </si>
-  <si>
-    <t>2,060,000</t>
-  </si>
-  <si>
-    <t>91.56%</t>
-  </si>
-  <si>
-    <t>حسن سعدون مزهر شنيور</t>
-  </si>
-  <si>
-    <t>حسن طالب حسين صادق</t>
-  </si>
-  <si>
-    <t>حسين فراس عكار مطير</t>
-  </si>
-  <si>
-    <t>650,000</t>
-  </si>
-  <si>
-    <t>63.89%</t>
-  </si>
-  <si>
-    <t>حليمه مؤيد خيري ذاكر</t>
-  </si>
-  <si>
-    <t>حمزة محمد فالح رخيص</t>
-  </si>
-  <si>
-    <t>حوراء سمير سوادي حسن</t>
-  </si>
-  <si>
-    <t>حيدر حبيب كاظم جواد</t>
-  </si>
-  <si>
-    <t>حيدر صفاء غازي حسن</t>
-  </si>
-  <si>
-    <t>حيدر غسان جليل اسماعيل</t>
-  </si>
-  <si>
-    <t>دعاء علي حسين علي</t>
-  </si>
-  <si>
-    <t>دلال سعدي ناجي داود</t>
-  </si>
-  <si>
-    <t>رحاب نهاد خزعل ابراهيم</t>
-  </si>
-  <si>
-    <t>رقيه حسين عدنان مهدي</t>
-  </si>
-  <si>
-    <t>ريام عز الدين جلوب حمادي</t>
-  </si>
-  <si>
-    <t>ريم حاتم جابر دحيح</t>
-  </si>
-  <si>
-    <t>ريم يونس مزيغر منصور</t>
-  </si>
-  <si>
-    <t>زهراء عبد الخضر كاظم عبيد</t>
-  </si>
-  <si>
-    <t>زهراء فراس جاسم حمادي</t>
-  </si>
-  <si>
-    <t>زيد احمد سالم حسن</t>
-  </si>
-  <si>
-    <t>1,110,000</t>
-  </si>
-  <si>
-    <t>15,000</t>
-  </si>
-  <si>
-    <t>98.67%</t>
-  </si>
-  <si>
-    <t>زينب حسن انور مصطفى</t>
-  </si>
-  <si>
-    <t>سارة احمد جواد كاظم</t>
-  </si>
-  <si>
-    <t>سما صفاء بشان عبيد</t>
-  </si>
-  <si>
-    <t>سما صلاح حسن حسين</t>
-  </si>
-  <si>
-    <t>شهد صالح حميد جواد</t>
-  </si>
-  <si>
-    <t>صادق طاهر جاسم محمد</t>
-  </si>
-  <si>
-    <t>صفا حسين حمود محمد</t>
-  </si>
-  <si>
-    <t>ضحى راضي علي سلوم</t>
-  </si>
-  <si>
-    <t>طارق صلاح ياسر موسى</t>
-  </si>
-  <si>
-    <t>775,000</t>
-  </si>
-  <si>
-    <t>61.73%</t>
-  </si>
-  <si>
-    <t>طيبه ايهاب نافع عيد</t>
-  </si>
-  <si>
-    <t>عباس رائد علي محمد</t>
-  </si>
-  <si>
-    <t>عباس علي حسين علي</t>
-  </si>
-  <si>
-    <t>عبد الجليل خالد عبد الجليل ثعبان</t>
-  </si>
-  <si>
-    <t>عبد الرحمن عباس محمود علي</t>
-  </si>
-  <si>
-    <t>عبد الله محمود اسماعيل جواد</t>
-  </si>
-  <si>
-    <t>عبد الله معمر موفق حمود</t>
-  </si>
-  <si>
-    <t>17.78%</t>
-  </si>
-  <si>
-    <t>عبد الوهاب ثامر محمد حسن</t>
-  </si>
-  <si>
-    <t>1,650,000</t>
-  </si>
-  <si>
-    <t>375,000</t>
-  </si>
-  <si>
-    <t>81.48%</t>
-  </si>
-  <si>
-    <t>علي سليمان عبد حسون</t>
-  </si>
-  <si>
-    <t>علي عادل نعمه</t>
-  </si>
-  <si>
-    <t>علي فرحان جاسم محمد</t>
-  </si>
-  <si>
-    <t>علي فلاح حسن فاضل</t>
-  </si>
-  <si>
-    <t>1,560,000</t>
-  </si>
-  <si>
-    <t>240,000</t>
-  </si>
-  <si>
-    <t>86.67%</t>
-  </si>
-  <si>
-    <t>عمار صباح عبد الستار احمد</t>
-  </si>
-  <si>
-    <t>ليلى سالم عبد اللطيف عبد الكريم</t>
-  </si>
-  <si>
-    <t>ماّب عامر عبد القادر فليح</t>
-  </si>
-  <si>
-    <t>محمد باقر نجم متعب</t>
-  </si>
-  <si>
-    <t>محمد جاسم محمد حسون</t>
-  </si>
-  <si>
-    <t>محمد جمال كاظم احمد</t>
-  </si>
-  <si>
-    <t>33.33%</t>
-  </si>
-  <si>
-    <t>محمد صلاح خالد جلاب</t>
-  </si>
-  <si>
-    <t>محمد فراس جبير ابراهيم</t>
-  </si>
-  <si>
-    <t>محمد وليد خالد رشيد</t>
-  </si>
-  <si>
-    <t>مصطفى اياد محمد جاسم</t>
-  </si>
-  <si>
-    <t>مصطفى شاكر محمود محمد</t>
-  </si>
-  <si>
-    <t>1,687,500</t>
-  </si>
-  <si>
-    <t>مصطفى علاء داود موسى</t>
-  </si>
-  <si>
-    <t>مصطفى علي ناصر حسين</t>
-  </si>
-  <si>
-    <t>مصطفى محمد علي طه</t>
-  </si>
-  <si>
-    <t>معتز محمود مطر حسين</t>
-  </si>
-  <si>
-    <t>ملاك عباس عبد علي</t>
-  </si>
-  <si>
-    <t>منقذ عبد الكريم حسين كاظم</t>
-  </si>
-  <si>
-    <t>موده شهاب احمد راكع</t>
-  </si>
-  <si>
-    <t>مؤمن محمد قادر شاواز</t>
-  </si>
-  <si>
-    <t>ميس محمد عصام عبد الوهاب</t>
-  </si>
-  <si>
-    <t>نور ابراهيم خالد محمد</t>
-  </si>
-  <si>
-    <t>يوسف سيف محي جواد</t>
-  </si>
-  <si>
-    <t>يوسف شاكر سالم خلف</t>
-  </si>
-  <si>
-    <t>يوسف نزار هادي ثجيل</t>
-  </si>
-  <si>
-    <t>60%</t>
-  </si>
-  <si>
-    <t>محمد حذيفة فليح حسن</t>
-  </si>
-  <si>
-    <t>حوراء محمد حسان ناجي</t>
-  </si>
-  <si>
-    <t>رقيه علاء صادق</t>
-  </si>
-  <si>
-    <t>مريم احمد محمود عبيد</t>
-  </si>
-  <si>
-    <t>1,375,000</t>
-  </si>
-  <si>
-    <t>67.9%</t>
-  </si>
-  <si>
-    <t>دينا اسعد حسين محمد</t>
-  </si>
-  <si>
-    <t>587,500</t>
-  </si>
-  <si>
-    <t>65.19%</t>
-  </si>
-  <si>
-    <t>تقى جعفر لعيبي جبار</t>
-  </si>
-  <si>
-    <t>600,000</t>
-  </si>
-  <si>
-    <t>اسياد اياد نايف عبد الحسين</t>
-  </si>
-  <si>
-    <t>80.25%</t>
-  </si>
-  <si>
-    <t>شمس مشتاق طالب علي</t>
-  </si>
-  <si>
-    <t>ترتيل عباس شهاب عبود</t>
-  </si>
-  <si>
-    <t>منتهى وسام عبد حسن حواس</t>
-  </si>
-  <si>
     <t>975,000</t>
   </si>
   <si>
@@ -1032,6 +1011,9 @@
     <t>1,940,000</t>
   </si>
   <si>
+    <t>85,000</t>
+  </si>
+  <si>
     <t>95.8%</t>
   </si>
   <si>
@@ -1047,15 +1029,6 @@
     <t>عبد الرزاق حسين فوزي اسماعيل</t>
   </si>
   <si>
-    <t>2,170,000</t>
-  </si>
-  <si>
-    <t>80,000</t>
-  </si>
-  <si>
-    <t>96.44%</t>
-  </si>
-  <si>
     <t>عزالدين عبدالكريم عفتان ثامر</t>
   </si>
   <si>
@@ -1102,9 +1075,6 @@
   </si>
   <si>
     <t>نور صباح صالح نصرالله</t>
-  </si>
-  <si>
-    <t>150,000</t>
   </si>
   <si>
     <t>هبه عبد الكريم جبار نفل</t>
@@ -1687,7 +1657,7 @@
         <v>90</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>10</v>
@@ -1712,32 +1682,32 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
+      <c r="A4" s="2">
         <v>101</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>64</v>
+      <c r="B4" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -1745,13 +1715,13 @@
         <v>102</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>12</v>
@@ -1803,13 +1773,13 @@
         <v>103</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>12</v>
@@ -1832,25 +1802,25 @@
         <v>194</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>21</v>
@@ -1861,25 +1831,25 @@
         <v>195</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>21</v>
@@ -1890,13 +1860,13 @@
         <v>104</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>12</v>
@@ -1919,13 +1889,13 @@
         <v>196</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>12</v>
@@ -1977,13 +1947,13 @@
         <v>197</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>12</v>
@@ -2035,25 +2005,25 @@
         <v>198</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>43</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>58</v>
@@ -2064,13 +2034,13 @@
         <v>105</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>12</v>
@@ -2093,13 +2063,13 @@
         <v>199</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>12</v>
@@ -2122,13 +2092,13 @@
         <v>200</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>18</v>
@@ -2151,25 +2121,25 @@
         <v>189</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>163</v>
+        <v>245</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>16</v>
@@ -2180,13 +2150,13 @@
         <v>106</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>12</v>
@@ -2209,25 +2179,25 @@
         <v>107</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>61</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>64</v>
@@ -2238,13 +2208,13 @@
         <v>108</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>12</v>
@@ -2267,13 +2237,13 @@
         <v>109</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>41</v>
@@ -2321,32 +2291,32 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="6">
+      <c r="A25" s="4">
         <v>110</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>64</v>
+      <c r="B25" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G25" s="4">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
@@ -2412,13 +2382,13 @@
         <v>201</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>12</v>
@@ -2470,13 +2440,13 @@
         <v>111</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>12</v>
@@ -2528,13 +2498,13 @@
         <v>202</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>12</v>
@@ -2557,13 +2527,13 @@
         <v>92</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>12</v>
@@ -2673,13 +2643,13 @@
         <v>112</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>12</v>
@@ -2702,7 +2672,7 @@
         <v>93</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>10</v>
@@ -2760,13 +2730,13 @@
         <v>203</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>12</v>
@@ -2818,13 +2788,13 @@
         <v>113</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>12</v>
@@ -2847,13 +2817,13 @@
         <v>114</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>12</v>
@@ -2876,13 +2846,13 @@
         <v>204</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>12</v>
@@ -2905,7 +2875,7 @@
         <v>77</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>10</v>
@@ -2934,7 +2904,7 @@
         <v>94</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>10</v>
@@ -2992,13 +2962,13 @@
         <v>191</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>12</v>
@@ -3021,22 +2991,22 @@
         <v>188</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>63</v>
@@ -3050,13 +3020,13 @@
         <v>115</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>12</v>
@@ -3079,25 +3049,25 @@
         <v>116</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>21</v>
@@ -3108,13 +3078,13 @@
         <v>117</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>12</v>
@@ -3137,25 +3107,25 @@
         <v>118</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="G53" s="2">
-        <v>0</v>
+        <v>203</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>204</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>16</v>
@@ -3195,13 +3165,13 @@
         <v>119</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>12</v>
@@ -3224,13 +3194,13 @@
         <v>120</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>12</v>
@@ -3340,25 +3310,25 @@
         <v>121</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="I60" s="6" t="s">
         <v>64</v>
@@ -3398,7 +3368,7 @@
         <v>83</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>10</v>
@@ -3427,25 +3397,25 @@
         <v>122</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="I63" s="6" t="s">
         <v>64</v>
@@ -3456,25 +3426,25 @@
         <v>123</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G64" s="3">
-        <v>0</v>
+        <v>198</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>199</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>21</v>
@@ -3510,32 +3480,32 @@
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" s="2">
+      <c r="A66" s="4">
         <v>124</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>16</v>
+      <c r="B66" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G66" s="4">
+        <v>0</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
@@ -3543,19 +3513,19 @@
         <v>230</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="G67" s="4">
         <v>0</v>
@@ -3572,13 +3542,13 @@
         <v>184</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>12</v>
@@ -3601,13 +3571,13 @@
         <v>125</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>12</v>
@@ -3630,13 +3600,13 @@
         <v>126</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E70" s="5" t="s">
         <v>12</v>
@@ -3659,13 +3629,13 @@
         <v>205</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>18</v>
@@ -3688,13 +3658,13 @@
         <v>127</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>12</v>
@@ -3746,13 +3716,13 @@
         <v>128</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>41</v>
@@ -3775,13 +3745,13 @@
         <v>129</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>12</v>
@@ -3804,25 +3774,25 @@
         <v>187</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="I76" s="6" t="s">
         <v>64</v>
@@ -3833,25 +3803,25 @@
         <v>234</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E77" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="I77" s="5" t="s">
         <v>58</v>
@@ -3862,13 +3832,13 @@
         <v>130</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>12</v>
@@ -3891,7 +3861,7 @@
         <v>84</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>10</v>
@@ -3920,25 +3890,25 @@
         <v>240</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>41</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="I80" s="6" t="s">
         <v>64</v>
@@ -3949,13 +3919,13 @@
         <v>231</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>43</v>
@@ -3964,10 +3934,10 @@
         <v>13</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>16</v>
@@ -3978,13 +3948,13 @@
         <v>131</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E82" s="5" t="s">
         <v>12</v>
@@ -4007,13 +3977,13 @@
         <v>185</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>12</v>
@@ -4065,7 +4035,7 @@
         <v>95</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>10</v>
@@ -4152,19 +4122,19 @@
         <v>132</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G88" s="4">
         <v>0</v>
@@ -4181,25 +4151,25 @@
         <v>235</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="G89" s="6" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="I89" s="6" t="s">
         <v>64</v>
@@ -4210,13 +4180,13 @@
         <v>133</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>41</v>
@@ -4239,13 +4209,13 @@
         <v>134</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>12</v>
@@ -4268,25 +4238,25 @@
         <v>206</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="G92" s="2">
-        <v>0</v>
+        <v>325</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>326</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>16</v>
@@ -4326,13 +4296,13 @@
         <v>135</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E94" s="5" t="s">
         <v>12</v>
@@ -4355,13 +4325,13 @@
         <v>207</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>18</v>
@@ -4384,13 +4354,13 @@
         <v>136</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>12</v>
@@ -4438,32 +4408,32 @@
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A98" s="2">
+      <c r="A98" s="4">
         <v>137</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E98" s="2" t="s">
+      <c r="B98" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E98" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F98" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="I98" s="2" t="s">
-        <v>16</v>
+      <c r="F98" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G98" s="4">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I98" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
@@ -4471,13 +4441,13 @@
         <v>138</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>18</v>
@@ -4500,13 +4470,13 @@
         <v>239</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>12</v>
@@ -4518,39 +4488,39 @@
         <v>18</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="I100" s="6" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A101" s="2">
+      <c r="A101" s="4">
         <v>88</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="I101" s="2" t="s">
-        <v>16</v>
+      <c r="B101" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G101" s="4">
+        <v>0</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I101" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
@@ -4587,13 +4557,13 @@
         <v>139</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E103" s="4" t="s">
         <v>12</v>
@@ -4616,13 +4586,13 @@
         <v>208</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E104" s="4" t="s">
         <v>18</v>
@@ -4674,13 +4644,13 @@
         <v>232</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>43</v>
@@ -4703,13 +4673,13 @@
         <v>140</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>12</v>
@@ -4732,13 +4702,13 @@
         <v>141</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>12</v>
@@ -4761,25 +4731,25 @@
         <v>193</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>163</v>
+        <v>245</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>162</v>
+        <v>246</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="I109" s="5" t="s">
         <v>58</v>
@@ -4790,25 +4760,25 @@
         <v>190</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I110" s="2" t="s">
         <v>16</v>
@@ -4819,13 +4789,13 @@
         <v>142</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E111" s="4" t="s">
         <v>18</v>
@@ -4848,13 +4818,13 @@
         <v>209</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E112" s="4" t="s">
         <v>18</v>
@@ -4935,13 +4905,13 @@
         <v>143</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E115" s="4" t="s">
         <v>12</v>
@@ -4964,13 +4934,13 @@
         <v>144</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E116" s="4">
         <v>0</v>
@@ -4989,32 +4959,32 @@
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A117" s="6">
+      <c r="A117" s="2">
         <v>145</v>
       </c>
-      <c r="B117" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="C117" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D117" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="E117" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F117" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G117" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H117" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="I117" s="6" t="s">
-        <v>64</v>
+      <c r="B117" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I117" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
@@ -5022,7 +4992,7 @@
         <v>85</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>10</v>
@@ -5051,25 +5021,25 @@
         <v>146</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E119" s="6" t="s">
         <v>41</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G119" s="6" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="I119" s="6" t="s">
         <v>64</v>
@@ -5109,25 +5079,25 @@
         <v>233</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>16</v>
@@ -5138,7 +5108,7 @@
         <v>89</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>10</v>
@@ -5167,13 +5137,13 @@
         <v>147</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E123" s="4" t="s">
         <v>12</v>
@@ -5254,13 +5224,13 @@
         <v>148</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>12</v>
@@ -5268,8 +5238,8 @@
       <c r="F126" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="G126" s="6">
-        <v>0</v>
+      <c r="G126" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="H126" s="6" t="s">
         <v>63</v>
@@ -5279,32 +5249,32 @@
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A127" s="6">
+      <c r="A127" s="4">
         <v>35</v>
       </c>
-      <c r="B127" s="6" t="s">
+      <c r="B127" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C127" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D127" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E127" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F127" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="G127" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="H127" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="I127" s="6" t="s">
-        <v>64</v>
+      <c r="C127" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E127" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G127" s="4">
+        <v>0</v>
+      </c>
+      <c r="H127" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I127" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
@@ -5312,13 +5282,13 @@
         <v>149</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E128" s="4" t="s">
         <v>12</v>
@@ -5341,13 +5311,13 @@
         <v>150</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E129" s="4" t="s">
         <v>12</v>
@@ -5370,7 +5340,7 @@
         <v>36</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C130" s="5" t="s">
         <v>10</v>
@@ -5399,13 +5369,13 @@
         <v>151</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E131" s="4" t="s">
         <v>12</v>
@@ -5424,32 +5394,32 @@
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A132" s="2">
+      <c r="A132" s="4">
         <v>210</v>
       </c>
-      <c r="B132" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F132" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="G132" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="H132" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="I132" s="2" t="s">
-        <v>16</v>
+      <c r="B132" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E132" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G132" s="4">
+        <v>0</v>
+      </c>
+      <c r="H132" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I132" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
@@ -5457,25 +5427,25 @@
         <v>37</v>
       </c>
       <c r="B133" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E133" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F133" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="G133" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H133" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="C133" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D133" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E133" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F133" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G133" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H133" s="6" t="s">
-        <v>73</v>
       </c>
       <c r="I133" s="6" t="s">
         <v>64</v>
@@ -5486,7 +5456,7 @@
         <v>38</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>10</v>
@@ -5515,7 +5485,7 @@
         <v>96</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>10</v>
@@ -5544,13 +5514,13 @@
         <v>152</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E136" s="4" t="s">
         <v>18</v>
@@ -5573,25 +5543,25 @@
         <v>153</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="C137" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>163</v>
+        <v>245</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>162</v>
+        <v>246</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="I137" s="5" t="s">
         <v>58</v>
@@ -5602,25 +5572,25 @@
         <v>154</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="G138" s="2">
-        <v>0</v>
+        <v>249</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>250</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="I138" s="2" t="s">
         <v>16</v>
@@ -5631,19 +5601,19 @@
         <v>211</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G139" s="4">
         <v>0</v>
@@ -5660,7 +5630,7 @@
         <v>99</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>10</v>
@@ -5672,45 +5642,45 @@
         <v>12</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="I140" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A141" s="2">
+      <c r="A141" s="4">
         <v>39</v>
       </c>
-      <c r="B141" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F141" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G141" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H141" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I141" s="2" t="s">
-        <v>16</v>
+      <c r="B141" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E141" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G141" s="4">
+        <v>0</v>
+      </c>
+      <c r="H141" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I141" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
@@ -5718,7 +5688,7 @@
         <v>40</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>10</v>
@@ -5747,7 +5717,7 @@
         <v>41</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C143" s="3" t="s">
         <v>10</v>
@@ -5759,10 +5729,10 @@
         <v>12</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="H143" s="3" t="s">
         <v>20</v>
@@ -5776,7 +5746,7 @@
         <v>42</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>10</v>
@@ -5805,13 +5775,13 @@
         <v>212</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E145" s="4" t="s">
         <v>12</v>
@@ -5834,7 +5804,7 @@
         <v>43</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>10</v>
@@ -5846,13 +5816,13 @@
         <v>12</v>
       </c>
       <c r="F146" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I146" s="6" t="s">
         <v>64</v>
@@ -5863,13 +5833,13 @@
         <v>155</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E147" s="4" t="s">
         <v>41</v>
@@ -5888,32 +5858,32 @@
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A148" s="6">
+      <c r="A148" s="2">
         <v>156</v>
       </c>
-      <c r="B148" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="C148" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D148" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="E148" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F148" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="G148" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="I148" s="6" t="s">
-        <v>64</v>
+      <c r="B148" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I148" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.3">
@@ -5921,25 +5891,25 @@
         <v>78</v>
       </c>
       <c r="B149" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E149" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F149" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="C149" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D149" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E149" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F149" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="G149" s="6" t="s">
         <v>19</v>
       </c>
       <c r="H149" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I149" s="6" t="s">
         <v>64</v>
@@ -5950,7 +5920,7 @@
         <v>44</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C150" s="5" t="s">
         <v>10</v>
@@ -5979,13 +5949,13 @@
         <v>157</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E151" s="4" t="s">
         <v>12</v>
@@ -6008,25 +5978,25 @@
         <v>158</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>43</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="I152" s="2" t="s">
         <v>16</v>
@@ -6037,7 +6007,7 @@
         <v>45</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>10</v>
@@ -6066,7 +6036,7 @@
         <v>46</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>10</v>
@@ -6095,13 +6065,13 @@
         <v>159</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E155" s="6" t="s">
         <v>12</v>
@@ -6124,7 +6094,7 @@
         <v>47</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>10</v>
@@ -6136,13 +6106,13 @@
         <v>12</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I156" s="2" t="s">
         <v>16</v>
@@ -6153,13 +6123,13 @@
         <v>213</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="C157" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E157" s="5" t="s">
         <v>12</v>
@@ -6182,7 +6152,7 @@
         <v>82</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C158" s="5" t="s">
         <v>10</v>
@@ -6194,13 +6164,13 @@
         <v>12</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G158" s="5" t="s">
         <v>43</v>
       </c>
       <c r="H158" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I158" s="5" t="s">
         <v>58</v>
@@ -6211,7 +6181,7 @@
         <v>48</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>10</v>
@@ -6240,7 +6210,7 @@
         <v>49</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>10</v>
@@ -6269,7 +6239,7 @@
         <v>81</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>10</v>
@@ -6298,7 +6268,7 @@
         <v>91</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>10</v>
@@ -6323,61 +6293,61 @@
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A163" s="2">
+      <c r="A163" s="4">
         <v>50</v>
       </c>
-      <c r="B163" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D163" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E163" s="2" t="s">
+      <c r="B163" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E163" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F163" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G163" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H163" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I163" s="2" t="s">
-        <v>16</v>
+      <c r="F163" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G163" s="4">
+        <v>0</v>
+      </c>
+      <c r="H163" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I163" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A164" s="6">
+      <c r="A164" s="4">
         <v>97</v>
       </c>
-      <c r="B164" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="C164" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D164" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E164" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F164" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="G164" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="H164" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="I164" s="6" t="s">
-        <v>64</v>
+      <c r="B164" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E164" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F164" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G164" s="4">
+        <v>0</v>
+      </c>
+      <c r="H164" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I164" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.3">
@@ -6385,25 +6355,25 @@
         <v>79</v>
       </c>
       <c r="B165" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D165" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E165" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F165" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C165" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D165" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E165" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F165" s="6" t="s">
+      <c r="G165" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="G165" s="6" t="s">
+      <c r="H165" s="6" t="s">
         <v>144</v>
-      </c>
-      <c r="H165" s="6" t="s">
-        <v>145</v>
       </c>
       <c r="I165" s="6" t="s">
         <v>64</v>
@@ -6414,7 +6384,7 @@
         <v>51</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C166" s="5" t="s">
         <v>10</v>
@@ -6426,13 +6396,13 @@
         <v>12</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G166" s="5" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="H166" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I166" s="5" t="s">
         <v>58</v>
@@ -6443,7 +6413,7 @@
         <v>52</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>10</v>
@@ -6452,10 +6422,10 @@
         <v>11</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G167" s="4">
         <v>0</v>
@@ -6472,13 +6442,13 @@
         <v>160</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E168" s="4" t="s">
         <v>12</v>
@@ -6501,13 +6471,13 @@
         <v>161</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E169" s="4" t="s">
         <v>12</v>
@@ -6530,13 +6500,13 @@
         <v>214</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="C170" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E170" s="5" t="s">
         <v>12</v>
@@ -6548,7 +6518,7 @@
         <v>124</v>
       </c>
       <c r="H170" s="5" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="I170" s="5" t="s">
         <v>58</v>
@@ -6559,13 +6529,13 @@
         <v>215</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E171" s="4" t="s">
         <v>43</v>
@@ -6588,13 +6558,13 @@
         <v>216</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E172" s="4" t="s">
         <v>41</v>
@@ -6617,13 +6587,13 @@
         <v>217</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="C173" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E173" s="5" t="s">
         <v>18</v>
@@ -6646,7 +6616,7 @@
         <v>53</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>10</v>
@@ -6658,45 +6628,45 @@
         <v>12</v>
       </c>
       <c r="F174" s="6" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G174" s="6" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="H174" s="6" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="I174" s="6" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A175" s="6">
+      <c r="A175" s="4">
         <v>162</v>
       </c>
-      <c r="B175" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="C175" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D175" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="E175" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F175" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="G175" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H175" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="I175" s="6" t="s">
-        <v>64</v>
+      <c r="B175" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E175" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F175" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G175" s="4">
+        <v>0</v>
+      </c>
+      <c r="H175" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I175" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.3">
@@ -6704,13 +6674,13 @@
         <v>163</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>12</v>
@@ -6719,10 +6689,10 @@
         <v>43</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I176" s="2" t="s">
         <v>16</v>
@@ -6733,25 +6703,25 @@
         <v>164</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="C177" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E177" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="G177" s="3" t="s">
         <v>62</v>
       </c>
       <c r="H177" s="3" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="I177" s="3" t="s">
         <v>21</v>
@@ -6762,13 +6732,13 @@
         <v>183</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E178" s="4" t="s">
         <v>12</v>
@@ -6791,7 +6761,7 @@
         <v>54</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C179" s="5" t="s">
         <v>10</v>
@@ -6803,13 +6773,13 @@
         <v>41</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G179" s="5" t="s">
         <v>27</v>
       </c>
       <c r="H179" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I179" s="5" t="s">
         <v>58</v>
@@ -6820,13 +6790,13 @@
         <v>165</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E180" s="4" t="s">
         <v>41</v>
@@ -6849,7 +6819,7 @@
         <v>55</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>10</v>
@@ -6861,13 +6831,13 @@
         <v>12</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I181" s="2" t="s">
         <v>16</v>
@@ -6878,13 +6848,13 @@
         <v>166</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E182" s="4" t="s">
         <v>41</v>
@@ -6907,7 +6877,7 @@
         <v>56</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C183" s="3" t="s">
         <v>10</v>
@@ -6919,10 +6889,10 @@
         <v>12</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="H183" s="3" t="s">
         <v>20</v>
@@ -6936,25 +6906,25 @@
         <v>57</v>
       </c>
       <c r="B184" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D184" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E184" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F184" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C184" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D184" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E184" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F184" s="6" t="s">
+      <c r="G184" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="G184" s="6" t="s">
+      <c r="H184" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="H184" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="I184" s="6" t="s">
         <v>64</v>
@@ -6965,25 +6935,25 @@
         <v>218</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E185" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F185" s="6" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G185" s="6" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="H185" s="6" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="I185" s="6" t="s">
         <v>64</v>
@@ -6994,7 +6964,7 @@
         <v>58</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>10</v>
@@ -7019,32 +6989,32 @@
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A187" s="5">
+      <c r="A187" s="6">
         <v>167</v>
       </c>
-      <c r="B187" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="C187" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D187" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="E187" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F187" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G187" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H187" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="I187" s="5" t="s">
-        <v>58</v>
+      <c r="B187" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C187" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D187" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="E187" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F187" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G187" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H187" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="I187" s="6" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.3">
@@ -7052,7 +7022,7 @@
         <v>98</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>10</v>
@@ -7081,7 +7051,7 @@
         <v>80</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>10</v>
@@ -7093,13 +7063,13 @@
         <v>41</v>
       </c>
       <c r="F189" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="G189" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="G189" s="6" t="s">
+      <c r="H189" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="H189" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="I189" s="6" t="s">
         <v>64</v>
@@ -7110,13 +7080,13 @@
         <v>237</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E190" s="4" t="s">
         <v>43</v>
@@ -7139,7 +7109,7 @@
         <v>59</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>10</v>
@@ -7168,25 +7138,25 @@
         <v>186</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>41</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="G192" s="6" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="I192" s="6" t="s">
         <v>64</v>
@@ -7197,7 +7167,7 @@
         <v>76</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>10</v>
@@ -7226,7 +7196,7 @@
         <v>100</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C194" s="4" t="s">
         <v>10</v>
@@ -7255,13 +7225,13 @@
         <v>168</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="C195" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E195" s="4" t="s">
         <v>12</v>
@@ -7284,7 +7254,7 @@
         <v>60</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C196" s="4" t="s">
         <v>10</v>
@@ -7313,13 +7283,13 @@
         <v>219</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="C197" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E197" s="4" t="s">
         <v>12</v>
@@ -7342,19 +7312,19 @@
         <v>169</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="C198" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E198" s="4" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G198" s="4">
         <v>0</v>
@@ -7371,7 +7341,7 @@
         <v>61</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C199" s="4" t="s">
         <v>10</v>
@@ -7400,13 +7370,13 @@
         <v>170</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="C200" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E200" s="4" t="s">
         <v>12</v>
@@ -7429,13 +7399,13 @@
         <v>171</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>12</v>
@@ -7458,13 +7428,13 @@
         <v>172</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="C202" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E202" s="4" t="s">
         <v>18</v>
@@ -7487,13 +7457,13 @@
         <v>220</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="C203" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E203" s="5" t="s">
         <v>12</v>
@@ -7505,7 +7475,7 @@
         <v>13</v>
       </c>
       <c r="H203" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I203" s="5" t="s">
         <v>58</v>
@@ -7516,7 +7486,7 @@
         <v>62</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>10</v>
@@ -7531,10 +7501,10 @@
         <v>43</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I204" s="2" t="s">
         <v>16</v>
@@ -7545,13 +7515,13 @@
         <v>173</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="C205" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E205" s="4" t="s">
         <v>12</v>
@@ -7574,7 +7544,7 @@
         <v>63</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C206" s="3" t="s">
         <v>10</v>
@@ -7586,10 +7556,10 @@
         <v>43</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="H206" s="3" t="s">
         <v>20</v>
@@ -7603,7 +7573,7 @@
         <v>64</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C207" s="4" t="s">
         <v>10</v>
@@ -7632,13 +7602,13 @@
         <v>174</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="C208" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E208" s="4" t="s">
         <v>12</v>
@@ -7661,7 +7631,7 @@
         <v>65</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C209" s="4" t="s">
         <v>10</v>
@@ -7690,13 +7660,13 @@
         <v>221</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="C210" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E210" s="4" t="s">
         <v>12</v>
@@ -7719,25 +7689,25 @@
         <v>66</v>
       </c>
       <c r="B211" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E211" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F211" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C211" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D211" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E211" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F211" s="3" t="s">
+      <c r="G211" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="G211" s="3">
-        <v>0</v>
-      </c>
       <c r="H211" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I211" s="3" t="s">
         <v>21</v>
@@ -7748,25 +7718,25 @@
         <v>192</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C212" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D212" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>41</v>
       </c>
       <c r="F212" s="6" t="s">
-        <v>186</v>
+        <v>302</v>
       </c>
       <c r="G212" s="6" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="H212" s="6" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="I212" s="6" t="s">
         <v>64</v>
@@ -7777,13 +7747,13 @@
         <v>175</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="C213" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E213" s="4" t="s">
         <v>12</v>
@@ -7806,57 +7776,57 @@
         <v>67</v>
       </c>
       <c r="B214" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C214" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D214" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E214" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F214" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G214" s="4">
+        <v>0</v>
+      </c>
+      <c r="H214" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I214" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A215" s="4">
+        <v>68</v>
+      </c>
+      <c r="B215" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C214" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D214" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E214" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F214" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G214" s="4">
-        <v>0</v>
-      </c>
-      <c r="H214" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I214" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A215" s="2">
-        <v>68</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D215" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E215" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F215" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="G215" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H215" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I215" s="2" t="s">
-        <v>16</v>
+      <c r="C215" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D215" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E215" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F215" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G215" s="4">
+        <v>0</v>
+      </c>
+      <c r="H215" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I215" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.3">
@@ -7864,13 +7834,13 @@
         <v>176</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C216" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E216" s="4" t="s">
         <v>12</v>
@@ -7893,13 +7863,13 @@
         <v>177</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="C217" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E217" s="4" t="s">
         <v>12</v>
@@ -7922,13 +7892,13 @@
         <v>222</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="C218" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E218" s="4" t="s">
         <v>12</v>
@@ -7951,25 +7921,25 @@
         <v>178</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>162</v>
+        <v>246</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>163</v>
+        <v>245</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>164</v>
+        <v>281</v>
       </c>
       <c r="I219" s="2" t="s">
         <v>16</v>
@@ -7980,13 +7950,13 @@
         <v>223</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="C220" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E220" s="5" t="s">
         <v>12</v>
@@ -7998,7 +7968,7 @@
         <v>13</v>
       </c>
       <c r="H220" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I220" s="5" t="s">
         <v>58</v>
@@ -8009,13 +7979,13 @@
         <v>238</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="C221" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E221" s="4" t="s">
         <v>18</v>
@@ -8038,25 +8008,25 @@
         <v>87</v>
       </c>
       <c r="B222" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C222" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D222" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E222" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F222" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="C222" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D222" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E222" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F222" s="6" t="s">
+      <c r="G222" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="G222" s="6" t="s">
+      <c r="H222" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H222" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I222" s="6" t="s">
         <v>64</v>
@@ -8067,7 +8037,7 @@
         <v>69</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>10</v>
@@ -8096,7 +8066,7 @@
         <v>70</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C224" s="4" t="s">
         <v>10</v>
@@ -8125,25 +8095,25 @@
         <v>224</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I225" s="2" t="s">
         <v>16</v>
@@ -8154,13 +8124,13 @@
         <v>179</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="C226" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E226" s="4" t="s">
         <v>12</v>
@@ -8183,7 +8153,7 @@
         <v>86</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C227" s="4" t="s">
         <v>10</v>
@@ -8208,32 +8178,32 @@
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A228" s="2">
+      <c r="A228" s="4">
         <v>225</v>
       </c>
-      <c r="B228" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D228" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E228" s="2" t="s">
+      <c r="B228" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C228" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D228" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E228" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F228" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="G228" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="H228" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I228" s="2" t="s">
-        <v>16</v>
+      <c r="F228" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G228" s="4">
+        <v>0</v>
+      </c>
+      <c r="H228" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I228" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.3">
@@ -8241,7 +8211,7 @@
         <v>71</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C229" s="4" t="s">
         <v>10</v>
@@ -8270,13 +8240,13 @@
         <v>226</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="C230" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E230" s="4" t="s">
         <v>12</v>
@@ -8299,25 +8269,25 @@
         <v>72</v>
       </c>
       <c r="B231" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F231" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C231" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D231" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E231" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F231" s="2" t="s">
+      <c r="G231" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="G231" s="2" t="s">
+      <c r="H231" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="H231" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="I231" s="2" t="s">
         <v>16</v>
@@ -8328,13 +8298,13 @@
         <v>236</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="C232" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E232" s="4" t="s">
         <v>41</v>
@@ -8357,25 +8327,25 @@
         <v>227</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="C233" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E233" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F233" s="6" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="G233" s="6" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="H233" s="6" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="I233" s="6" t="s">
         <v>64</v>
@@ -8386,19 +8356,19 @@
         <v>229</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="C234" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E234" s="4" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G234" s="4">
         <v>0</v>
@@ -8415,13 +8385,13 @@
         <v>228</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="C235" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E235" s="4" t="s">
         <v>12</v>
@@ -8444,7 +8414,7 @@
         <v>73</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C236" s="4" t="s">
         <v>10</v>
@@ -8473,7 +8443,7 @@
         <v>74</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C237" s="4" t="s">
         <v>10</v>
@@ -8502,7 +8472,7 @@
         <v>75</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C238" s="4" t="s">
         <v>10</v>
@@ -8527,32 +8497,32 @@
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A239" s="6">
+      <c r="A239" s="4">
         <v>180</v>
       </c>
-      <c r="B239" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="C239" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D239" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="E239" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F239" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="G239" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="H239" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="I239" s="6" t="s">
-        <v>64</v>
+      <c r="B239" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C239" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D239" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E239" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F239" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G239" s="4">
+        <v>0</v>
+      </c>
+      <c r="H239" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I239" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.3">
@@ -8560,13 +8530,13 @@
         <v>181</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="C240" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E240" s="3" t="s">
         <v>18</v>
@@ -8585,37 +8555,37 @@
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A241" s="6">
+      <c r="A241" s="4">
         <v>182</v>
       </c>
-      <c r="B241" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="C241" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D241" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="E241" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F241" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="G241" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="H241" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="I241" s="6" t="s">
-        <v>64</v>
+      <c r="B241" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C241" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D241" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E241" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F241" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G241" s="4">
+        <v>0</v>
+      </c>
+      <c r="H241" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I241" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I242">
-    <sortCondition ref="B195:B242"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I241">
+    <sortCondition ref="B3:B241"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pay.xlsx
+++ b/pay.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80EF98BE-5B43-4B69-8543-94F60C26013F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834750B1-9098-43A5-A102-926017230415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1032" windowWidth="21600" windowHeight="11208" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1747" uniqueCount="367">
   <si>
     <t>#</t>
   </si>
@@ -5550,8 +5550,8 @@
       <c r="F138" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="G138" s="2" t="s">
-        <v>234</v>
+      <c r="G138" s="2">
+        <v>0</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>235</v>

--- a/pay.xlsx
+++ b/pay.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="356">
   <si>
     <t>#</t>
   </si>
@@ -818,9 +818,6 @@
     <t>ميس محمد عصام عبد الوهاب</t>
   </si>
   <si>
-    <t>82.22%</t>
-  </si>
-  <si>
     <t>نور ابراهيم خالد محمد</t>
   </si>
   <si>
@@ -872,150 +869,150 @@
     <t>شمس مشتاق طالب علي</t>
   </si>
   <si>
+    <t>ترتيل عباس شهاب عبود</t>
+  </si>
+  <si>
+    <t>منتهى وسام عبد حسن حواس</t>
+  </si>
+  <si>
+    <t>1,050,000</t>
+  </si>
+  <si>
+    <t>975,000</t>
+  </si>
+  <si>
+    <t>51.85%</t>
+  </si>
+  <si>
+    <t>شايان مهدي داود عوده</t>
+  </si>
+  <si>
+    <t>احمد داود سلمان محمد</t>
+  </si>
+  <si>
+    <t>560,000</t>
+  </si>
+  <si>
+    <t>565,000</t>
+  </si>
+  <si>
+    <t>49.78%</t>
+  </si>
+  <si>
+    <t>احمد عبد الرحيم ابراهيم العسكري</t>
+  </si>
+  <si>
+    <t>860,000</t>
+  </si>
+  <si>
+    <t>1,390,000</t>
+  </si>
+  <si>
+    <t>38.22%</t>
+  </si>
+  <si>
+    <t>احمد عطيه محمد جياد</t>
+  </si>
+  <si>
+    <t>احمدي جعفر صادق حسين</t>
+  </si>
+  <si>
+    <t>اسامه خالد قدوري سلمان</t>
+  </si>
+  <si>
+    <t>اسراء سعد نعمة كاظم</t>
+  </si>
+  <si>
+    <t>اسراء شعلان احمد حزوم</t>
+  </si>
+  <si>
+    <t>امين عماد عبد الحميد احمد</t>
+  </si>
+  <si>
+    <t>ايه حامد حسين علوان</t>
+  </si>
+  <si>
+    <t>بشار محمد حاتم حسين</t>
+  </si>
+  <si>
+    <t>بهاء الدين احمد عويد كيطان</t>
+  </si>
+  <si>
+    <t>حيدر علي حسين كاظم</t>
+  </si>
+  <si>
+    <t>زمن داود بناي عبد الله</t>
+  </si>
+  <si>
+    <t>1,940,000</t>
+  </si>
+  <si>
+    <t>85,000</t>
+  </si>
+  <si>
+    <t>95.8%</t>
+  </si>
+  <si>
+    <t>زهراء عبد الكريم رضا جابر</t>
+  </si>
+  <si>
+    <t>سجاد فراس عباس فاضل</t>
+  </si>
+  <si>
+    <t>شهد عبد الكريم كاظم جلوب</t>
+  </si>
+  <si>
+    <t>عبد الرزاق حسين فوزي اسماعيل</t>
+  </si>
+  <si>
+    <t>عزالدين عبدالكريم عفتان ثامر</t>
+  </si>
+  <si>
+    <t>علي رزاق عباس يوسف</t>
+  </si>
+  <si>
+    <t>عواد قدوري عواد داود</t>
+  </si>
+  <si>
+    <t>مائده عبد محسن فرحان</t>
+  </si>
+  <si>
+    <t>24.44%</t>
+  </si>
+  <si>
+    <t>مجتبى علي فيصل علوان</t>
+  </si>
+  <si>
+    <t>مجيد محمود مجيد حميد</t>
+  </si>
+  <si>
+    <t>محب جاسم محمد صالح</t>
+  </si>
+  <si>
+    <t>محمد محمود صابر صادق</t>
+  </si>
+  <si>
+    <t>مصطفى خلف عبد الله وهيب</t>
+  </si>
+  <si>
+    <t>مصطفى محمود صالح</t>
+  </si>
+  <si>
+    <t>منتظر معتز مهدي عبدالسادة</t>
+  </si>
+  <si>
+    <t>مؤيد وليد مؤيد احمد</t>
+  </si>
+  <si>
+    <t>ميلاد عبد الزهرة عبيد حسين</t>
+  </si>
+  <si>
+    <t>ندى علي عبد الحسين ابراهيم</t>
+  </si>
+  <si>
     <t>88.89%</t>
   </si>
   <si>
-    <t>ترتيل عباس شهاب عبود</t>
-  </si>
-  <si>
-    <t>منتهى وسام عبد حسن حواس</t>
-  </si>
-  <si>
-    <t>1,050,000</t>
-  </si>
-  <si>
-    <t>975,000</t>
-  </si>
-  <si>
-    <t>51.85%</t>
-  </si>
-  <si>
-    <t>شايان مهدي داود عوده</t>
-  </si>
-  <si>
-    <t>احمد داود سلمان محمد</t>
-  </si>
-  <si>
-    <t>560,000</t>
-  </si>
-  <si>
-    <t>565,000</t>
-  </si>
-  <si>
-    <t>49.78%</t>
-  </si>
-  <si>
-    <t>احمد عبد الرحيم ابراهيم العسكري</t>
-  </si>
-  <si>
-    <t>860,000</t>
-  </si>
-  <si>
-    <t>1,390,000</t>
-  </si>
-  <si>
-    <t>38.22%</t>
-  </si>
-  <si>
-    <t>احمد عطيه محمد جياد</t>
-  </si>
-  <si>
-    <t>احمدي جعفر صادق حسين</t>
-  </si>
-  <si>
-    <t>اسامه خالد قدوري سلمان</t>
-  </si>
-  <si>
-    <t>اسراء سعد نعمة كاظم</t>
-  </si>
-  <si>
-    <t>اسراء شعلان احمد حزوم</t>
-  </si>
-  <si>
-    <t>امين عماد عبد الحميد احمد</t>
-  </si>
-  <si>
-    <t>ايه حامد حسين علوان</t>
-  </si>
-  <si>
-    <t>بشار محمد حاتم حسين</t>
-  </si>
-  <si>
-    <t>بهاء الدين احمد عويد كيطان</t>
-  </si>
-  <si>
-    <t>حيدر علي حسين كاظم</t>
-  </si>
-  <si>
-    <t>زمن داود بناي عبد الله</t>
-  </si>
-  <si>
-    <t>1,940,000</t>
-  </si>
-  <si>
-    <t>85,000</t>
-  </si>
-  <si>
-    <t>95.8%</t>
-  </si>
-  <si>
-    <t>زهراء عبد الكريم رضا جابر</t>
-  </si>
-  <si>
-    <t>سجاد فراس عباس فاضل</t>
-  </si>
-  <si>
-    <t>شهد عبد الكريم كاظم جلوب</t>
-  </si>
-  <si>
-    <t>عبد الرزاق حسين فوزي اسماعيل</t>
-  </si>
-  <si>
-    <t>عزالدين عبدالكريم عفتان ثامر</t>
-  </si>
-  <si>
-    <t>علي رزاق عباس يوسف</t>
-  </si>
-  <si>
-    <t>عواد قدوري عواد داود</t>
-  </si>
-  <si>
-    <t>مائده عبد محسن فرحان</t>
-  </si>
-  <si>
-    <t>24.44%</t>
-  </si>
-  <si>
-    <t>مجتبى علي فيصل علوان</t>
-  </si>
-  <si>
-    <t>مجيد محمود مجيد حميد</t>
-  </si>
-  <si>
-    <t>محب جاسم محمد صالح</t>
-  </si>
-  <si>
-    <t>محمد محمود صابر صادق</t>
-  </si>
-  <si>
-    <t>مصطفى خلف عبد الله وهيب</t>
-  </si>
-  <si>
-    <t>مصطفى محمود صالح</t>
-  </si>
-  <si>
-    <t>منتظر معتز مهدي عبدالسادة</t>
-  </si>
-  <si>
-    <t>مؤيد وليد مؤيد احمد</t>
-  </si>
-  <si>
-    <t>ميلاد عبد الزهرة عبيد حسين</t>
-  </si>
-  <si>
-    <t>ندى علي عبد الحسين ابراهيم</t>
-  </si>
-  <si>
     <t>نور صباح صالح نصرالله</t>
   </si>
   <si>
@@ -1055,27 +1052,9 @@
     <t>طيبة اثير عبد المنعم</t>
   </si>
   <si>
-    <t>2,225,000</t>
-  </si>
-  <si>
-    <t>25,000</t>
-  </si>
-  <si>
-    <t>98.89%</t>
-  </si>
-  <si>
     <t>رباب اركان حسين علي</t>
   </si>
   <si>
-    <t>200,000</t>
-  </si>
-  <si>
-    <t>2,050,000</t>
-  </si>
-  <si>
-    <t>8.89%</t>
-  </si>
-  <si>
     <t>ريام ماجد محمد علي</t>
   </si>
   <si>
@@ -1095,9 +1074,6 @@
   </si>
   <si>
     <t>زينب صالح كريم صالح</t>
-  </si>
-  <si>
-    <t>50%</t>
   </si>
   <si>
     <t>رشا ابراهيم كاظم محسن</t>
@@ -6701,32 +6677,32 @@
       </c>
     </row>
     <row r="179" spans="1:9">
-      <c r="A179" s="2">
+      <c r="A179" s="4">
         <v>178</v>
       </c>
-      <c r="B179" s="2" t="s">
+      <c r="B179" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="C179" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D179" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E179" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F179" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="G179" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="H179" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="I179" s="2" t="s">
-        <v>16</v>
+      <c r="C179" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E179" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F179" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G179" s="4">
+        <v>0</v>
+      </c>
+      <c r="H179" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I179" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="180" spans="1:9">
@@ -6734,7 +6710,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>10</v>
@@ -6763,7 +6739,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>10</v>
@@ -6792,7 +6768,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C182" s="3" t="s">
         <v>10</v>
@@ -6821,7 +6797,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>10</v>
@@ -6850,7 +6826,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>10</v>
@@ -6879,7 +6855,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>10</v>
@@ -6908,7 +6884,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>10</v>
@@ -6937,7 +6913,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>10</v>
@@ -6966,7 +6942,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>10</v>
@@ -6978,13 +6954,13 @@
         <v>257</v>
       </c>
       <c r="F188" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="G188" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="G188" s="6" t="s">
+      <c r="H188" s="6" t="s">
         <v>278</v>
-      </c>
-      <c r="H188" s="6" t="s">
-        <v>279</v>
       </c>
       <c r="I188" s="6" t="s">
         <v>64</v>
@@ -6995,7 +6971,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>10</v>
@@ -7010,7 +6986,7 @@
         <v>130</v>
       </c>
       <c r="G189" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H189" s="6" t="s">
         <v>63</v>
@@ -7024,7 +7000,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>10</v>
@@ -7042,39 +7018,39 @@
         <v>228</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I190" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="191" spans="1:9">
-      <c r="A191" s="2">
+      <c r="A191" s="4">
         <v>190</v>
       </c>
-      <c r="B191" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="C191" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D191" s="2" t="s">
+      <c r="B191" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D191" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="E191" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F191" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G191" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H191" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="I191" s="2" t="s">
-        <v>16</v>
+      <c r="E191" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F191" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G191" s="4">
+        <v>0</v>
+      </c>
+      <c r="H191" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I191" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="192" spans="1:9">
@@ -7082,7 +7058,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>10</v>
@@ -7111,7 +7087,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>10</v>
@@ -7123,13 +7099,13 @@
         <v>41</v>
       </c>
       <c r="F193" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="G193" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="H193" s="6" t="s">
         <v>288</v>
-      </c>
-      <c r="G193" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="H193" s="6" t="s">
-        <v>290</v>
       </c>
       <c r="I193" s="6" t="s">
         <v>64</v>
@@ -7140,7 +7116,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C194" s="5" t="s">
         <v>10</v>
@@ -7169,7 +7145,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C195" s="3" t="s">
         <v>10</v>
@@ -7181,13 +7157,13 @@
         <v>18</v>
       </c>
       <c r="F195" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="H195" s="3" t="s">
         <v>293</v>
-      </c>
-      <c r="G195" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="H195" s="3" t="s">
-        <v>295</v>
       </c>
       <c r="I195" s="3" t="s">
         <v>21</v>
@@ -7198,25 +7174,25 @@
         <v>195</v>
       </c>
       <c r="B196" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F196" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="G196" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="C196" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D196" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="E196" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F196" s="3" t="s">
+      <c r="H196" s="3" t="s">
         <v>297</v>
-      </c>
-      <c r="G196" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="H196" s="3" t="s">
-        <v>299</v>
       </c>
       <c r="I196" s="3" t="s">
         <v>21</v>
@@ -7227,7 +7203,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C197" s="4" t="s">
         <v>10</v>
@@ -7256,7 +7232,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C198" s="4" t="s">
         <v>10</v>
@@ -7285,7 +7261,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C199" s="5" t="s">
         <v>10</v>
@@ -7314,7 +7290,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C200" s="4" t="s">
         <v>10</v>
@@ -7343,7 +7319,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C201" s="4" t="s">
         <v>10</v>
@@ -7372,7 +7348,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C202" s="5" t="s">
         <v>10</v>
@@ -7401,7 +7377,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C203" s="4" t="s">
         <v>10</v>
@@ -7430,7 +7406,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C204" s="4" t="s">
         <v>10</v>
@@ -7459,7 +7435,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C205" s="4" t="s">
         <v>10</v>
@@ -7488,7 +7464,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C206" s="4" t="s">
         <v>10</v>
@@ -7517,7 +7493,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>10</v>
@@ -7529,13 +7505,13 @@
         <v>41</v>
       </c>
       <c r="F207" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="G207" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="H207" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="G207" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="H207" s="2" t="s">
-        <v>313</v>
       </c>
       <c r="I207" s="2" t="s">
         <v>16</v>
@@ -7546,7 +7522,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C208" s="4" t="s">
         <v>10</v>
@@ -7575,7 +7551,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C209" s="4" t="s">
         <v>10</v>
@@ -7604,7 +7580,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C210" s="4" t="s">
         <v>10</v>
@@ -7633,7 +7609,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C211" s="4" t="s">
         <v>10</v>
@@ -7662,7 +7638,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C212" s="4" t="s">
         <v>10</v>
@@ -7691,7 +7667,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C213" s="4" t="s">
         <v>10</v>
@@ -7720,7 +7696,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C214" s="5" t="s">
         <v>10</v>
@@ -7749,7 +7725,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C215" s="5" t="s">
         <v>10</v>
@@ -7767,7 +7743,7 @@
         <v>215</v>
       </c>
       <c r="H215" s="5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="I215" s="5" t="s">
         <v>58</v>
@@ -7778,7 +7754,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C216" s="4" t="s">
         <v>10</v>
@@ -7807,7 +7783,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C217" s="4" t="s">
         <v>10</v>
@@ -7836,7 +7812,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C218" s="5" t="s">
         <v>10</v>
@@ -7865,7 +7841,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>10</v>
@@ -7894,7 +7870,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C220" s="4" t="s">
         <v>10</v>
@@ -7923,7 +7899,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C221" s="5" t="s">
         <v>10</v>
@@ -7952,7 +7928,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C222" s="4" t="s">
         <v>10</v>
@@ -7981,7 +7957,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C223" s="4" t="s">
         <v>10</v>
@@ -8010,7 +7986,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C224" s="5" t="s">
         <v>10</v>
@@ -8039,7 +8015,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>10</v>
@@ -8057,7 +8033,7 @@
         <v>87</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>285</v>
+        <v>331</v>
       </c>
       <c r="I225" s="2" t="s">
         <v>16</v>
@@ -8068,7 +8044,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C226" s="4" t="s">
         <v>10</v>
@@ -8097,7 +8073,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C227" s="4" t="s">
         <v>10</v>
@@ -8126,25 +8102,25 @@
         <v>227</v>
       </c>
       <c r="B228" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="C228" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D228" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E228" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F228" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="C228" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D228" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="E228" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F228" s="6" t="s">
+      <c r="G228" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="G228" s="6" t="s">
+      <c r="H228" s="6" t="s">
         <v>337</v>
-      </c>
-      <c r="H228" s="6" t="s">
-        <v>338</v>
       </c>
       <c r="I228" s="6" t="s">
         <v>64</v>
@@ -8155,7 +8131,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C229" s="4" t="s">
         <v>10</v>
@@ -8184,7 +8160,7 @@
         <v>229</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C230" s="4" t="s">
         <v>10</v>
@@ -8213,7 +8189,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C231" s="4" t="s">
         <v>10</v>
@@ -8222,10 +8198,10 @@
         <v>146</v>
       </c>
       <c r="E231" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G231" s="4">
         <v>0</v>
@@ -8242,7 +8218,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C232" s="4" t="s">
         <v>10</v>
@@ -8271,7 +8247,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C233" s="4" t="s">
         <v>10</v>
@@ -8296,61 +8272,61 @@
       </c>
     </row>
     <row r="234" spans="1:9">
-      <c r="A234" s="2">
+      <c r="A234" s="4">
         <v>233</v>
       </c>
-      <c r="B234" s="2" t="s">
+      <c r="B234" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C234" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D234" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E234" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F234" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G234" s="4">
+        <v>0</v>
+      </c>
+      <c r="H234" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I234" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9">
+      <c r="A235" s="2">
+        <v>234</v>
+      </c>
+      <c r="B235" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="C234" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D234" s="2" t="s">
+      <c r="C235" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D235" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="E234" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F234" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="G234" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="H234" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="I234" s="2" t="s">
+      <c r="E235" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F235" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="G235" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="H235" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="I235" s="2" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="235" spans="1:9">
-      <c r="A235" s="5">
-        <v>234</v>
-      </c>
-      <c r="B235" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="C235" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D235" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="E235" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F235" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="G235" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="H235" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="I235" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="236" spans="1:9">
@@ -8358,7 +8334,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C236" s="6" t="s">
         <v>10</v>
@@ -8367,16 +8343,16 @@
         <v>146</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F236" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G236" s="6" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="H236" s="6" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="I236" s="6" t="s">
         <v>64</v>
@@ -8387,7 +8363,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="C237" s="4" t="s">
         <v>10</v>
@@ -8416,7 +8392,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C238" s="4" t="s">
         <v>10</v>
@@ -8445,7 +8421,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="C239" s="4" t="s">
         <v>10</v>
@@ -8470,32 +8446,32 @@
       </c>
     </row>
     <row r="240" spans="1:9">
-      <c r="A240" s="6">
+      <c r="A240" s="4">
         <v>239</v>
       </c>
-      <c r="B240" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="C240" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D240" s="6" t="s">
+      <c r="B240" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C240" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D240" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="E240" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F240" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G240" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H240" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="I240" s="6" t="s">
-        <v>64</v>
+      <c r="E240" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F240" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G240" s="4">
+        <v>0</v>
+      </c>
+      <c r="H240" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I240" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="241" spans="1:9">
@@ -8503,7 +8479,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="C241" s="6" t="s">
         <v>10</v>
@@ -8515,13 +8491,13 @@
         <v>41</v>
       </c>
       <c r="F241" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G241" s="6" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="H241" s="6" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="I241" s="6" t="s">
         <v>64</v>

--- a/pay.xlsx
+++ b/pay.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="355">
   <si>
     <t>#</t>
   </si>
@@ -863,9 +863,6 @@
     <t>اسياد اياد نايف عبد الحسين</t>
   </si>
   <si>
-    <t>80.25%</t>
-  </si>
-  <si>
     <t>شمس مشتاق طالب علي</t>
   </si>
   <si>
@@ -875,18 +872,24 @@
     <t>منتهى وسام عبد حسن حواس</t>
   </si>
   <si>
-    <t>1,050,000</t>
-  </si>
-  <si>
-    <t>975,000</t>
-  </si>
-  <si>
-    <t>51.85%</t>
+    <t>25,000</t>
+  </si>
+  <si>
+    <t>98.77%</t>
   </si>
   <si>
     <t>شايان مهدي داود عوده</t>
   </si>
   <si>
+    <t>1,400,000</t>
+  </si>
+  <si>
+    <t>850,000</t>
+  </si>
+  <si>
+    <t>62.22%</t>
+  </si>
+  <si>
     <t>احمد داود سلمان محمد</t>
   </si>
   <si>
@@ -1056,12 +1059,6 @@
   </si>
   <si>
     <t>ريام ماجد محمد علي</t>
-  </si>
-  <si>
-    <t>937,500</t>
-  </si>
-  <si>
-    <t>50.98%</t>
   </si>
   <si>
     <t>هند وليد سلمان يوسف</t>
@@ -6996,32 +6993,32 @@
       </c>
     </row>
     <row r="190" spans="1:9">
-      <c r="A190" s="2">
+      <c r="A190" s="4">
         <v>189</v>
       </c>
-      <c r="B190" s="2" t="s">
+      <c r="B190" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="C190" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D190" s="2" t="s">
+      <c r="C190" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D190" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="E190" s="2" t="s">
+      <c r="E190" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F190" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G190" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="H190" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="I190" s="2" t="s">
-        <v>16</v>
+      <c r="F190" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G190" s="4">
+        <v>0</v>
+      </c>
+      <c r="H190" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I190" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="191" spans="1:9">
@@ -7029,7 +7026,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>10</v>
@@ -7058,7 +7055,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>10</v>
@@ -7083,61 +7080,61 @@
       </c>
     </row>
     <row r="193" spans="1:9">
-      <c r="A193" s="6">
+      <c r="A193" s="2">
         <v>192</v>
       </c>
-      <c r="B193" s="6" t="s">
+      <c r="B193" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F193" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G193" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C193" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D193" s="6" t="s">
+      <c r="H193" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I193" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9">
+      <c r="A194" s="6">
+        <v>193</v>
+      </c>
+      <c r="B194" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="C194" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D194" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="E193" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F193" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="G193" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="H193" s="6" t="s">
+      <c r="E194" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F194" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="I193" s="6" t="s">
+      <c r="G194" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="H194" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="I194" s="6" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="194" spans="1:9">
-      <c r="A194" s="5">
-        <v>193</v>
-      </c>
-      <c r="B194" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="C194" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D194" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="E194" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F194" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="G194" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="H194" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="I194" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="195" spans="1:9">
@@ -7145,7 +7142,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C195" s="3" t="s">
         <v>10</v>
@@ -7157,13 +7154,13 @@
         <v>18</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H195" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I195" s="3" t="s">
         <v>21</v>
@@ -7174,7 +7171,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C196" s="3" t="s">
         <v>10</v>
@@ -7186,13 +7183,13 @@
         <v>12</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H196" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I196" s="3" t="s">
         <v>21</v>
@@ -7203,7 +7200,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C197" s="4" t="s">
         <v>10</v>
@@ -7232,7 +7229,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C198" s="4" t="s">
         <v>10</v>
@@ -7261,7 +7258,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C199" s="5" t="s">
         <v>10</v>
@@ -7290,7 +7287,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C200" s="4" t="s">
         <v>10</v>
@@ -7319,7 +7316,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C201" s="4" t="s">
         <v>10</v>
@@ -7348,7 +7345,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C202" s="5" t="s">
         <v>10</v>
@@ -7377,7 +7374,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C203" s="4" t="s">
         <v>10</v>
@@ -7406,7 +7403,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C204" s="4" t="s">
         <v>10</v>
@@ -7435,7 +7432,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C205" s="4" t="s">
         <v>10</v>
@@ -7464,7 +7461,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C206" s="4" t="s">
         <v>10</v>
@@ -7493,7 +7490,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>10</v>
@@ -7505,13 +7502,13 @@
         <v>41</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H207" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I207" s="2" t="s">
         <v>16</v>
@@ -7522,7 +7519,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C208" s="4" t="s">
         <v>10</v>
@@ -7551,7 +7548,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C209" s="4" t="s">
         <v>10</v>
@@ -7580,7 +7577,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C210" s="4" t="s">
         <v>10</v>
@@ -7609,7 +7606,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C211" s="4" t="s">
         <v>10</v>
@@ -7638,7 +7635,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C212" s="4" t="s">
         <v>10</v>
@@ -7667,7 +7664,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C213" s="4" t="s">
         <v>10</v>
@@ -7696,7 +7693,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C214" s="5" t="s">
         <v>10</v>
@@ -7725,7 +7722,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C215" s="5" t="s">
         <v>10</v>
@@ -7743,7 +7740,7 @@
         <v>215</v>
       </c>
       <c r="H215" s="5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I215" s="5" t="s">
         <v>58</v>
@@ -7754,7 +7751,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C216" s="4" t="s">
         <v>10</v>
@@ -7783,7 +7780,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C217" s="4" t="s">
         <v>10</v>
@@ -7812,7 +7809,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C218" s="5" t="s">
         <v>10</v>
@@ -7841,7 +7838,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>10</v>
@@ -7870,7 +7867,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C220" s="4" t="s">
         <v>10</v>
@@ -7899,7 +7896,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C221" s="5" t="s">
         <v>10</v>
@@ -7928,7 +7925,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C222" s="4" t="s">
         <v>10</v>
@@ -7957,7 +7954,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C223" s="4" t="s">
         <v>10</v>
@@ -7986,7 +7983,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C224" s="5" t="s">
         <v>10</v>
@@ -8015,7 +8012,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>10</v>
@@ -8033,7 +8030,7 @@
         <v>87</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="I225" s="2" t="s">
         <v>16</v>
@@ -8044,7 +8041,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C226" s="4" t="s">
         <v>10</v>
@@ -8073,7 +8070,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C227" s="4" t="s">
         <v>10</v>
@@ -8102,7 +8099,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C228" s="6" t="s">
         <v>10</v>
@@ -8114,13 +8111,13 @@
         <v>12</v>
       </c>
       <c r="F228" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G228" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H228" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I228" s="6" t="s">
         <v>64</v>
@@ -8131,7 +8128,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C229" s="4" t="s">
         <v>10</v>
@@ -8160,7 +8157,7 @@
         <v>229</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C230" s="4" t="s">
         <v>10</v>
@@ -8189,7 +8186,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C231" s="4" t="s">
         <v>10</v>
@@ -8198,10 +8195,10 @@
         <v>146</v>
       </c>
       <c r="E231" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G231" s="4">
         <v>0</v>
@@ -8218,7 +8215,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C232" s="4" t="s">
         <v>10</v>
@@ -8247,7 +8244,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C233" s="4" t="s">
         <v>10</v>
@@ -8276,7 +8273,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C234" s="4" t="s">
         <v>10</v>
@@ -8305,7 +8302,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>10</v>
@@ -8330,32 +8327,32 @@
       </c>
     </row>
     <row r="236" spans="1:9">
-      <c r="A236" s="6">
+      <c r="A236" s="4">
         <v>235</v>
       </c>
-      <c r="B236" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="C236" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D236" s="6" t="s">
+      <c r="B236" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C236" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D236" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="E236" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="F236" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="G236" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="H236" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="I236" s="6" t="s">
-        <v>64</v>
+      <c r="E236" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="F236" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="G236" s="4">
+        <v>0</v>
+      </c>
+      <c r="H236" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I236" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="237" spans="1:9">
@@ -8363,7 +8360,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C237" s="4" t="s">
         <v>10</v>
@@ -8392,7 +8389,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C238" s="4" t="s">
         <v>10</v>
@@ -8421,7 +8418,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C239" s="4" t="s">
         <v>10</v>
@@ -8450,7 +8447,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C240" s="4" t="s">
         <v>10</v>
@@ -8479,7 +8476,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C241" s="6" t="s">
         <v>10</v>
@@ -8494,10 +8491,10 @@
         <v>276</v>
       </c>
       <c r="G241" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="H241" s="6" t="s">
         <v>354</v>
-      </c>
-      <c r="H241" s="6" t="s">
-        <v>355</v>
       </c>
       <c r="I241" s="6" t="s">
         <v>64</v>

--- a/pay.xlsx
+++ b/pay.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="356">
   <si>
     <t>#</t>
   </si>
@@ -1076,10 +1076,13 @@
     <t>رشا ابراهيم كاظم محسن</t>
   </si>
   <si>
-    <t>925,000</t>
-  </si>
-  <si>
-    <t>54.32%</t>
+    <t>1,600,000</t>
+  </si>
+  <si>
+    <t>425,000</t>
+  </si>
+  <si>
+    <t>79.01%</t>
   </si>
 </sst>
 </file>
@@ -8282,7 +8285,7 @@
         <v>146</v>
       </c>
       <c r="E234" s="4" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="F234" s="4" t="s">
         <v>12</v>
@@ -8472,32 +8475,32 @@
       </c>
     </row>
     <row r="241" spans="1:9">
-      <c r="A241" s="6">
+      <c r="A241" s="2">
         <v>240</v>
       </c>
-      <c r="B241" s="6" t="s">
+      <c r="B241" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="C241" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D241" s="6" t="s">
+      <c r="C241" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D241" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="E241" s="6" t="s">
+      <c r="E241" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F241" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="G241" s="6" t="s">
+      <c r="F241" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="H241" s="6" t="s">
+      <c r="G241" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="I241" s="6" t="s">
-        <v>64</v>
+      <c r="H241" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="I241" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/pay.xlsx
+++ b/pay.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="354">
   <si>
     <t>#</t>
   </si>
@@ -870,12 +870,6 @@
   </si>
   <si>
     <t>منتهى وسام عبد حسن حواس</t>
-  </si>
-  <si>
-    <t>25,000</t>
-  </si>
-  <si>
-    <t>98.77%</t>
   </si>
   <si>
     <t>شايان مهدي داود عوده</t>
@@ -7083,32 +7077,32 @@
       </c>
     </row>
     <row r="193" spans="1:9">
-      <c r="A193" s="2">
+      <c r="A193" s="4">
         <v>192</v>
       </c>
-      <c r="B193" s="2" t="s">
+      <c r="B193" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="C193" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D193" s="2" t="s">
+      <c r="C193" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D193" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="E193" s="2" t="s">
+      <c r="E193" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F193" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G193" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="H193" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="I193" s="2" t="s">
-        <v>16</v>
+      <c r="F193" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G193" s="4">
+        <v>0</v>
+      </c>
+      <c r="H193" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I193" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="194" spans="1:9">
@@ -7116,7 +7110,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C194" s="6" t="s">
         <v>10</v>
@@ -7128,13 +7122,13 @@
         <v>12</v>
       </c>
       <c r="F194" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="G194" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="H194" s="6" t="s">
         <v>288</v>
-      </c>
-      <c r="G194" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="H194" s="6" t="s">
-        <v>290</v>
       </c>
       <c r="I194" s="6" t="s">
         <v>64</v>
@@ -7145,7 +7139,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C195" s="3" t="s">
         <v>10</v>
@@ -7157,13 +7151,13 @@
         <v>18</v>
       </c>
       <c r="F195" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="H195" s="3" t="s">
         <v>292</v>
-      </c>
-      <c r="G195" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="H195" s="3" t="s">
-        <v>294</v>
       </c>
       <c r="I195" s="3" t="s">
         <v>21</v>
@@ -7174,25 +7168,25 @@
         <v>195</v>
       </c>
       <c r="B196" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F196" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="G196" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="C196" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D196" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="E196" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F196" s="3" t="s">
+      <c r="H196" s="3" t="s">
         <v>296</v>
-      </c>
-      <c r="G196" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="H196" s="3" t="s">
-        <v>298</v>
       </c>
       <c r="I196" s="3" t="s">
         <v>21</v>
@@ -7203,7 +7197,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C197" s="4" t="s">
         <v>10</v>
@@ -7232,7 +7226,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C198" s="4" t="s">
         <v>10</v>
@@ -7261,7 +7255,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C199" s="5" t="s">
         <v>10</v>
@@ -7290,7 +7284,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C200" s="4" t="s">
         <v>10</v>
@@ -7319,7 +7313,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C201" s="4" t="s">
         <v>10</v>
@@ -7348,7 +7342,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C202" s="5" t="s">
         <v>10</v>
@@ -7377,7 +7371,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C203" s="4" t="s">
         <v>10</v>
@@ -7406,7 +7400,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C204" s="4" t="s">
         <v>10</v>
@@ -7435,7 +7429,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C205" s="4" t="s">
         <v>10</v>
@@ -7464,7 +7458,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C206" s="4" t="s">
         <v>10</v>
@@ -7493,7 +7487,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>10</v>
@@ -7505,13 +7499,13 @@
         <v>41</v>
       </c>
       <c r="F207" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="G207" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="H207" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="G207" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="H207" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="I207" s="2" t="s">
         <v>16</v>
@@ -7522,7 +7516,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C208" s="4" t="s">
         <v>10</v>
@@ -7551,7 +7545,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C209" s="4" t="s">
         <v>10</v>
@@ -7580,7 +7574,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C210" s="4" t="s">
         <v>10</v>
@@ -7609,7 +7603,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C211" s="4" t="s">
         <v>10</v>
@@ -7638,7 +7632,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C212" s="4" t="s">
         <v>10</v>
@@ -7667,7 +7661,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C213" s="4" t="s">
         <v>10</v>
@@ -7696,7 +7690,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C214" s="5" t="s">
         <v>10</v>
@@ -7725,7 +7719,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C215" s="5" t="s">
         <v>10</v>
@@ -7743,7 +7737,7 @@
         <v>215</v>
       </c>
       <c r="H215" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="I215" s="5" t="s">
         <v>58</v>
@@ -7754,7 +7748,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C216" s="4" t="s">
         <v>10</v>
@@ -7783,7 +7777,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C217" s="4" t="s">
         <v>10</v>
@@ -7812,7 +7806,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C218" s="5" t="s">
         <v>10</v>
@@ -7841,7 +7835,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>10</v>
@@ -7870,7 +7864,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C220" s="4" t="s">
         <v>10</v>
@@ -7899,7 +7893,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C221" s="5" t="s">
         <v>10</v>
@@ -7928,7 +7922,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C222" s="4" t="s">
         <v>10</v>
@@ -7957,7 +7951,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C223" s="4" t="s">
         <v>10</v>
@@ -7986,7 +7980,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C224" s="5" t="s">
         <v>10</v>
@@ -8015,7 +8009,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>10</v>
@@ -8033,7 +8027,7 @@
         <v>87</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="I225" s="2" t="s">
         <v>16</v>
@@ -8044,7 +8038,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C226" s="4" t="s">
         <v>10</v>
@@ -8073,7 +8067,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C227" s="4" t="s">
         <v>10</v>
@@ -8102,25 +8096,25 @@
         <v>227</v>
       </c>
       <c r="B228" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="C228" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D228" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E228" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F228" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="G228" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="C228" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D228" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="E228" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F228" s="6" t="s">
+      <c r="H228" s="6" t="s">
         <v>336</v>
-      </c>
-      <c r="G228" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="H228" s="6" t="s">
-        <v>338</v>
       </c>
       <c r="I228" s="6" t="s">
         <v>64</v>
@@ -8131,7 +8125,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C229" s="4" t="s">
         <v>10</v>
@@ -8160,7 +8154,7 @@
         <v>229</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C230" s="4" t="s">
         <v>10</v>
@@ -8189,7 +8183,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C231" s="4" t="s">
         <v>10</v>
@@ -8198,10 +8192,10 @@
         <v>146</v>
       </c>
       <c r="E231" s="4" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G231" s="4">
         <v>0</v>
@@ -8218,7 +8212,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C232" s="4" t="s">
         <v>10</v>
@@ -8247,7 +8241,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C233" s="4" t="s">
         <v>10</v>
@@ -8276,7 +8270,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C234" s="4" t="s">
         <v>10</v>
@@ -8305,7 +8299,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>10</v>
@@ -8334,7 +8328,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C236" s="4" t="s">
         <v>10</v>
@@ -8343,10 +8337,10 @@
         <v>146</v>
       </c>
       <c r="E236" s="4" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G236" s="4">
         <v>0</v>
@@ -8363,7 +8357,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C237" s="4" t="s">
         <v>10</v>
@@ -8392,7 +8386,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C238" s="4" t="s">
         <v>10</v>
@@ -8421,7 +8415,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C239" s="4" t="s">
         <v>10</v>
@@ -8450,7 +8444,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C240" s="4" t="s">
         <v>10</v>
@@ -8479,7 +8473,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>10</v>
@@ -8491,13 +8485,13 @@
         <v>41</v>
       </c>
       <c r="F241" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="G241" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="H241" s="2" t="s">
         <v>353</v>
-      </c>
-      <c r="G241" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="H241" s="2" t="s">
-        <v>355</v>
       </c>
       <c r="I241" s="2" t="s">
         <v>16</v>

--- a/pay.xlsx
+++ b/pay.xlsx
@@ -1,21 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46652C8-7BA1-479F-9227-74E1DD68CB84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="1440" yWindow="1032" windowWidth="21600" windowHeight="11208" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="191029" forceFullCalc="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="353">
   <si>
     <t>#</t>
   </si>
@@ -1071,9 +1087,6 @@
   </si>
   <si>
     <t>1,600,000</t>
-  </si>
-  <si>
-    <t>425,000</t>
   </si>
   <si>
     <t>79.01%</t>
@@ -1082,23 +1095,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
@@ -1176,31 +1181,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="5" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="6" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="7" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1490,25 +1503,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I241"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="41.133" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="43.418" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="12.568" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="17.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="21.566" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="21.566" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="19.138" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="19.138" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1537,7 +1545,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1566,7 +1574,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1595,7 +1603,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -1624,7 +1632,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -1653,7 +1661,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -1682,7 +1690,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -1711,7 +1719,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -1740,7 +1748,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -1769,7 +1777,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -1798,7 +1806,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -1827,7 +1835,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -1856,7 +1864,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -1885,7 +1893,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -1914,7 +1922,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -1943,7 +1951,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -1972,7 +1980,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -2001,7 +2009,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -2030,7 +2038,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -2059,7 +2067,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -2088,7 +2096,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -2117,7 +2125,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -2146,7 +2154,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -2175,7 +2183,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -2204,7 +2212,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -2233,7 +2241,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -2262,7 +2270,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -2291,7 +2299,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -2320,7 +2328,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -2349,7 +2357,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -2378,7 +2386,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -2407,7 +2415,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -2436,7 +2444,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -2465,7 +2473,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -2494,7 +2502,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="6">
         <v>34</v>
       </c>
@@ -2523,7 +2531,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -2552,7 +2560,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -2581,7 +2589,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="6">
         <v>37</v>
       </c>
@@ -2610,7 +2618,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -2639,7 +2647,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -2668,7 +2676,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -2697,7 +2705,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -2726,7 +2734,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -2755,7 +2763,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>43</v>
       </c>
@@ -2784,7 +2792,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -2813,7 +2821,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -2842,7 +2850,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -2871,7 +2879,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>47</v>
       </c>
@@ -2900,7 +2908,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -2929,7 +2937,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>49</v>
       </c>
@@ -2958,7 +2966,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -2987,7 +2995,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -3016,7 +3024,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -3045,7 +3053,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="6">
         <v>53</v>
       </c>
@@ -3074,7 +3082,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>54</v>
       </c>
@@ -3103,7 +3111,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>55</v>
       </c>
@@ -3132,7 +3140,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -3161,7 +3169,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="6">
         <v>57</v>
       </c>
@@ -3190,7 +3198,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -3219,7 +3227,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
         <v>59</v>
       </c>
@@ -3248,7 +3256,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -3277,7 +3285,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>61</v>
       </c>
@@ -3306,7 +3314,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -3335,7 +3343,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -3364,7 +3372,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -3393,7 +3401,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -3422,7 +3430,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -3451,7 +3459,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
         <v>67</v>
       </c>
@@ -3480,7 +3488,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
         <v>68</v>
       </c>
@@ -3509,7 +3517,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
         <v>69</v>
       </c>
@@ -3538,7 +3546,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
         <v>70</v>
       </c>
@@ -3567,7 +3575,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
         <v>71</v>
       </c>
@@ -3596,7 +3604,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -3625,7 +3633,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
         <v>73</v>
       </c>
@@ -3654,7 +3662,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -3683,7 +3691,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
         <v>75</v>
       </c>
@@ -3712,7 +3720,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -3741,7 +3749,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
         <v>77</v>
       </c>
@@ -3770,7 +3778,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="6">
         <v>78</v>
       </c>
@@ -3799,7 +3807,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="4">
         <v>79</v>
       </c>
@@ -3828,7 +3836,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="6">
         <v>80</v>
       </c>
@@ -3857,7 +3865,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
         <v>81</v>
       </c>
@@ -3886,7 +3894,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>82</v>
       </c>
@@ -3915,7 +3923,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
         <v>83</v>
       </c>
@@ -3944,7 +3952,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -3973,7 +3981,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
         <v>85</v>
       </c>
@@ -4002,7 +4010,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -4031,7 +4039,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
         <v>87</v>
       </c>
@@ -4060,7 +4068,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
         <v>88</v>
       </c>
@@ -4089,7 +4097,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
         <v>89</v>
       </c>
@@ -4118,7 +4126,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
         <v>90</v>
       </c>
@@ -4147,7 +4155,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="4">
         <v>91</v>
       </c>
@@ -4176,7 +4184,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
         <v>92</v>
       </c>
@@ -4205,7 +4213,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="4">
         <v>93</v>
       </c>
@@ -4234,7 +4242,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
         <v>94</v>
       </c>
@@ -4263,7 +4271,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" s="4">
         <v>95</v>
       </c>
@@ -4292,7 +4300,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" s="4">
         <v>96</v>
       </c>
@@ -4321,7 +4329,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="4">
         <v>97</v>
       </c>
@@ -4350,7 +4358,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="6">
         <v>98</v>
       </c>
@@ -4379,7 +4387,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="4">
         <v>99</v>
       </c>
@@ -4408,7 +4416,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -4437,7 +4445,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -4466,7 +4474,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="4">
         <v>102</v>
       </c>
@@ -4495,7 +4503,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" s="4">
         <v>103</v>
       </c>
@@ -4524,7 +4532,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
         <v>104</v>
       </c>
@@ -4553,7 +4561,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="4">
         <v>105</v>
       </c>
@@ -4582,7 +4590,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" s="4">
         <v>106</v>
       </c>
@@ -4611,7 +4619,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="6">
         <v>107</v>
       </c>
@@ -4640,7 +4648,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="4">
         <v>108</v>
       </c>
@@ -4669,7 +4677,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="4">
         <v>109</v>
       </c>
@@ -4698,7 +4706,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="4">
         <v>110</v>
       </c>
@@ -4727,7 +4735,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
         <v>111</v>
       </c>
@@ -4756,7 +4764,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>112</v>
       </c>
@@ -4785,7 +4793,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
         <v>113</v>
       </c>
@@ -4814,7 +4822,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" s="4">
         <v>114</v>
       </c>
@@ -4843,7 +4851,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="116" spans="1:9">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="4">
         <v>115</v>
       </c>
@@ -4872,7 +4880,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>116</v>
       </c>
@@ -4901,7 +4909,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="4">
         <v>117</v>
       </c>
@@ -4930,7 +4938,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>118</v>
       </c>
@@ -4959,7 +4967,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="4">
         <v>119</v>
       </c>
@@ -4988,7 +4996,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="4">
         <v>120</v>
       </c>
@@ -5017,7 +5025,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="122" spans="1:9">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="6">
         <v>121</v>
       </c>
@@ -5046,7 +5054,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="123" spans="1:9">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="6">
         <v>122</v>
       </c>
@@ -5075,7 +5083,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="124" spans="1:9">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
         <v>123</v>
       </c>
@@ -5104,7 +5112,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="125" spans="1:9">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" s="4">
         <v>124</v>
       </c>
@@ -5133,7 +5141,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="126" spans="1:9">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="4">
         <v>125</v>
       </c>
@@ -5162,7 +5170,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="127" spans="1:9">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>126</v>
       </c>
@@ -5191,7 +5199,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="128" spans="1:9">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
         <v>127</v>
       </c>
@@ -5220,7 +5228,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="129" spans="1:9">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="4">
         <v>128</v>
       </c>
@@ -5249,7 +5257,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="4">
         <v>129</v>
       </c>
@@ -5278,7 +5286,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="131" spans="1:9">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="4">
         <v>130</v>
       </c>
@@ -5307,7 +5315,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="132" spans="1:9">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="5">
         <v>131</v>
       </c>
@@ -5336,7 +5344,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="133" spans="1:9">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="4">
         <v>132</v>
       </c>
@@ -5365,7 +5373,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="134" spans="1:9">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="4">
         <v>133</v>
       </c>
@@ -5394,7 +5402,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="135" spans="1:9">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -5423,7 +5431,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="136" spans="1:9">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="5">
         <v>135</v>
       </c>
@@ -5452,7 +5460,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="137" spans="1:9">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="4">
         <v>136</v>
       </c>
@@ -5481,7 +5489,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="138" spans="1:9">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="4">
         <v>137</v>
       </c>
@@ -5510,7 +5518,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="139" spans="1:9">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
         <v>138</v>
       </c>
@@ -5539,7 +5547,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="140" spans="1:9">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="4">
         <v>139</v>
       </c>
@@ -5568,7 +5576,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="141" spans="1:9">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -5597,7 +5605,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="142" spans="1:9">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" s="4">
         <v>141</v>
       </c>
@@ -5626,7 +5634,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="143" spans="1:9">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
         <v>142</v>
       </c>
@@ -5655,7 +5663,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="144" spans="1:9">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
         <v>143</v>
       </c>
@@ -5684,7 +5692,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="145" spans="1:9">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -5713,7 +5721,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="146" spans="1:9">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
         <v>145</v>
       </c>
@@ -5742,7 +5750,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="147" spans="1:9">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="6">
         <v>146</v>
       </c>
@@ -5771,7 +5779,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="148" spans="1:9">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" s="4">
         <v>147</v>
       </c>
@@ -5800,7 +5808,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="149" spans="1:9">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" s="6">
         <v>148</v>
       </c>
@@ -5829,7 +5837,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="150" spans="1:9">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="4">
         <v>149</v>
       </c>
@@ -5858,7 +5866,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="151" spans="1:9">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" s="4">
         <v>150</v>
       </c>
@@ -5887,7 +5895,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="152" spans="1:9">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" s="4">
         <v>151</v>
       </c>
@@ -5916,7 +5924,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="153" spans="1:9">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="4">
         <v>152</v>
       </c>
@@ -5945,7 +5953,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="154" spans="1:9">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" s="5">
         <v>153</v>
       </c>
@@ -5974,7 +5982,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="155" spans="1:9">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
         <v>154</v>
       </c>
@@ -6003,7 +6011,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="156" spans="1:9">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" s="4">
         <v>155</v>
       </c>
@@ -6032,7 +6040,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="157" spans="1:9">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
         <v>156</v>
       </c>
@@ -6061,7 +6069,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="158" spans="1:9">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" s="4">
         <v>157</v>
       </c>
@@ -6090,7 +6098,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="159" spans="1:9">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
         <v>158</v>
       </c>
@@ -6119,7 +6127,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="160" spans="1:9">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" s="6">
         <v>159</v>
       </c>
@@ -6148,7 +6156,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="161" spans="1:9">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" s="4">
         <v>160</v>
       </c>
@@ -6177,7 +6185,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="162" spans="1:9">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" s="4">
         <v>161</v>
       </c>
@@ -6206,7 +6214,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="163" spans="1:9">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" s="4">
         <v>162</v>
       </c>
@@ -6235,7 +6243,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="164" spans="1:9">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
         <v>163</v>
       </c>
@@ -6264,7 +6272,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="165" spans="1:9">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" s="3">
         <v>164</v>
       </c>
@@ -6293,7 +6301,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="166" spans="1:9">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" s="4">
         <v>165</v>
       </c>
@@ -6322,7 +6330,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="167" spans="1:9">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" s="4">
         <v>166</v>
       </c>
@@ -6351,7 +6359,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="168" spans="1:9">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" s="6">
         <v>167</v>
       </c>
@@ -6380,7 +6388,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="169" spans="1:9">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" s="4">
         <v>168</v>
       </c>
@@ -6409,7 +6417,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="170" spans="1:9">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" s="4">
         <v>169</v>
       </c>
@@ -6438,7 +6446,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="171" spans="1:9">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" s="4">
         <v>170</v>
       </c>
@@ -6467,7 +6475,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="172" spans="1:9">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
         <v>171</v>
       </c>
@@ -6496,7 +6504,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="173" spans="1:9">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" s="4">
         <v>172</v>
       </c>
@@ -6525,7 +6533,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="174" spans="1:9">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" s="4">
         <v>173</v>
       </c>
@@ -6554,7 +6562,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="175" spans="1:9">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" s="4">
         <v>174</v>
       </c>
@@ -6583,7 +6591,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="176" spans="1:9">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" s="4">
         <v>175</v>
       </c>
@@ -6612,7 +6620,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="177" spans="1:9">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" s="4">
         <v>176</v>
       </c>
@@ -6641,7 +6649,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="178" spans="1:9">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" s="4">
         <v>177</v>
       </c>
@@ -6670,7 +6678,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="179" spans="1:9">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" s="4">
         <v>178</v>
       </c>
@@ -6699,7 +6707,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="180" spans="1:9">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" s="4">
         <v>179</v>
       </c>
@@ -6728,7 +6736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="181" spans="1:9">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" s="4">
         <v>180</v>
       </c>
@@ -6757,7 +6765,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="182" spans="1:9">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" s="3">
         <v>181</v>
       </c>
@@ -6786,7 +6794,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="183" spans="1:9">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" s="4">
         <v>182</v>
       </c>
@@ -6815,7 +6823,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="184" spans="1:9">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" s="4">
         <v>183</v>
       </c>
@@ -6844,7 +6852,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="185" spans="1:9">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" s="6">
         <v>184</v>
       </c>
@@ -6873,7 +6881,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="186" spans="1:9">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" s="4">
         <v>185</v>
       </c>
@@ -6902,7 +6910,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="187" spans="1:9">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" s="4">
         <v>186</v>
       </c>
@@ -6931,7 +6939,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="188" spans="1:9">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" s="6">
         <v>187</v>
       </c>
@@ -6960,7 +6968,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="189" spans="1:9">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" s="6">
         <v>188</v>
       </c>
@@ -6989,7 +6997,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="190" spans="1:9">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" s="4">
         <v>189</v>
       </c>
@@ -7018,7 +7026,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="191" spans="1:9">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" s="4">
         <v>190</v>
       </c>
@@ -7047,7 +7055,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="192" spans="1:9">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" s="4">
         <v>191</v>
       </c>
@@ -7076,7 +7084,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="193" spans="1:9">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" s="4">
         <v>192</v>
       </c>
@@ -7105,7 +7113,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="194" spans="1:9">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" s="6">
         <v>193</v>
       </c>
@@ -7134,7 +7142,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="195" spans="1:9">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" s="3">
         <v>194</v>
       </c>
@@ -7163,7 +7171,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="196" spans="1:9">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
         <v>195</v>
       </c>
@@ -7192,7 +7200,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="197" spans="1:9">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" s="4">
         <v>196</v>
       </c>
@@ -7221,7 +7229,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="198" spans="1:9">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" s="4">
         <v>197</v>
       </c>
@@ -7250,7 +7258,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="199" spans="1:9">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" s="5">
         <v>198</v>
       </c>
@@ -7279,7 +7287,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="200" spans="1:9">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" s="4">
         <v>199</v>
       </c>
@@ -7308,7 +7316,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="201" spans="1:9">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" s="4">
         <v>200</v>
       </c>
@@ -7337,7 +7345,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="202" spans="1:9">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="5">
         <v>201</v>
       </c>
@@ -7366,7 +7374,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="203" spans="1:9">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" s="4">
         <v>202</v>
       </c>
@@ -7395,7 +7403,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="204" spans="1:9">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" s="4">
         <v>203</v>
       </c>
@@ -7424,7 +7432,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="205" spans="1:9">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" s="4">
         <v>204</v>
       </c>
@@ -7453,7 +7461,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="206" spans="1:9">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" s="4">
         <v>205</v>
       </c>
@@ -7482,7 +7490,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="207" spans="1:9">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" s="2">
         <v>206</v>
       </c>
@@ -7511,7 +7519,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="208" spans="1:9">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" s="4">
         <v>207</v>
       </c>
@@ -7540,7 +7548,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="209" spans="1:9">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" s="4">
         <v>208</v>
       </c>
@@ -7569,7 +7577,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="210" spans="1:9">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" s="4">
         <v>209</v>
       </c>
@@ -7598,7 +7606,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="211" spans="1:9">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" s="4">
         <v>210</v>
       </c>
@@ -7627,7 +7635,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="212" spans="1:9">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" s="4">
         <v>211</v>
       </c>
@@ -7656,7 +7664,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="213" spans="1:9">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" s="4">
         <v>212</v>
       </c>
@@ -7685,7 +7693,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="214" spans="1:9">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" s="5">
         <v>213</v>
       </c>
@@ -7714,7 +7722,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="215" spans="1:9">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" s="5">
         <v>214</v>
       </c>
@@ -7743,7 +7751,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="216" spans="1:9">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" s="4">
         <v>215</v>
       </c>
@@ -7772,7 +7780,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="217" spans="1:9">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" s="4">
         <v>216</v>
       </c>
@@ -7801,7 +7809,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="218" spans="1:9">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" s="5">
         <v>217</v>
       </c>
@@ -7830,7 +7838,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="219" spans="1:9">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" s="6">
         <v>218</v>
       </c>
@@ -7859,7 +7867,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="220" spans="1:9">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" s="4">
         <v>219</v>
       </c>
@@ -7888,7 +7896,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="221" spans="1:9">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" s="5">
         <v>220</v>
       </c>
@@ -7917,7 +7925,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="222" spans="1:9">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" s="4">
         <v>221</v>
       </c>
@@ -7946,7 +7954,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="223" spans="1:9">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" s="4">
         <v>222</v>
       </c>
@@ -7975,7 +7983,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="224" spans="1:9">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" s="5">
         <v>223</v>
       </c>
@@ -8004,7 +8012,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="225" spans="1:9">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" s="2">
         <v>224</v>
       </c>
@@ -8033,7 +8041,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="226" spans="1:9">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" s="4">
         <v>225</v>
       </c>
@@ -8062,7 +8070,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="227" spans="1:9">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" s="4">
         <v>226</v>
       </c>
@@ -8091,7 +8099,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="228" spans="1:9">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" s="6">
         <v>227</v>
       </c>
@@ -8120,7 +8128,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="229" spans="1:9">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" s="4">
         <v>228</v>
       </c>
@@ -8149,7 +8157,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="230" spans="1:9">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" s="4">
         <v>229</v>
       </c>
@@ -8178,7 +8186,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="231" spans="1:9">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" s="4">
         <v>230</v>
       </c>
@@ -8207,7 +8215,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="232" spans="1:9">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" s="4">
         <v>231</v>
       </c>
@@ -8236,7 +8244,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="233" spans="1:9">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" s="4">
         <v>232</v>
       </c>
@@ -8265,7 +8273,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="234" spans="1:9">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" s="4">
         <v>233</v>
       </c>
@@ -8294,7 +8302,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="235" spans="1:9">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" s="2">
         <v>234</v>
       </c>
@@ -8323,7 +8331,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="236" spans="1:9">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" s="4">
         <v>235</v>
       </c>
@@ -8352,7 +8360,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="237" spans="1:9">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" s="4">
         <v>236</v>
       </c>
@@ -8381,7 +8389,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="238" spans="1:9">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" s="4">
         <v>237</v>
       </c>
@@ -8410,7 +8418,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="239" spans="1:9">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" s="4">
         <v>238</v>
       </c>
@@ -8439,7 +8447,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="240" spans="1:9">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" s="4">
         <v>239</v>
       </c>
@@ -8468,7 +8476,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="241" spans="1:9">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" s="2">
         <v>240</v>
       </c>
@@ -8487,28 +8495,17 @@
       <c r="F241" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="G241" s="2" t="s">
+      <c r="G241" s="2">
+        <v>0</v>
+      </c>
+      <c r="H241" s="2" t="s">
         <v>352</v>
-      </c>
-      <c r="H241" s="2" t="s">
-        <v>353</v>
       </c>
       <c r="I241" s="2" t="s">
         <v>16</v>
       </c>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>